--- a/packages/calculators/src/modules/test/10.1-solid-waste.xlsx
+++ b/packages/calculators/src/modules/test/10.1-solid-waste.xlsx
@@ -1,20 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators-internal/packages/calculators/src/modules/test/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C17E295-9462-B64B-8EF0-E6EBC04BC2CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB77C36-C68E-D748-B59F-24285B8FDE41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15880" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15880" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
   <sheets>
     <sheet name="10.1" sheetId="4" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -297,14 +295,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -320,6 +316,34 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="common"/>
+    </sheetNames>
+    <definedNames>
+      <definedName name="common_cch4" refersTo="='common'!$B$3"/>
+      <definedName name="common_cco2" refersTo="='common'!$B$2"/>
+    </definedNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="B2">
+            <v>3.67</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>1.33</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -820,11 +844,11 @@
         <v>6000</v>
       </c>
       <c r="G5">
-        <f>$Y$5</f>
+        <f t="shared" ref="G5:G10" si="0">$Y$5</f>
         <v>7.5000000000000002E-4</v>
       </c>
       <c r="H5">
-        <f>$Y$6</f>
+        <f t="shared" ref="H5:H10" si="1">$Y$6</f>
         <v>1E-4</v>
       </c>
       <c r="I5">
@@ -832,11 +856,11 @@
         <v>0.95</v>
       </c>
       <c r="J5">
-        <f>$Z$5</f>
+        <f t="shared" ref="J5:J10" si="2">$Z$5</f>
         <v>9.4300000000000002E-5</v>
       </c>
       <c r="K5">
-        <f>$Z$6</f>
+        <f t="shared" ref="K5:K10" si="3">$Z$6</f>
         <v>0</v>
       </c>
       <c r="L5">
@@ -844,27 +868,27 @@
         <v>9.4299999999999995E-2</v>
       </c>
       <c r="M5">
-        <f>$AC$4</f>
+        <f t="shared" ref="M5:M10" si="4">$AC$4</f>
         <v>5.0500000000000003E-2</v>
       </c>
       <c r="N5">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
+        <f t="shared" ref="N5:N10" si="5">$AC$5</f>
+        <v>3.67</v>
       </c>
       <c r="O5">
         <f>C5*M5*N5</f>
-        <v>555.5</v>
+        <v>556.005</v>
       </c>
       <c r="P5">
-        <f>$Y$9</f>
+        <f t="shared" ref="P5:P10" si="6">$Y$9</f>
         <v>5.0200000000000002E-2</v>
       </c>
       <c r="Q5">
-        <f>$Y$10</f>
+        <f t="shared" ref="Q5:Q10" si="7">$Y$10</f>
         <v>2.5100000000000001E-2</v>
       </c>
       <c r="R5">
-        <f>$Y$11</f>
+        <f t="shared" ref="R5:R10" si="8">$Y$11</f>
         <v>3.95E-2</v>
       </c>
       <c r="S5">
@@ -873,7 +897,7 @@
       </c>
       <c r="T5">
         <f>O5</f>
-        <v>555.5</v>
+        <v>556.005</v>
       </c>
       <c r="U5">
         <f>I5+S5</f>
@@ -896,8 +920,8 @@
         <v>20</v>
       </c>
       <c r="AC5">
-        <f>44/12</f>
-        <v>3.6666666666666665</v>
+        <f>[1]!common_cco2</f>
+        <v>3.67</v>
       </c>
       <c r="AE5" t="s">
         <v>6</v>
@@ -944,70 +968,70 @@
         <v>1000</v>
       </c>
       <c r="G6">
-        <f>$Y$5</f>
+        <f t="shared" si="0"/>
         <v>7.5000000000000002E-4</v>
       </c>
       <c r="H6">
-        <f>$Y$6</f>
+        <f t="shared" si="1"/>
         <v>1E-4</v>
       </c>
       <c r="I6">
-        <f t="shared" ref="I6:I10" si="0">A6*G6+B6*H6</f>
+        <f t="shared" ref="I6:I10" si="9">A6*G6+B6*H6</f>
         <v>0.85</v>
       </c>
       <c r="J6">
-        <f>$Z$5</f>
+        <f t="shared" si="2"/>
         <v>9.4300000000000002E-5</v>
       </c>
       <c r="K6">
-        <f>$Z$6</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L6">
-        <f t="shared" ref="L6:L10" si="1">A6*J6+B6*K6</f>
+        <f t="shared" ref="L6:L10" si="10">A6*J6+B6*K6</f>
         <v>9.4299999999999995E-2</v>
       </c>
       <c r="M6">
-        <f>$AC$4</f>
+        <f t="shared" si="4"/>
         <v>5.0500000000000003E-2</v>
       </c>
       <c r="N6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
+        <f t="shared" si="5"/>
+        <v>3.67</v>
       </c>
       <c r="O6">
-        <f t="shared" ref="O6:O10" si="2">C6*M6*N6</f>
-        <v>185.16666666666666</v>
+        <f t="shared" ref="O6:O10" si="11">C6*M6*N6</f>
+        <v>185.33500000000001</v>
       </c>
       <c r="P6">
-        <f>$Y$9</f>
+        <f t="shared" si="6"/>
         <v>5.0200000000000002E-2</v>
       </c>
       <c r="Q6">
-        <f>$Y$10</f>
+        <f t="shared" si="7"/>
         <v>2.5100000000000001E-2</v>
       </c>
       <c r="R6">
-        <f>$Y$11</f>
+        <f t="shared" si="8"/>
         <v>3.95E-2</v>
       </c>
       <c r="S6">
-        <f t="shared" ref="S6:S10" si="3">D6*P6+E6*Q6+F6*R6</f>
+        <f t="shared" ref="S6:S10" si="12">D6*P6+E6*Q6+F6*R6</f>
         <v>114.80000000000001</v>
       </c>
       <c r="T6">
-        <f t="shared" ref="T6:T10" si="4">O6</f>
-        <v>185.16666666666666</v>
+        <f t="shared" ref="T6:T10" si="13">O6</f>
+        <v>185.33500000000001</v>
       </c>
       <c r="U6">
-        <f t="shared" ref="U6:U10" si="5">I6+S6</f>
+        <f t="shared" ref="U6:U10" si="14">I6+S6</f>
         <v>115.65</v>
       </c>
       <c r="V6">
-        <f t="shared" ref="V6:V10" si="6">L6</f>
+        <f t="shared" ref="V6:V10" si="15">L6</f>
         <v>9.4299999999999995E-2</v>
       </c>
-      <c r="X6" s="3" t="s">
+      <c r="X6" t="s">
         <v>9</v>
       </c>
       <c r="Y6">
@@ -1020,8 +1044,8 @@
         <v>62</v>
       </c>
       <c r="AC6">
-        <f>16/12</f>
-        <v>1.3333333333333333</v>
+        <f>[1]!common_cch4</f>
+        <v>1.33</v>
       </c>
       <c r="AE6" t="s">
         <v>4</v>
@@ -1059,67 +1083,67 @@
         <v>1234</v>
       </c>
       <c r="G7">
-        <f>$Y$5</f>
+        <f t="shared" si="0"/>
         <v>7.5000000000000002E-4</v>
       </c>
       <c r="H7">
-        <f>$Y$6</f>
+        <f t="shared" si="1"/>
         <v>1E-4</v>
       </c>
       <c r="I7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>0.95</v>
       </c>
       <c r="J7">
-        <f>$Z$5</f>
+        <f t="shared" si="2"/>
         <v>9.4300000000000002E-5</v>
       </c>
       <c r="K7">
-        <f>$Z$6</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>9.4299999999999995E-2</v>
       </c>
       <c r="M7">
-        <f>$AC$4</f>
+        <f t="shared" si="4"/>
         <v>5.0500000000000003E-2</v>
       </c>
       <c r="N7">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
+        <f t="shared" si="5"/>
+        <v>3.67</v>
       </c>
       <c r="O7">
-        <f t="shared" si="2"/>
-        <v>228.49566666666669</v>
+        <f t="shared" si="11"/>
+        <v>228.70339000000001</v>
       </c>
       <c r="P7">
-        <f>$Y$9</f>
+        <f t="shared" si="6"/>
         <v>5.0200000000000002E-2</v>
       </c>
       <c r="Q7">
-        <f>$Y$10</f>
+        <f t="shared" si="7"/>
         <v>2.5100000000000001E-2</v>
       </c>
       <c r="R7">
-        <f>$Y$11</f>
+        <f t="shared" si="8"/>
         <v>3.95E-2</v>
       </c>
       <c r="S7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T7">
-        <f t="shared" si="4"/>
-        <v>228.49566666666669</v>
+        <f t="shared" si="13"/>
+        <v>228.70339000000001</v>
       </c>
       <c r="U7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>0.95</v>
       </c>
       <c r="V7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>9.4299999999999995E-2</v>
       </c>
       <c r="AB7" t="s">
@@ -1164,67 +1188,67 @@
         <v>6000</v>
       </c>
       <c r="G8">
-        <f>$Y$5</f>
+        <f t="shared" si="0"/>
         <v>7.5000000000000002E-4</v>
       </c>
       <c r="H8">
-        <f>$Y$6</f>
+        <f t="shared" si="1"/>
         <v>1E-4</v>
       </c>
       <c r="I8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J8">
-        <f>$Z$5</f>
+        <f t="shared" si="2"/>
         <v>9.4300000000000002E-5</v>
       </c>
       <c r="K8">
-        <f>$Z$6</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M8">
-        <f>$AC$4</f>
+        <f t="shared" si="4"/>
         <v>5.0500000000000003E-2</v>
       </c>
       <c r="N8">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
+        <f t="shared" si="5"/>
+        <v>3.67</v>
       </c>
       <c r="O8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P8">
-        <f>$Y$9</f>
+        <f t="shared" si="6"/>
         <v>5.0200000000000002E-2</v>
       </c>
       <c r="Q8">
-        <f>$Y$10</f>
+        <f t="shared" si="7"/>
         <v>2.5100000000000001E-2</v>
       </c>
       <c r="R8">
-        <f>$Y$11</f>
+        <f t="shared" si="8"/>
         <v>3.95E-2</v>
       </c>
       <c r="S8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>563.29999999999995</v>
       </c>
       <c r="T8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="U8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>563.29999999999995</v>
       </c>
       <c r="V8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="X8" t="s">
@@ -1278,67 +1302,67 @@
         <v>6000</v>
       </c>
       <c r="G9">
-        <f>$Y$5</f>
+        <f t="shared" si="0"/>
         <v>7.5000000000000002E-4</v>
       </c>
       <c r="H9">
-        <f>$Y$6</f>
+        <f t="shared" si="1"/>
         <v>1E-4</v>
       </c>
       <c r="I9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
       <c r="J9">
-        <f>$Z$5</f>
+        <f t="shared" si="2"/>
         <v>9.4300000000000002E-5</v>
       </c>
       <c r="K9">
-        <f>$Z$6</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M9">
-        <f>$AC$4</f>
+        <f t="shared" si="4"/>
         <v>5.0500000000000003E-2</v>
       </c>
       <c r="N9">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
+        <f t="shared" si="5"/>
+        <v>3.67</v>
       </c>
       <c r="O9">
-        <f t="shared" si="2"/>
-        <v>434.21583333333336</v>
+        <f t="shared" si="11"/>
+        <v>434.61057500000004</v>
       </c>
       <c r="P9">
-        <f>$Y$9</f>
+        <f t="shared" si="6"/>
         <v>5.0200000000000002E-2</v>
       </c>
       <c r="Q9">
-        <f>$Y$10</f>
+        <f t="shared" si="7"/>
         <v>2.5100000000000001E-2</v>
       </c>
       <c r="R9">
-        <f>$Y$11</f>
+        <f t="shared" si="8"/>
         <v>3.95E-2</v>
       </c>
       <c r="S9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>437.8</v>
       </c>
       <c r="T9">
-        <f t="shared" si="4"/>
-        <v>434.21583333333336</v>
+        <f t="shared" si="13"/>
+        <v>434.61057500000004</v>
       </c>
       <c r="U9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>438</v>
       </c>
       <c r="V9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="X9" t="s">
@@ -1395,67 +1419,67 @@
         <v>6000</v>
       </c>
       <c r="G10">
-        <f>$Y$5</f>
+        <f t="shared" si="0"/>
         <v>7.5000000000000002E-4</v>
       </c>
       <c r="H10">
-        <f>$Y$6</f>
+        <f t="shared" si="1"/>
         <v>1E-4</v>
       </c>
       <c r="I10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>0.95</v>
       </c>
       <c r="J10">
-        <f>$Z$5</f>
+        <f t="shared" si="2"/>
         <v>9.4300000000000002E-5</v>
       </c>
       <c r="K10">
-        <f>$Z$6</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>9.4299999999999995E-2</v>
       </c>
       <c r="M10">
-        <f>$AC$4</f>
+        <f t="shared" si="4"/>
         <v>5.0500000000000003E-2</v>
       </c>
       <c r="N10">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
+        <f t="shared" si="5"/>
+        <v>3.67</v>
       </c>
       <c r="O10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P10">
-        <f>$Y$9</f>
+        <f t="shared" si="6"/>
         <v>5.0200000000000002E-2</v>
       </c>
       <c r="Q10">
-        <f>$Y$10</f>
+        <f t="shared" si="7"/>
         <v>2.5100000000000001E-2</v>
       </c>
       <c r="R10">
-        <f>$Y$11</f>
+        <f t="shared" si="8"/>
         <v>3.95E-2</v>
       </c>
       <c r="S10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>563.29999999999995</v>
       </c>
       <c r="T10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="U10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>564.25</v>
       </c>
       <c r="V10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>9.4299999999999995E-2</v>
       </c>
       <c r="X10" t="s">
@@ -1660,1031 +1684,997 @@
       <c r="W16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="X16" s="5" t="s">
+      <c r="X16" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="Y16" s="5" t="s">
+      <c r="Y16" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="Z16" s="5" t="s">
+      <c r="Z16" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
+      <c r="A17" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17">
         <v>1234</v>
       </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6">
+      <c r="E17">
         <f>_xlfn.XLOOKUP(B17, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.5</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17">
         <f>IF(C17&lt;&gt;"", C17,D17*E17)</f>
         <v>1234</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17">
         <f>_xlfn.XLOOKUP(A17,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17">
         <f>G17*F17</f>
         <v>0</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17">
         <f>_xlfn.XLOOKUP(A17,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="6">
+      <c r="J17">
         <f>F17*I17</f>
         <v>0</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K17">
         <f>_xlfn.XLOOKUP($B17,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L17" s="6">
+      <c r="L17">
         <f>_xlfn.XLOOKUP($B17, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.38</v>
       </c>
-      <c r="M17" s="6">
+      <c r="M17">
         <f>_xlfn.XLOOKUP($B17, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N17" s="6">
+      <c r="N17">
         <f>_xlfn.XLOOKUP($B17, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O17" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P17" s="6">
+      <c r="O17">
+        <f t="shared" ref="O17:O24" si="16">$AC$5</f>
+        <v>3.67</v>
+      </c>
+      <c r="P17">
         <f>IF(A17&lt;&gt;"Incineration", 0, F17*K17*L17*M17*N17*O17)</f>
         <v>0</v>
       </c>
-      <c r="Q17" s="6">
+      <c r="Q17">
         <f>_xlfn.XLOOKUP($B17,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.15</v>
       </c>
-      <c r="R17" s="6">
+      <c r="R17">
         <f>_xlfn.XLOOKUP($B17,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.84</v>
       </c>
-      <c r="S17" s="6">
+      <c r="S17">
         <f>$AC$7</f>
         <v>0.5</v>
       </c>
-      <c r="T17" s="6">
-        <f>_xlfn.XLOOKUP(A17,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U17" s="6">
-        <f>_xlfn.XLOOKUP(A17,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V17" s="6">
+      <c r="T17">
+        <f t="shared" ref="T17:T56" si="17">_xlfn.XLOOKUP(A17,$X$9:$X$11,Z$9:Z$11, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <f t="shared" ref="U17:U56" si="18">_xlfn.XLOOKUP(A17,$X$9:$X$11,AA$9:AA$11, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="V17">
         <f>$AC$6</f>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W17" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="W17">
         <f>F17*Q17*R17*S17*T17*V17*(1-U17)</f>
         <v>0</v>
       </c>
-      <c r="X17" s="6">
+      <c r="X17">
         <f>SUM(P17:P26)</f>
-        <v>188.51871719999997</v>
-      </c>
-      <c r="Y17" s="6">
+        <v>188.69009785199998</v>
+      </c>
+      <c r="Y17">
         <f>SUM(H17:H26,W17:W26)</f>
         <v>0</v>
       </c>
-      <c r="Z17" s="6">
+      <c r="Z17">
         <f>SUM(J17:J26)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
+      <c r="A18" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18">
         <v>342</v>
       </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6">
+      <c r="E18">
         <f>_xlfn.XLOOKUP(B18, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.09</v>
       </c>
-      <c r="F18" s="6">
-        <f t="shared" ref="F18:F24" si="7">IF(C18&lt;&gt;"", C18,D18*E18)</f>
+      <c r="F18">
+        <f t="shared" ref="F18:F24" si="19">IF(C18&lt;&gt;"", C18,D18*E18)</f>
         <v>342</v>
       </c>
-      <c r="G18" s="6">
-        <f t="shared" ref="G18:G24" si="8">_xlfn.XLOOKUP(A18,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="6">
-        <f t="shared" ref="H18:H23" si="9">G18*F18</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="6">
-        <f t="shared" ref="I18:I24" si="10">_xlfn.XLOOKUP(A18,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="6">
-        <f t="shared" ref="J18:J24" si="11">F18*I18</f>
-        <v>0</v>
-      </c>
-      <c r="K18" s="6">
+      <c r="G18">
+        <f t="shared" ref="G18:G24" si="20">_xlfn.XLOOKUP(A18,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <f t="shared" ref="H18:H23" si="21">G18*F18</f>
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <f t="shared" ref="I18:I24" si="22">_xlfn.XLOOKUP(A18,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <f t="shared" ref="J18:J24" si="23">F18*I18</f>
+        <v>0</v>
+      </c>
+      <c r="K18">
         <f>_xlfn.XLOOKUP($B18,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.9</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L18">
         <f>_xlfn.XLOOKUP($B18, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.46</v>
       </c>
-      <c r="M18" s="6">
+      <c r="M18">
         <f>_xlfn.XLOOKUP($B18, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.01</v>
       </c>
-      <c r="N18" s="6">
+      <c r="N18">
         <f>_xlfn.XLOOKUP($B18, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O18" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P18" s="6">
-        <f t="shared" ref="P18:P24" si="12">IF(A18&lt;&gt;"Incineration", 0, F18*K18*L18*M18*N18*O18)</f>
-        <v>3.6860075999999999</v>
-      </c>
-      <c r="Q18" s="6">
+      <c r="O18">
+        <f t="shared" si="16"/>
+        <v>3.67</v>
+      </c>
+      <c r="P18">
+        <f t="shared" ref="P18:P24" si="24">IF(A18&lt;&gt;"Incineration", 0, F18*K18*L18*M18*N18*O18)</f>
+        <v>3.689358516</v>
+      </c>
+      <c r="Q18">
         <f>_xlfn.XLOOKUP($B18,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.4</v>
       </c>
-      <c r="R18" s="6">
+      <c r="R18">
         <f>_xlfn.XLOOKUP($B18,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.49</v>
       </c>
-      <c r="S18" s="6">
-        <f t="shared" ref="S18:S56" si="13">$AC$7</f>
-        <v>0.5</v>
-      </c>
-      <c r="T18" s="6">
-        <f>_xlfn.XLOOKUP(A18,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U18" s="6">
-        <f>_xlfn.XLOOKUP(A18,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V18" s="6">
-        <f t="shared" ref="V18:V56" si="14">$AC$6</f>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W18" s="6">
-        <f t="shared" ref="W18:W24" si="15">F18*Q18*R18*S18*T18*V18*(1-U18)</f>
-        <v>0</v>
-      </c>
-      <c r="X18" s="6"/>
-      <c r="Y18" s="6"/>
-      <c r="Z18" s="6"/>
+      <c r="S18">
+        <f t="shared" ref="S18:S56" si="25">$AC$7</f>
+        <v>0.5</v>
+      </c>
+      <c r="T18">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <f t="shared" ref="V18:V56" si="26">$AC$6</f>
+        <v>1.33</v>
+      </c>
+      <c r="W18">
+        <f t="shared" ref="W18:W24" si="27">F18*Q18*R18*S18*T18*V18*(1-U18)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
+      <c r="A19" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" t="s">
         <v>4</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19">
         <v>346</v>
       </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6">
+      <c r="E19">
         <f>_xlfn.XLOOKUP(B19, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.24</v>
       </c>
-      <c r="F19" s="6">
-        <f t="shared" si="7"/>
+      <c r="F19">
+        <f t="shared" si="19"/>
         <v>346</v>
       </c>
-      <c r="G19" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H19" s="6">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="I19" s="6">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K19" s="6">
+      <c r="G19">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="K19">
         <f>_xlfn.XLOOKUP($B19,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L19" s="6">
+      <c r="L19">
         <f>_xlfn.XLOOKUP($B19, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.49</v>
       </c>
-      <c r="M19" s="6">
+      <c r="M19">
         <f>_xlfn.XLOOKUP($B19, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N19" s="6">
+      <c r="N19">
         <f>_xlfn.XLOOKUP($B19, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O19" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P19" s="6">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="6">
+      <c r="O19">
+        <f t="shared" si="16"/>
+        <v>3.67</v>
+      </c>
+      <c r="P19">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Q19">
         <f>_xlfn.XLOOKUP($B19,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.2</v>
       </c>
-      <c r="R19" s="6">
+      <c r="R19">
         <f>_xlfn.XLOOKUP($B19,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.47</v>
       </c>
-      <c r="S19" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T19" s="6">
-        <f>_xlfn.XLOOKUP(A19,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U19" s="6">
-        <f>_xlfn.XLOOKUP(A19,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V19" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W19" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X19" s="6"/>
-      <c r="Y19" s="6"/>
-      <c r="Z19" s="6"/>
+      <c r="S19">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W19">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
+      <c r="A20" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20">
         <v>1435</v>
       </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6">
+      <c r="E20">
         <f>_xlfn.XLOOKUP(B20, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.15</v>
       </c>
-      <c r="F20" s="6">
-        <f t="shared" si="7"/>
+      <c r="F20">
+        <f t="shared" si="19"/>
         <v>1435</v>
       </c>
-      <c r="G20" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H20" s="6">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="6">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="6">
+      <c r="G20">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="K20">
         <f>_xlfn.XLOOKUP($B20,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L20" s="6">
+      <c r="L20">
         <f>_xlfn.XLOOKUP($B20, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M20" s="6">
+      <c r="M20">
         <f>_xlfn.XLOOKUP($B20, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N20" s="6">
+      <c r="N20">
         <f>_xlfn.XLOOKUP($B20, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O20" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P20" s="6">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="6">
+      <c r="O20">
+        <f t="shared" si="16"/>
+        <v>3.67</v>
+      </c>
+      <c r="P20">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Q20">
         <f>_xlfn.XLOOKUP($B20,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.43</v>
       </c>
-      <c r="R20" s="6">
+      <c r="R20">
         <f>_xlfn.XLOOKUP($B20,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.1</v>
       </c>
-      <c r="S20" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T20" s="6">
-        <f>_xlfn.XLOOKUP(A20,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U20" s="6">
-        <f>_xlfn.XLOOKUP(A20,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V20" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W20" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X20" s="6"/>
-      <c r="Y20" s="6"/>
-      <c r="Z20" s="6"/>
+      <c r="S20">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W20">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A21" s="6" t="s">
+      <c r="A21" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6">
+      <c r="D21">
         <v>1235</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21">
         <f>_xlfn.XLOOKUP(B21, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.15</v>
       </c>
-      <c r="F21" s="6">
-        <f t="shared" si="7"/>
+      <c r="F21">
+        <f t="shared" si="19"/>
         <v>185.25</v>
       </c>
-      <c r="G21" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="6">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="6">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K21" s="6">
+      <c r="G21">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="K21">
         <f>_xlfn.XLOOKUP($B21,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.9</v>
       </c>
-      <c r="L21" s="6">
+      <c r="L21">
         <f>_xlfn.XLOOKUP($B21, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M21" s="6">
+      <c r="M21">
         <f>_xlfn.XLOOKUP($B21, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N21" s="6">
+      <c r="N21">
         <f>_xlfn.XLOOKUP($B21, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O21" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P21" s="6">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="6">
+      <c r="O21">
+        <f t="shared" si="16"/>
+        <v>3.67</v>
+      </c>
+      <c r="P21">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Q21">
         <f>_xlfn.XLOOKUP($B21,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.43</v>
       </c>
-      <c r="R21" s="6">
+      <c r="R21">
         <f>_xlfn.XLOOKUP($B21,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.1</v>
       </c>
-      <c r="S21" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T21" s="6">
-        <f>_xlfn.XLOOKUP(A21,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U21" s="6">
-        <f>_xlfn.XLOOKUP(A21,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V21" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W21" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X21" s="6"/>
-      <c r="Y21" s="6"/>
-      <c r="Z21" s="6"/>
+      <c r="S21">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W21">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A22" s="6" t="s">
+      <c r="A22" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6">
+      <c r="D22">
         <v>345</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22">
         <f>_xlfn.XLOOKUP(B22, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="F22" s="6">
-        <f t="shared" si="7"/>
+      <c r="F22">
+        <f t="shared" si="19"/>
         <v>48.300000000000004</v>
       </c>
-      <c r="G22" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H22" s="6">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="I22" s="6">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J22" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="6">
+      <c r="G22">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="K22">
         <f>_xlfn.XLOOKUP($B22,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.8</v>
       </c>
-      <c r="L22" s="6">
+      <c r="L22">
         <f>_xlfn.XLOOKUP($B22, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M22" s="6">
+      <c r="M22">
         <f>_xlfn.XLOOKUP($B22, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.2</v>
       </c>
-      <c r="N22" s="6">
+      <c r="N22">
         <f>_xlfn.XLOOKUP($B22, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O22" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P22" s="6">
-        <f t="shared" si="12"/>
-        <v>10.059280000000001</v>
-      </c>
-      <c r="Q22" s="6">
+      <c r="O22">
+        <f t="shared" si="16"/>
+        <v>3.67</v>
+      </c>
+      <c r="P22">
+        <f t="shared" si="24"/>
+        <v>10.068424800000003</v>
+      </c>
+      <c r="Q22">
         <f>_xlfn.XLOOKUP($B22,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.24</v>
       </c>
-      <c r="R22" s="6">
+      <c r="R22">
         <f>_xlfn.XLOOKUP($B22,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S22" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T22" s="6">
-        <f>_xlfn.XLOOKUP(A22,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U22" s="6">
-        <f>_xlfn.XLOOKUP(A22,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V22" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W22" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X22" s="6"/>
-      <c r="Y22" s="6"/>
-      <c r="Z22" s="6"/>
+      <c r="S22">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T22">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W22">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A23" s="6" t="s">
+      <c r="A23" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" t="s">
         <v>1</v>
       </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6">
+      <c r="D23">
         <v>4356</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23">
         <f>_xlfn.XLOOKUP(B23, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.72</v>
       </c>
-      <c r="F23" s="6">
-        <f t="shared" si="7"/>
+      <c r="F23">
+        <f t="shared" si="19"/>
         <v>3136.3199999999997</v>
       </c>
-      <c r="G23" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H23" s="6">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="I23" s="6">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="6">
+      <c r="G23">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="K23">
         <f>_xlfn.XLOOKUP($B23,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0</v>
       </c>
-      <c r="L23" s="6">
+      <c r="L23">
         <f>_xlfn.XLOOKUP($B23, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M23" s="6">
+      <c r="M23">
         <f>_xlfn.XLOOKUP($B23, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N23" s="6">
+      <c r="N23">
         <f>_xlfn.XLOOKUP($B23, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O23" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P23" s="6">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="6">
+      <c r="O23">
+        <f t="shared" si="16"/>
+        <v>3.67</v>
+      </c>
+      <c r="P23">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Q23">
         <f>_xlfn.XLOOKUP($B23,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.05</v>
       </c>
-      <c r="R23" s="6">
+      <c r="R23">
         <f>_xlfn.XLOOKUP($B23,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S23" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T23" s="6">
-        <f>_xlfn.XLOOKUP(A23,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U23" s="6">
-        <f>_xlfn.XLOOKUP(A23,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V23" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W23" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X23" s="6"/>
-      <c r="Y23" s="6"/>
-      <c r="Z23" s="6"/>
+      <c r="S23">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T23">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W23">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A24" s="6" t="s">
+      <c r="A24" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6">
+      <c r="D24">
         <v>324</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24">
         <f>_xlfn.XLOOKUP(B24, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.39</v>
       </c>
-      <c r="F24" s="6">
-        <f t="shared" si="7"/>
+      <c r="F24">
+        <f t="shared" si="19"/>
         <v>126.36</v>
       </c>
-      <c r="G24" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H24" s="6">
+      <c r="G24">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H24">
         <f>G24*F24</f>
         <v>0</v>
       </c>
-      <c r="I24" s="6">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J24" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K24" s="6">
+      <c r="I24">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="K24">
         <f>_xlfn.XLOOKUP($B24,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L24" s="6">
+      <c r="L24">
         <f>_xlfn.XLOOKUP($B24, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.7</v>
       </c>
-      <c r="M24" s="6">
+      <c r="M24">
         <f>_xlfn.XLOOKUP($B24, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.1</v>
       </c>
-      <c r="N24" s="6">
+      <c r="N24">
         <f>_xlfn.XLOOKUP($B24, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O24" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P24" s="6">
-        <f t="shared" si="12"/>
-        <v>9.2108015999999999</v>
-      </c>
-      <c r="Q24" s="6">
+      <c r="O24">
+        <f t="shared" si="16"/>
+        <v>3.67</v>
+      </c>
+      <c r="P24">
+        <f t="shared" si="24"/>
+        <v>9.219175056000001</v>
+      </c>
+      <c r="Q24">
         <f>_xlfn.XLOOKUP($B24,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.24</v>
       </c>
-      <c r="R24" s="6">
+      <c r="R24">
         <f>_xlfn.XLOOKUP($B24,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S24" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T24" s="6">
-        <f>_xlfn.XLOOKUP(A24,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U24" s="6">
-        <f>_xlfn.XLOOKUP(A24,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V24" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W24" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X24" s="6"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
+      <c r="S24">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T24">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W24">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A25" s="6" t="s">
+      <c r="A25" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25">
         <v>565</v>
       </c>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6">
+      <c r="E25">
         <f>_xlfn.XLOOKUP(B25, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="F25" s="6">
-        <f t="shared" ref="F25:F26" si="16">IF(C25&lt;&gt;"", C25,D25*E25)</f>
+      <c r="F25">
+        <f t="shared" ref="F25:F26" si="28">IF(C25&lt;&gt;"", C25,D25*E25)</f>
         <v>565</v>
       </c>
-      <c r="G25" s="6">
-        <f t="shared" ref="G25:G26" si="17">_xlfn.XLOOKUP(A25,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="6">
-        <f t="shared" ref="H25:H26" si="18">G25*F25</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="6">
-        <f t="shared" ref="I25:I26" si="19">_xlfn.XLOOKUP(A25,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="J25" s="6">
-        <f t="shared" ref="J25:J26" si="20">F25*I25</f>
-        <v>0</v>
-      </c>
-      <c r="K25" s="6">
+      <c r="G25">
+        <f t="shared" ref="G25:G26" si="29">_xlfn.XLOOKUP(A25,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <f t="shared" ref="H25:H26" si="30">G25*F25</f>
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <f t="shared" ref="I25:I26" si="31">_xlfn.XLOOKUP(A25,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <f t="shared" ref="J25:J26" si="32">F25*I25</f>
+        <v>0</v>
+      </c>
+      <c r="K25">
         <f>_xlfn.XLOOKUP($B25,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.84</v>
       </c>
-      <c r="L25" s="6">
+      <c r="L25">
         <f>_xlfn.XLOOKUP($B25, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.67</v>
       </c>
-      <c r="M25" s="6">
+      <c r="M25">
         <f>_xlfn.XLOOKUP($B25, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.2</v>
       </c>
-      <c r="N25" s="6">
+      <c r="N25">
         <f>_xlfn.XLOOKUP($B25, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O25" s="6">
-        <f t="shared" ref="O25:O26" si="21">$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P25" s="6">
+      <c r="O25">
+        <f t="shared" ref="O25:O26" si="33">$AC$5</f>
+        <v>3.67</v>
+      </c>
+      <c r="P25">
         <f>IF(A25&lt;&gt;"Incineration", 0, F25*K25*L25*M25*N25*O25)</f>
-        <v>165.56262799999996</v>
-      </c>
-      <c r="Q25" s="6">
+        <v>165.71313947999997</v>
+      </c>
+      <c r="Q25">
         <f>_xlfn.XLOOKUP($B25,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.39</v>
       </c>
-      <c r="R25" s="6">
+      <c r="R25">
         <f>_xlfn.XLOOKUP($B25,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S25" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T25" s="6">
-        <f>_xlfn.XLOOKUP(A25,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U25" s="6">
-        <f>_xlfn.XLOOKUP(A25,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V25" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W25" s="6">
-        <f t="shared" ref="W25:W26" si="22">F25*Q25*R25*S25*T25*V25*(1-U25)</f>
-        <v>0</v>
-      </c>
-      <c r="X25" s="6"/>
-      <c r="Y25" s="6"/>
-      <c r="Z25" s="6"/>
+      <c r="S25">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T25">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W25">
+        <f t="shared" ref="W25:W26" si="34">F25*Q25*R25*S25*T25*V25*(1-U25)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="4">
-        <v>0</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4">
+      <c r="C26" s="3">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3">
         <f>_xlfn.XLOOKUP(B26, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.42</v>
       </c>
-      <c r="F26" s="4">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="4">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="4">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="4">
+      <c r="F26" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
         <f>_xlfn.XLOOKUP($B26,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.9</v>
       </c>
-      <c r="L26" s="4">
+      <c r="L26" s="3">
         <f>_xlfn.XLOOKUP($B26, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.03</v>
       </c>
-      <c r="M26" s="4">
+      <c r="M26" s="3">
         <f>_xlfn.XLOOKUP($B26, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>1</v>
       </c>
-      <c r="N26" s="4">
+      <c r="N26" s="3">
         <f>_xlfn.XLOOKUP($B26, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O26" s="4">
-        <f t="shared" si="21"/>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P26" s="4">
-        <f t="shared" ref="P25:P26" si="23">IF(A26&lt;&gt;"Incineration", 0, F26*K26*L26*M26*N26*O26)</f>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="4">
+      <c r="O26" s="3">
+        <f t="shared" si="33"/>
+        <v>3.67</v>
+      </c>
+      <c r="P26" s="3">
+        <f t="shared" ref="P26" si="35">IF(A26&lt;&gt;"Incineration", 0, F26*K26*L26*M26*N26*O26)</f>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
         <f>_xlfn.XLOOKUP($B26,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0</v>
       </c>
-      <c r="R26" s="4">
+      <c r="R26" s="3">
         <f>_xlfn.XLOOKUP($B26,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0</v>
       </c>
-      <c r="S26" s="4">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T26" s="4">
-        <f>_xlfn.XLOOKUP(A26,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U26" s="4">
-        <f>_xlfn.XLOOKUP(A26,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V26" s="4">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W26" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="X26" s="4"/>
-      <c r="Y26" s="4"/>
-      <c r="Z26" s="4"/>
+      <c r="S26" s="3">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T26" s="3">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="3">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W26" s="3">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="X26" s="3"/>
+      <c r="Y26" s="3"/>
+      <c r="Z26" s="3"/>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27">
         <v>1234</v>
       </c>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6">
+      <c r="E27">
         <f>_xlfn.XLOOKUP(B27, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.5</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27">
         <f>IF(C27&lt;&gt;"", C27,D27*E27)</f>
         <v>1234</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G27">
         <f>_xlfn.XLOOKUP(A27,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
         <v>0</v>
       </c>
-      <c r="H27" s="6">
+      <c r="H27">
         <f>G27*F27</f>
         <v>0</v>
       </c>
-      <c r="I27" s="6">
+      <c r="I27">
         <f>_xlfn.XLOOKUP(A27,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
         <v>0</v>
       </c>
-      <c r="J27" s="6">
+      <c r="J27">
         <f>F27*I27</f>
         <v>0</v>
       </c>
-      <c r="K27" s="6">
+      <c r="K27">
         <f>_xlfn.XLOOKUP($B27,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L27" s="6">
+      <c r="L27">
         <f>_xlfn.XLOOKUP($B27, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.38</v>
       </c>
-      <c r="M27" s="6">
+      <c r="M27">
         <f>_xlfn.XLOOKUP($B27, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N27" s="6">
+      <c r="N27">
         <f>_xlfn.XLOOKUP($B27, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O27" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P27" s="6">
+      <c r="O27">
+        <f t="shared" ref="O27:O34" si="36">$AC$5</f>
+        <v>3.67</v>
+      </c>
+      <c r="P27">
         <f>IF(A27&lt;&gt;"Incineration", 0, F27*K27*L27*M27*N27*O27)</f>
         <v>0</v>
       </c>
-      <c r="Q27" s="6">
+      <c r="Q27">
         <f>_xlfn.XLOOKUP($B27,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.15</v>
       </c>
-      <c r="R27" s="6">
+      <c r="R27">
         <f>_xlfn.XLOOKUP($B27,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.84</v>
       </c>
-      <c r="S27" s="6">
+      <c r="S27">
         <f>$AC$7</f>
         <v>0.5</v>
       </c>
-      <c r="T27" s="6">
-        <f>_xlfn.XLOOKUP(A27,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="T27">
+        <f t="shared" si="17"/>
         <v>0.8</v>
       </c>
-      <c r="U27" s="6">
-        <f>_xlfn.XLOOKUP(A27,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V27" s="6">
+      <c r="U27">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V27">
         <f>$AC$6</f>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W27" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="W27">
         <f>F27*Q27*R27*S27*T27*V27*(1-U27)</f>
-        <v>82.924799999999991</v>
-      </c>
-      <c r="X27" s="6">
+        <v>82.717488000000003</v>
+      </c>
+      <c r="X27">
         <f>SUM(P27:P36)</f>
         <v>0</v>
       </c>
-      <c r="Y27" s="6">
+      <c r="Y27">
         <f>SUM(H27:H36,W27:W36)</f>
-        <v>231.21257333333332</v>
-      </c>
-      <c r="Z27" s="6">
+        <v>230.63454189999999</v>
+      </c>
+      <c r="Z27">
         <f>SUM(J27:J36)</f>
         <v>0</v>
       </c>
@@ -2693,2658 +2683,2560 @@
       <c r="A28" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28">
         <v>342</v>
       </c>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6">
+      <c r="E28">
         <f>_xlfn.XLOOKUP(B28, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.09</v>
       </c>
-      <c r="F28" s="6">
-        <f t="shared" ref="F28:F36" si="24">IF(C28&lt;&gt;"", C28,D28*E28)</f>
+      <c r="F28">
+        <f t="shared" ref="F28:F36" si="37">IF(C28&lt;&gt;"", C28,D28*E28)</f>
         <v>342</v>
       </c>
-      <c r="G28" s="6">
-        <f t="shared" ref="G28:G36" si="25">_xlfn.XLOOKUP(A28,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="H28" s="6">
-        <f t="shared" ref="H28:H33" si="26">G28*F28</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="6">
-        <f t="shared" ref="I28:I36" si="27">_xlfn.XLOOKUP(A28,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="J28" s="6">
-        <f t="shared" ref="J28:J36" si="28">F28*I28</f>
-        <v>0</v>
-      </c>
-      <c r="K28" s="6">
+      <c r="G28">
+        <f t="shared" ref="G28:G36" si="38">_xlfn.XLOOKUP(A28,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <f t="shared" ref="H28:H33" si="39">G28*F28</f>
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <f t="shared" ref="I28:I36" si="40">_xlfn.XLOOKUP(A28,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <f t="shared" ref="J28:J36" si="41">F28*I28</f>
+        <v>0</v>
+      </c>
+      <c r="K28">
         <f>_xlfn.XLOOKUP($B28,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.9</v>
       </c>
-      <c r="L28" s="6">
+      <c r="L28">
         <f>_xlfn.XLOOKUP($B28, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.46</v>
       </c>
-      <c r="M28" s="6">
+      <c r="M28">
         <f>_xlfn.XLOOKUP($B28, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.01</v>
       </c>
-      <c r="N28" s="6">
+      <c r="N28">
         <f>_xlfn.XLOOKUP($B28, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O28" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P28" s="6">
-        <f t="shared" ref="P28:P36" si="29">IF(A28&lt;&gt;"Incineration", 0, F28*K28*L28*M28*N28*O28)</f>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="6">
+      <c r="O28">
+        <f t="shared" si="36"/>
+        <v>3.67</v>
+      </c>
+      <c r="P28">
+        <f t="shared" ref="P28:P36" si="42">IF(A28&lt;&gt;"Incineration", 0, F28*K28*L28*M28*N28*O28)</f>
+        <v>0</v>
+      </c>
+      <c r="Q28">
         <f>_xlfn.XLOOKUP($B28,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.4</v>
       </c>
-      <c r="R28" s="6">
+      <c r="R28">
         <f>_xlfn.XLOOKUP($B28,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.49</v>
       </c>
-      <c r="S28" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T28" s="6">
-        <f>_xlfn.XLOOKUP(A28,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S28">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T28">
+        <f t="shared" si="17"/>
         <v>0.4</v>
       </c>
-      <c r="U28" s="6">
-        <f>_xlfn.XLOOKUP(A28,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V28" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W28" s="6">
-        <f t="shared" ref="W28:W36" si="30">F28*Q28*R28*S28*T28*V28*(1-U28)</f>
-        <v>17.875200000000003</v>
-      </c>
-      <c r="X28" s="6"/>
-      <c r="Y28" s="6"/>
-      <c r="Z28" s="6"/>
+      <c r="U28">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W28">
+        <f t="shared" ref="W28:W36" si="43">F28*Q28*R28*S28*T28*V28*(1-U28)</f>
+        <v>17.830512000000006</v>
+      </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" t="s">
         <v>4</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29">
         <v>346</v>
       </c>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6">
+      <c r="E29">
         <f>_xlfn.XLOOKUP(B29, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.24</v>
       </c>
-      <c r="F29" s="6">
-        <f t="shared" si="24"/>
+      <c r="F29">
+        <f t="shared" si="37"/>
         <v>346</v>
       </c>
-      <c r="G29" s="6">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="H29" s="6">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="I29" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="J29" s="6">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="K29" s="6">
+      <c r="G29">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="K29">
         <f>_xlfn.XLOOKUP($B29,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L29" s="6">
+      <c r="L29">
         <f>_xlfn.XLOOKUP($B29, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.49</v>
       </c>
-      <c r="M29" s="6">
+      <c r="M29">
         <f>_xlfn.XLOOKUP($B29, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N29" s="6">
+      <c r="N29">
         <f>_xlfn.XLOOKUP($B29, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O29" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P29" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="6">
+      <c r="O29">
+        <f t="shared" si="36"/>
+        <v>3.67</v>
+      </c>
+      <c r="P29">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="Q29">
         <f>_xlfn.XLOOKUP($B29,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.2</v>
       </c>
-      <c r="R29" s="6">
+      <c r="R29">
         <f>_xlfn.XLOOKUP($B29,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.47</v>
       </c>
-      <c r="S29" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T29" s="6">
-        <f>_xlfn.XLOOKUP(A29,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S29">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T29">
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
-      <c r="U29" s="6">
-        <f>_xlfn.XLOOKUP(A29,$X$9:$X$11,AA$9:AA$11, 0)</f>
+      <c r="U29">
+        <f t="shared" si="18"/>
         <v>0.1</v>
       </c>
-      <c r="V29" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W29" s="6">
-        <f t="shared" si="30"/>
-        <v>13.660080000000001</v>
-      </c>
-      <c r="X29" s="6"/>
-      <c r="Y29" s="6"/>
-      <c r="Z29" s="6"/>
+      <c r="V29">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W29">
+        <f t="shared" si="43"/>
+        <v>13.6259298</v>
+      </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" t="s">
         <v>45</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30">
         <v>1435</v>
       </c>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6">
+      <c r="E30">
         <f>_xlfn.XLOOKUP(B30, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.15</v>
       </c>
-      <c r="F30" s="6">
-        <f t="shared" si="24"/>
+      <c r="F30">
+        <f t="shared" si="37"/>
         <v>1435</v>
       </c>
-      <c r="G30" s="6">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="H30" s="6">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="I30" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="J30" s="6">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="K30" s="6">
+      <c r="G30">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="K30">
         <f>_xlfn.XLOOKUP($B30,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L30" s="6">
+      <c r="L30">
         <f>_xlfn.XLOOKUP($B30, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M30" s="6">
+      <c r="M30">
         <f>_xlfn.XLOOKUP($B30, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N30" s="6">
+      <c r="N30">
         <f>_xlfn.XLOOKUP($B30, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O30" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P30" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="Q30" s="6">
+      <c r="O30">
+        <f t="shared" si="36"/>
+        <v>3.67</v>
+      </c>
+      <c r="P30">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="Q30">
         <f>_xlfn.XLOOKUP($B30,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.43</v>
       </c>
-      <c r="R30" s="6">
+      <c r="R30">
         <f>_xlfn.XLOOKUP($B30,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.1</v>
       </c>
-      <c r="S30" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T30" s="6">
-        <f>_xlfn.XLOOKUP(A30,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S30">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T30">
+        <f t="shared" si="17"/>
         <v>0.8</v>
       </c>
-      <c r="U30" s="6">
-        <f>_xlfn.XLOOKUP(A30,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V30" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W30" s="6">
-        <f t="shared" si="30"/>
-        <v>32.909333333333336</v>
-      </c>
-      <c r="X30" s="6"/>
-      <c r="Y30" s="6"/>
-      <c r="Z30" s="6"/>
+      <c r="U30">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W30">
+        <f t="shared" si="43"/>
+        <v>32.827060000000003</v>
+      </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" t="s">
         <v>46</v>
       </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6">
+      <c r="D31">
         <v>1235</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31">
         <f>_xlfn.XLOOKUP(B31, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.15</v>
       </c>
-      <c r="F31" s="6">
-        <f t="shared" si="24"/>
+      <c r="F31">
+        <f t="shared" si="37"/>
         <v>185.25</v>
       </c>
-      <c r="G31" s="6">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="H31" s="6">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="I31" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="J31" s="6">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="K31" s="6">
+      <c r="G31">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="K31">
         <f>_xlfn.XLOOKUP($B31,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.9</v>
       </c>
-      <c r="L31" s="6">
+      <c r="L31">
         <f>_xlfn.XLOOKUP($B31, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M31" s="6">
+      <c r="M31">
         <f>_xlfn.XLOOKUP($B31, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N31" s="6">
+      <c r="N31">
         <f>_xlfn.XLOOKUP($B31, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O31" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P31" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="6">
+      <c r="O31">
+        <f t="shared" si="36"/>
+        <v>3.67</v>
+      </c>
+      <c r="P31">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="Q31">
         <f>_xlfn.XLOOKUP($B31,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.43</v>
       </c>
-      <c r="R31" s="6">
+      <c r="R31">
         <f>_xlfn.XLOOKUP($B31,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.1</v>
       </c>
-      <c r="S31" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T31" s="6">
-        <f>_xlfn.XLOOKUP(A31,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S31">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T31">
+        <f t="shared" si="17"/>
         <v>0.4</v>
       </c>
-      <c r="U31" s="6">
-        <f>_xlfn.XLOOKUP(A31,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V31" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W31" s="6">
-        <f t="shared" si="30"/>
-        <v>2.1242000000000001</v>
-      </c>
-      <c r="X31" s="6"/>
-      <c r="Y31" s="6"/>
-      <c r="Z31" s="6"/>
+      <c r="U31">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W31">
+        <f t="shared" si="43"/>
+        <v>2.1188895000000003</v>
+      </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6">
+      <c r="D32">
         <v>345</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E32">
         <f>_xlfn.XLOOKUP(B32, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="F32" s="6">
-        <f t="shared" si="24"/>
+      <c r="F32">
+        <f t="shared" si="37"/>
         <v>48.300000000000004</v>
       </c>
-      <c r="G32" s="6">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="H32" s="6">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="I32" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="J32" s="6">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="K32" s="6">
+      <c r="G32">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="K32">
         <f>_xlfn.XLOOKUP($B32,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.8</v>
       </c>
-      <c r="L32" s="6">
+      <c r="L32">
         <f>_xlfn.XLOOKUP($B32, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M32" s="6">
+      <c r="M32">
         <f>_xlfn.XLOOKUP($B32, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.2</v>
       </c>
-      <c r="N32" s="6">
+      <c r="N32">
         <f>_xlfn.XLOOKUP($B32, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O32" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P32" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="Q32" s="6">
+      <c r="O32">
+        <f t="shared" si="36"/>
+        <v>3.67</v>
+      </c>
+      <c r="P32">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="Q32">
         <f>_xlfn.XLOOKUP($B32,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.24</v>
       </c>
-      <c r="R32" s="6">
+      <c r="R32">
         <f>_xlfn.XLOOKUP($B32,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S32" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T32" s="6">
-        <f>_xlfn.XLOOKUP(A32,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S32">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T32">
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
-      <c r="U32" s="6">
-        <f>_xlfn.XLOOKUP(A32,$X$9:$X$11,AA$9:AA$11, 0)</f>
+      <c r="U32">
+        <f t="shared" si="18"/>
         <v>0.1</v>
       </c>
-      <c r="V32" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W32" s="6">
-        <f t="shared" si="30"/>
-        <v>2.4343199999999996</v>
-      </c>
-      <c r="X32" s="6"/>
-      <c r="Y32" s="6"/>
-      <c r="Z32" s="6"/>
+      <c r="V32">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W32">
+        <f t="shared" si="43"/>
+        <v>2.4282341999999999</v>
+      </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" t="s">
         <v>1</v>
       </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6">
+      <c r="D33">
         <v>4356</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E33">
         <f>_xlfn.XLOOKUP(B33, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.72</v>
       </c>
-      <c r="F33" s="6">
-        <f t="shared" si="24"/>
+      <c r="F33">
+        <f t="shared" si="37"/>
         <v>3136.3199999999997</v>
       </c>
-      <c r="G33" s="6">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="H33" s="6">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="I33" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="J33" s="6">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="K33" s="6">
+      <c r="G33">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="K33">
         <f>_xlfn.XLOOKUP($B33,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0</v>
       </c>
-      <c r="L33" s="6">
+      <c r="L33">
         <f>_xlfn.XLOOKUP($B33, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M33" s="6">
+      <c r="M33">
         <f>_xlfn.XLOOKUP($B33, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N33" s="6">
+      <c r="N33">
         <f>_xlfn.XLOOKUP($B33, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O33" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P33" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="Q33" s="6">
+      <c r="O33">
+        <f t="shared" si="36"/>
+        <v>3.67</v>
+      </c>
+      <c r="P33">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="Q33">
         <f>_xlfn.XLOOKUP($B33,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.05</v>
       </c>
-      <c r="R33" s="6">
+      <c r="R33">
         <f>_xlfn.XLOOKUP($B33,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S33" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T33" s="6">
-        <f>_xlfn.XLOOKUP(A33,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S33">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T33">
+        <f t="shared" si="17"/>
         <v>0.8</v>
       </c>
-      <c r="U33" s="6">
-        <f>_xlfn.XLOOKUP(A33,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V33" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W33" s="6">
-        <f t="shared" si="30"/>
-        <v>41.817599999999999</v>
-      </c>
-      <c r="X33" s="6"/>
-      <c r="Y33" s="6"/>
-      <c r="Z33" s="6"/>
+      <c r="U33">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W33">
+        <f t="shared" si="43"/>
+        <v>41.713056000000009</v>
+      </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" t="s">
         <v>54</v>
       </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6">
+      <c r="D34">
         <v>324</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E34">
         <f>_xlfn.XLOOKUP(B34, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.39</v>
       </c>
-      <c r="F34" s="6">
-        <f t="shared" si="24"/>
+      <c r="F34">
+        <f t="shared" si="37"/>
         <v>126.36</v>
       </c>
-      <c r="G34" s="6">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="H34" s="6">
+      <c r="G34">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="H34">
         <f>G34*F34</f>
         <v>0</v>
       </c>
-      <c r="I34" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="J34" s="6">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="K34" s="6">
+      <c r="I34">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="K34">
         <f>_xlfn.XLOOKUP($B34,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L34" s="6">
+      <c r="L34">
         <f>_xlfn.XLOOKUP($B34, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.7</v>
       </c>
-      <c r="M34" s="6">
+      <c r="M34">
         <f>_xlfn.XLOOKUP($B34, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.1</v>
       </c>
-      <c r="N34" s="6">
+      <c r="N34">
         <f>_xlfn.XLOOKUP($B34, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O34" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P34" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="Q34" s="6">
+      <c r="O34">
+        <f t="shared" si="36"/>
+        <v>3.67</v>
+      </c>
+      <c r="P34">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="Q34">
         <f>_xlfn.XLOOKUP($B34,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.24</v>
       </c>
-      <c r="R34" s="6">
+      <c r="R34">
         <f>_xlfn.XLOOKUP($B34,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S34" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T34" s="6">
-        <f>_xlfn.XLOOKUP(A34,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S34">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T34">
+        <f t="shared" si="17"/>
         <v>0.8</v>
       </c>
-      <c r="U34" s="6">
-        <f>_xlfn.XLOOKUP(A34,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V34" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W34" s="6">
-        <f t="shared" si="30"/>
-        <v>8.08704</v>
-      </c>
-      <c r="X34" s="6"/>
-      <c r="Y34" s="6"/>
-      <c r="Z34" s="6"/>
+      <c r="U34">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W34">
+        <f t="shared" si="43"/>
+        <v>8.0668224000000013</v>
+      </c>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" t="s">
         <v>8</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35">
         <v>565</v>
       </c>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6">
+      <c r="E35">
         <f>_xlfn.XLOOKUP(B35, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="F35" s="6">
-        <f t="shared" si="24"/>
+      <c r="F35">
+        <f t="shared" si="37"/>
         <v>565</v>
       </c>
-      <c r="G35" s="6">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="H35" s="6">
-        <f t="shared" ref="H35:H36" si="31">G35*F35</f>
-        <v>0</v>
-      </c>
-      <c r="I35" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="J35" s="6">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="K35" s="6">
+      <c r="G35">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <f t="shared" ref="H35:H36" si="44">G35*F35</f>
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="K35">
         <f>_xlfn.XLOOKUP($B35,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.84</v>
       </c>
-      <c r="L35" s="6">
+      <c r="L35">
         <f>_xlfn.XLOOKUP($B35, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.67</v>
       </c>
-      <c r="M35" s="6">
+      <c r="M35">
         <f>_xlfn.XLOOKUP($B35, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.2</v>
       </c>
-      <c r="N35" s="6">
+      <c r="N35">
         <f>_xlfn.XLOOKUP($B35, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O35" s="6">
-        <f t="shared" ref="O35:O36" si="32">$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P35" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="Q35" s="6">
+      <c r="O35">
+        <f t="shared" ref="O35:O36" si="45">$AC$5</f>
+        <v>3.67</v>
+      </c>
+      <c r="P35">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="Q35">
         <f>_xlfn.XLOOKUP($B35,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.39</v>
       </c>
-      <c r="R35" s="6">
+      <c r="R35">
         <f>_xlfn.XLOOKUP($B35,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S35" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T35" s="6">
-        <f>_xlfn.XLOOKUP(A35,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S35">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T35">
+        <f t="shared" si="17"/>
         <v>0.4</v>
       </c>
-      <c r="U35" s="6">
-        <f>_xlfn.XLOOKUP(A35,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V35" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W35" s="6">
-        <f t="shared" si="30"/>
-        <v>29.38</v>
-      </c>
-      <c r="X35" s="6"/>
-      <c r="Y35" s="6"/>
-      <c r="Z35" s="6"/>
+      <c r="U35">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W35">
+        <f t="shared" si="43"/>
+        <v>29.306550000000001</v>
+      </c>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="3">
         <v>7643</v>
       </c>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4">
+      <c r="D36" s="3"/>
+      <c r="E36" s="3">
         <f>_xlfn.XLOOKUP(B36, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.42</v>
       </c>
-      <c r="F36" s="4">
-        <f t="shared" si="24"/>
+      <c r="F36" s="3">
+        <f t="shared" si="37"/>
         <v>7643</v>
       </c>
-      <c r="G36" s="4">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="H36" s="4">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="I36" s="4">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="J36" s="4">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="K36" s="4">
+      <c r="G36" s="3">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="3">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="3">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="3">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="3">
         <f>_xlfn.XLOOKUP($B36,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.9</v>
       </c>
-      <c r="L36" s="4">
+      <c r="L36" s="3">
         <f>_xlfn.XLOOKUP($B36, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.03</v>
       </c>
-      <c r="M36" s="4">
+      <c r="M36" s="3">
         <f>_xlfn.XLOOKUP($B36, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>1</v>
       </c>
-      <c r="N36" s="4">
+      <c r="N36" s="3">
         <f>_xlfn.XLOOKUP($B36, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O36" s="4">
-        <f t="shared" si="32"/>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P36" s="4">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="Q36" s="4">
+      <c r="O36" s="3">
+        <f t="shared" si="45"/>
+        <v>3.67</v>
+      </c>
+      <c r="P36" s="3">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="3">
         <f>_xlfn.XLOOKUP($B36,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0</v>
       </c>
-      <c r="R36" s="4">
+      <c r="R36" s="3">
         <f>_xlfn.XLOOKUP($B36,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0</v>
       </c>
-      <c r="S36" s="4">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T36" s="4">
-        <f>_xlfn.XLOOKUP(A36,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S36" s="3">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T36" s="3">
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
-      <c r="U36" s="4">
-        <f>_xlfn.XLOOKUP(A36,$X$9:$X$11,AA$9:AA$11, 0)</f>
+      <c r="U36" s="3">
+        <f t="shared" si="18"/>
         <v>0.1</v>
       </c>
-      <c r="V36" s="4">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W36" s="4">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="X36" s="4"/>
-      <c r="Y36" s="4"/>
-      <c r="Z36" s="4"/>
+      <c r="V36" s="3">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W36" s="3">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="3"/>
+      <c r="Y36" s="3"/>
+      <c r="Z36" s="3"/>
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A37" s="6" t="s">
+      <c r="A37" t="s">
         <v>5</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" t="s">
         <v>3</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37">
         <v>1234</v>
       </c>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6">
+      <c r="E37">
         <f>_xlfn.XLOOKUP(B37, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.5</v>
       </c>
-      <c r="F37" s="6">
+      <c r="F37">
         <f>IF(C37&lt;&gt;"", C37,D37*E37)</f>
         <v>1234</v>
       </c>
-      <c r="G37" s="6">
+      <c r="G37">
         <f>_xlfn.XLOOKUP(A37,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
         <v>7.5000000000000002E-4</v>
       </c>
-      <c r="H37" s="6">
+      <c r="H37">
         <f>G37*F37</f>
         <v>0.92549999999999999</v>
       </c>
-      <c r="I37" s="6">
+      <c r="I37">
         <f>_xlfn.XLOOKUP(A37,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
         <v>9.4300000000000002E-5</v>
       </c>
-      <c r="J37" s="6">
+      <c r="J37">
         <f>F37*I37</f>
         <v>0.1163662</v>
       </c>
-      <c r="K37" s="6">
+      <c r="K37">
         <f>_xlfn.XLOOKUP($B37,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L37" s="6">
+      <c r="L37">
         <f>_xlfn.XLOOKUP($B37, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.38</v>
       </c>
-      <c r="M37" s="6">
+      <c r="M37">
         <f>_xlfn.XLOOKUP($B37, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N37" s="6">
+      <c r="N37">
         <f>_xlfn.XLOOKUP($B37, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O37" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P37" s="6">
+      <c r="O37">
+        <f t="shared" ref="O37:O44" si="46">$AC$5</f>
+        <v>3.67</v>
+      </c>
+      <c r="P37">
         <f>IF(A37&lt;&gt;"Incineration", 0, F37*K37*L37*M37*N37*O37)</f>
         <v>0</v>
       </c>
-      <c r="Q37" s="6">
+      <c r="Q37">
         <f>_xlfn.XLOOKUP($B37,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.15</v>
       </c>
-      <c r="R37" s="6">
+      <c r="R37">
         <f>_xlfn.XLOOKUP($B37,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.84</v>
       </c>
-      <c r="S37" s="6">
+      <c r="S37">
         <f>$AC$7</f>
         <v>0.5</v>
       </c>
-      <c r="T37" s="6">
-        <f>_xlfn.XLOOKUP(A37,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U37" s="6">
-        <f>_xlfn.XLOOKUP(A37,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V37" s="6">
+      <c r="T37">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V37">
         <f>$AC$6</f>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W37" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="W37">
         <f>F37*Q37*R37*S37*T37*V37*(1-U37)</f>
         <v>0</v>
       </c>
-      <c r="X37" s="6">
+      <c r="X37">
         <f>SUM(P37:P46)</f>
-        <v>547.28574999999978</v>
-      </c>
-      <c r="Y37" s="6">
+        <v>547.78328249999993</v>
+      </c>
+      <c r="Y37">
         <f>SUM(H37:H46,W37:W46)</f>
-        <v>108.46994266666667</v>
-      </c>
-      <c r="Z37" s="6">
+        <v>108.20251439</v>
+      </c>
+      <c r="Z37">
         <f>SUM(J37:J46)</f>
         <v>0.14899400000000002</v>
       </c>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A38" s="6" t="s">
+      <c r="A38" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38">
         <v>342</v>
       </c>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6">
+      <c r="E38">
         <f>_xlfn.XLOOKUP(B38, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.09</v>
       </c>
-      <c r="F38" s="6">
-        <f t="shared" ref="F38:F46" si="33">IF(C38&lt;&gt;"", C38,D38*E38)</f>
+      <c r="F38">
+        <f t="shared" ref="F38:F46" si="47">IF(C38&lt;&gt;"", C38,D38*E38)</f>
         <v>342</v>
       </c>
-      <c r="G38" s="6">
-        <f t="shared" ref="G38:G46" si="34">_xlfn.XLOOKUP(A38,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="H38" s="6">
-        <f t="shared" ref="H38:H43" si="35">G38*F38</f>
-        <v>0</v>
-      </c>
-      <c r="I38" s="6">
-        <f t="shared" ref="I38:I46" si="36">_xlfn.XLOOKUP(A38,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="J38" s="6">
-        <f t="shared" ref="J38:J46" si="37">F38*I38</f>
-        <v>0</v>
-      </c>
-      <c r="K38" s="6">
+      <c r="G38">
+        <f t="shared" ref="G38:G46" si="48">_xlfn.XLOOKUP(A38,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <f t="shared" ref="H38:H43" si="49">G38*F38</f>
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <f t="shared" ref="I38:I46" si="50">_xlfn.XLOOKUP(A38,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <f t="shared" ref="J38:J46" si="51">F38*I38</f>
+        <v>0</v>
+      </c>
+      <c r="K38">
         <f>_xlfn.XLOOKUP($B38,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.9</v>
       </c>
-      <c r="L38" s="6">
+      <c r="L38">
         <f>_xlfn.XLOOKUP($B38, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.46</v>
       </c>
-      <c r="M38" s="6">
+      <c r="M38">
         <f>_xlfn.XLOOKUP($B38, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.01</v>
       </c>
-      <c r="N38" s="6">
+      <c r="N38">
         <f>_xlfn.XLOOKUP($B38, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O38" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P38" s="6">
-        <f t="shared" ref="P38:P46" si="38">IF(A38&lt;&gt;"Incineration", 0, F38*K38*L38*M38*N38*O38)</f>
-        <v>0</v>
-      </c>
-      <c r="Q38" s="6">
+      <c r="O38">
+        <f t="shared" si="46"/>
+        <v>3.67</v>
+      </c>
+      <c r="P38">
+        <f t="shared" ref="P38:P46" si="52">IF(A38&lt;&gt;"Incineration", 0, F38*K38*L38*M38*N38*O38)</f>
+        <v>0</v>
+      </c>
+      <c r="Q38">
         <f>_xlfn.XLOOKUP($B38,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.4</v>
       </c>
-      <c r="R38" s="6">
+      <c r="R38">
         <f>_xlfn.XLOOKUP($B38,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.49</v>
       </c>
-      <c r="S38" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T38" s="6">
-        <f>_xlfn.XLOOKUP(A38,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S38">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T38">
+        <f t="shared" si="17"/>
         <v>0.8</v>
       </c>
-      <c r="U38" s="6">
-        <f>_xlfn.XLOOKUP(A38,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V38" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W38" s="6">
-        <f t="shared" ref="W38:W46" si="39">F38*Q38*R38*S38*T38*V38*(1-U38)</f>
-        <v>35.750400000000006</v>
-      </c>
-      <c r="X38" s="6"/>
-      <c r="Y38" s="6"/>
-      <c r="Z38" s="6"/>
+      <c r="U38">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W38">
+        <f t="shared" ref="W38:W46" si="53">F38*Q38*R38*S38*T38*V38*(1-U38)</f>
+        <v>35.661024000000012</v>
+      </c>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A39" s="6" t="s">
+      <c r="A39" t="s">
         <v>5</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" t="s">
         <v>4</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39">
         <v>346</v>
       </c>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6">
+      <c r="E39">
         <f>_xlfn.XLOOKUP(B39, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.24</v>
       </c>
-      <c r="F39" s="6">
-        <f t="shared" si="33"/>
+      <c r="F39">
+        <f t="shared" si="47"/>
         <v>346</v>
       </c>
-      <c r="G39" s="6">
-        <f t="shared" si="34"/>
+      <c r="G39">
+        <f t="shared" si="48"/>
         <v>7.5000000000000002E-4</v>
       </c>
-      <c r="H39" s="6">
-        <f t="shared" si="35"/>
+      <c r="H39">
+        <f t="shared" si="49"/>
         <v>0.25950000000000001</v>
       </c>
-      <c r="I39" s="6">
-        <f t="shared" si="36"/>
+      <c r="I39">
+        <f t="shared" si="50"/>
         <v>9.4300000000000002E-5</v>
       </c>
-      <c r="J39" s="6">
-        <f t="shared" si="37"/>
+      <c r="J39">
+        <f t="shared" si="51"/>
         <v>3.2627799999999998E-2</v>
       </c>
-      <c r="K39" s="6">
+      <c r="K39">
         <f>_xlfn.XLOOKUP($B39,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L39" s="6">
+      <c r="L39">
         <f>_xlfn.XLOOKUP($B39, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.49</v>
       </c>
-      <c r="M39" s="6">
+      <c r="M39">
         <f>_xlfn.XLOOKUP($B39, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N39" s="6">
+      <c r="N39">
         <f>_xlfn.XLOOKUP($B39, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O39" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P39" s="6">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="Q39" s="6">
+      <c r="O39">
+        <f t="shared" si="46"/>
+        <v>3.67</v>
+      </c>
+      <c r="P39">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="Q39">
         <f>_xlfn.XLOOKUP($B39,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.2</v>
       </c>
-      <c r="R39" s="6">
+      <c r="R39">
         <f>_xlfn.XLOOKUP($B39,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.47</v>
       </c>
-      <c r="S39" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T39" s="6">
-        <f>_xlfn.XLOOKUP(A39,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U39" s="6">
-        <f>_xlfn.XLOOKUP(A39,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V39" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W39" s="6">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="X39" s="6"/>
-      <c r="Y39" s="6"/>
-      <c r="Z39" s="6"/>
+      <c r="S39">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T39">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W39">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A40" s="6" t="s">
+      <c r="A40" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40">
         <v>1435</v>
       </c>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6">
+      <c r="E40">
         <f>_xlfn.XLOOKUP(B40, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.15</v>
       </c>
-      <c r="F40" s="6">
-        <f t="shared" si="33"/>
+      <c r="F40">
+        <f t="shared" si="47"/>
         <v>1435</v>
       </c>
-      <c r="G40" s="6">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="H40" s="6">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="I40" s="6">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="J40" s="6">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="K40" s="6">
+      <c r="G40">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K40">
         <f>_xlfn.XLOOKUP($B40,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L40" s="6">
+      <c r="L40">
         <f>_xlfn.XLOOKUP($B40, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M40" s="6">
+      <c r="M40">
         <f>_xlfn.XLOOKUP($B40, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N40" s="6">
+      <c r="N40">
         <f>_xlfn.XLOOKUP($B40, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O40" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P40" s="6">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="Q40" s="6">
+      <c r="O40">
+        <f t="shared" si="46"/>
+        <v>3.67</v>
+      </c>
+      <c r="P40">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="Q40">
         <f>_xlfn.XLOOKUP($B40,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.43</v>
       </c>
-      <c r="R40" s="6">
+      <c r="R40">
         <f>_xlfn.XLOOKUP($B40,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.1</v>
       </c>
-      <c r="S40" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T40" s="6">
-        <f>_xlfn.XLOOKUP(A40,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S40">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T40">
+        <f t="shared" si="17"/>
         <v>0.4</v>
       </c>
-      <c r="U40" s="6">
-        <f>_xlfn.XLOOKUP(A40,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V40" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W40" s="6">
-        <f t="shared" si="39"/>
-        <v>16.454666666666668</v>
-      </c>
-      <c r="X40" s="6"/>
-      <c r="Y40" s="6"/>
-      <c r="Z40" s="6"/>
+      <c r="U40">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W40">
+        <f t="shared" si="53"/>
+        <v>16.413530000000002</v>
+      </c>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A41" s="6" t="s">
+      <c r="A41" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" t="s">
         <v>46</v>
       </c>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6">
+      <c r="D41">
         <v>1235</v>
       </c>
-      <c r="E41" s="6">
+      <c r="E41">
         <f>_xlfn.XLOOKUP(B41, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.15</v>
       </c>
-      <c r="F41" s="6">
-        <f t="shared" si="33"/>
+      <c r="F41">
+        <f t="shared" si="47"/>
         <v>185.25</v>
       </c>
-      <c r="G41" s="6">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="H41" s="6">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="I41" s="6">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="J41" s="6">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="K41" s="6">
+      <c r="G41">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K41">
         <f>_xlfn.XLOOKUP($B41,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.9</v>
       </c>
-      <c r="L41" s="6">
+      <c r="L41">
         <f>_xlfn.XLOOKUP($B41, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M41" s="6">
+      <c r="M41">
         <f>_xlfn.XLOOKUP($B41, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N41" s="6">
+      <c r="N41">
         <f>_xlfn.XLOOKUP($B41, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O41" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P41" s="6">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="Q41" s="6">
+      <c r="O41">
+        <f t="shared" si="46"/>
+        <v>3.67</v>
+      </c>
+      <c r="P41">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="Q41">
         <f>_xlfn.XLOOKUP($B41,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.43</v>
       </c>
-      <c r="R41" s="6">
+      <c r="R41">
         <f>_xlfn.XLOOKUP($B41,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.1</v>
       </c>
-      <c r="S41" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T41" s="6">
-        <f>_xlfn.XLOOKUP(A41,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S41">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T41">
+        <f t="shared" si="17"/>
         <v>0.4</v>
       </c>
-      <c r="U41" s="6">
-        <f>_xlfn.XLOOKUP(A41,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V41" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W41" s="6">
-        <f t="shared" si="39"/>
-        <v>2.1242000000000001</v>
-      </c>
-      <c r="X41" s="6"/>
-      <c r="Y41" s="6"/>
-      <c r="Z41" s="6"/>
+      <c r="U41">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W41">
+        <f t="shared" si="53"/>
+        <v>2.1188895000000003</v>
+      </c>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A42" s="6" t="s">
+      <c r="A42" t="s">
         <v>2</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6">
+      <c r="D42">
         <v>345</v>
       </c>
-      <c r="E42" s="6">
+      <c r="E42">
         <f>_xlfn.XLOOKUP(B42, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="F42" s="6">
-        <f t="shared" si="33"/>
+      <c r="F42">
+        <f t="shared" si="47"/>
         <v>48.300000000000004</v>
       </c>
-      <c r="G42" s="6">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="H42" s="6">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="I42" s="6">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="J42" s="6">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="K42" s="6">
+      <c r="G42">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K42">
         <f>_xlfn.XLOOKUP($B42,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.8</v>
       </c>
-      <c r="L42" s="6">
+      <c r="L42">
         <f>_xlfn.XLOOKUP($B42, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M42" s="6">
+      <c r="M42">
         <f>_xlfn.XLOOKUP($B42, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.2</v>
       </c>
-      <c r="N42" s="6">
+      <c r="N42">
         <f>_xlfn.XLOOKUP($B42, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O42" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P42" s="6">
-        <f t="shared" si="38"/>
-        <v>10.059280000000001</v>
-      </c>
-      <c r="Q42" s="6">
+      <c r="O42">
+        <f t="shared" si="46"/>
+        <v>3.67</v>
+      </c>
+      <c r="P42">
+        <f t="shared" si="52"/>
+        <v>10.068424800000003</v>
+      </c>
+      <c r="Q42">
         <f>_xlfn.XLOOKUP($B42,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.24</v>
       </c>
-      <c r="R42" s="6">
+      <c r="R42">
         <f>_xlfn.XLOOKUP($B42,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S42" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T42" s="6">
-        <f>_xlfn.XLOOKUP(A42,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U42" s="6">
-        <f>_xlfn.XLOOKUP(A42,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V42" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W42" s="6">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="X42" s="6"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
+      <c r="S42">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T42">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W42">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A43" s="6" t="s">
+      <c r="A43" t="s">
         <v>9</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" t="s">
         <v>1</v>
       </c>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6">
+      <c r="D43">
         <v>4356</v>
       </c>
-      <c r="E43" s="6">
+      <c r="E43">
         <f>_xlfn.XLOOKUP(B43, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.72</v>
       </c>
-      <c r="F43" s="6">
-        <f t="shared" si="33"/>
+      <c r="F43">
+        <f t="shared" si="47"/>
         <v>3136.3199999999997</v>
       </c>
-      <c r="G43" s="6">
-        <f t="shared" si="34"/>
+      <c r="G43">
+        <f t="shared" si="48"/>
         <v>1E-4</v>
       </c>
-      <c r="H43" s="6">
-        <f t="shared" si="35"/>
+      <c r="H43">
+        <f t="shared" si="49"/>
         <v>0.31363199999999997</v>
       </c>
-      <c r="I43" s="6">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="J43" s="6">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="K43" s="6">
+      <c r="I43">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K43">
         <f>_xlfn.XLOOKUP($B43,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0</v>
       </c>
-      <c r="L43" s="6">
+      <c r="L43">
         <f>_xlfn.XLOOKUP($B43, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M43" s="6">
+      <c r="M43">
         <f>_xlfn.XLOOKUP($B43, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N43" s="6">
+      <c r="N43">
         <f>_xlfn.XLOOKUP($B43, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O43" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P43" s="6">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="Q43" s="6">
+      <c r="O43">
+        <f t="shared" si="46"/>
+        <v>3.67</v>
+      </c>
+      <c r="P43">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="Q43">
         <f>_xlfn.XLOOKUP($B43,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.05</v>
       </c>
-      <c r="R43" s="6">
+      <c r="R43">
         <f>_xlfn.XLOOKUP($B43,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S43" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T43" s="6">
-        <f>_xlfn.XLOOKUP(A43,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U43" s="6">
-        <f>_xlfn.XLOOKUP(A43,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V43" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W43" s="6">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="X43" s="6"/>
-      <c r="Y43" s="6"/>
-      <c r="Z43" s="6"/>
+      <c r="S43">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T43">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W43">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A44" s="6" t="s">
+      <c r="A44" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" t="s">
         <v>54</v>
       </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6">
+      <c r="D44">
         <v>324</v>
       </c>
-      <c r="E44" s="6">
+      <c r="E44">
         <f>_xlfn.XLOOKUP(B44, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.39</v>
       </c>
-      <c r="F44" s="6">
-        <f t="shared" si="33"/>
+      <c r="F44">
+        <f t="shared" si="47"/>
         <v>126.36</v>
       </c>
-      <c r="G44" s="6">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="H44" s="6">
+      <c r="G44">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="H44">
         <f>G44*F44</f>
         <v>0</v>
       </c>
-      <c r="I44" s="6">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="J44" s="6">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="K44" s="6">
+      <c r="I44">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K44">
         <f>_xlfn.XLOOKUP($B44,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L44" s="6">
+      <c r="L44">
         <f>_xlfn.XLOOKUP($B44, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.7</v>
       </c>
-      <c r="M44" s="6">
+      <c r="M44">
         <f>_xlfn.XLOOKUP($B44, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.1</v>
       </c>
-      <c r="N44" s="6">
+      <c r="N44">
         <f>_xlfn.XLOOKUP($B44, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O44" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P44" s="6">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="Q44" s="6">
+      <c r="O44">
+        <f t="shared" si="46"/>
+        <v>3.67</v>
+      </c>
+      <c r="P44">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="Q44">
         <f>_xlfn.XLOOKUP($B44,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.24</v>
       </c>
-      <c r="R44" s="6">
+      <c r="R44">
         <f>_xlfn.XLOOKUP($B44,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S44" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T44" s="6">
-        <f>_xlfn.XLOOKUP(A44,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S44">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T44">
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
-      <c r="U44" s="6">
-        <f>_xlfn.XLOOKUP(A44,$X$9:$X$11,AA$9:AA$11, 0)</f>
+      <c r="U44">
+        <f t="shared" si="18"/>
         <v>0.1</v>
       </c>
-      <c r="V44" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W44" s="6">
-        <f t="shared" si="39"/>
-        <v>6.3685439999999991</v>
-      </c>
-      <c r="X44" s="6"/>
-      <c r="Y44" s="6"/>
-      <c r="Z44" s="6"/>
+      <c r="V44">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W44">
+        <f t="shared" si="53"/>
+        <v>6.3526226399999999</v>
+      </c>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A45" s="6" t="s">
+      <c r="A45" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" t="s">
         <v>8</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C45">
         <v>565</v>
       </c>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6">
+      <c r="E45">
         <f>_xlfn.XLOOKUP(B45, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="F45" s="6">
-        <f t="shared" si="33"/>
+      <c r="F45">
+        <f t="shared" si="47"/>
         <v>565</v>
       </c>
-      <c r="G45" s="6">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="H45" s="6">
-        <f t="shared" ref="H45:H46" si="40">G45*F45</f>
-        <v>0</v>
-      </c>
-      <c r="I45" s="6">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="J45" s="6">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="K45" s="6">
+      <c r="G45">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <f t="shared" ref="H45:H46" si="54">G45*F45</f>
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K45">
         <f>_xlfn.XLOOKUP($B45,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.84</v>
       </c>
-      <c r="L45" s="6">
+      <c r="L45">
         <f>_xlfn.XLOOKUP($B45, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.67</v>
       </c>
-      <c r="M45" s="6">
+      <c r="M45">
         <f>_xlfn.XLOOKUP($B45, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.2</v>
       </c>
-      <c r="N45" s="6">
+      <c r="N45">
         <f>_xlfn.XLOOKUP($B45, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O45" s="6">
-        <f t="shared" ref="O45:O46" si="41">$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P45" s="6">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="Q45" s="6">
+      <c r="O45">
+        <f t="shared" ref="O45:O46" si="55">$AC$5</f>
+        <v>3.67</v>
+      </c>
+      <c r="P45">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="Q45">
         <f>_xlfn.XLOOKUP($B45,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.39</v>
       </c>
-      <c r="R45" s="6">
+      <c r="R45">
         <f>_xlfn.XLOOKUP($B45,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S45" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T45" s="6">
-        <f>_xlfn.XLOOKUP(A45,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S45">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T45">
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
-      <c r="U45" s="6">
-        <f>_xlfn.XLOOKUP(A45,$X$9:$X$11,AA$9:AA$11, 0)</f>
+      <c r="U45">
+        <f t="shared" si="18"/>
         <v>0.1</v>
       </c>
-      <c r="V45" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W45" s="6">
-        <f t="shared" si="39"/>
-        <v>46.273499999999991</v>
-      </c>
-      <c r="X45" s="6"/>
-      <c r="Y45" s="6"/>
-      <c r="Z45" s="6"/>
+      <c r="V45">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W45">
+        <f t="shared" si="53"/>
+        <v>46.157816249999996</v>
+      </c>
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C46" s="4">
+      <c r="C46" s="3">
         <v>7643</v>
       </c>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4">
+      <c r="D46" s="3"/>
+      <c r="E46" s="3">
         <f>_xlfn.XLOOKUP(B46, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.42</v>
       </c>
-      <c r="F46" s="4">
-        <f t="shared" si="33"/>
+      <c r="F46" s="3">
+        <f t="shared" si="47"/>
         <v>7643</v>
       </c>
-      <c r="G46" s="4">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="H46" s="4">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="I46" s="4">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="J46" s="4">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="K46" s="4">
+      <c r="G46" s="3">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="3">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="I46" s="3">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="3">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="3">
         <f>_xlfn.XLOOKUP($B46,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.9</v>
       </c>
-      <c r="L46" s="4">
+      <c r="L46" s="3">
         <f>_xlfn.XLOOKUP($B46, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.03</v>
       </c>
-      <c r="M46" s="4">
+      <c r="M46" s="3">
         <f>_xlfn.XLOOKUP($B46, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>1</v>
       </c>
-      <c r="N46" s="4">
+      <c r="N46" s="3">
         <f>_xlfn.XLOOKUP($B46, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O46" s="4">
-        <f t="shared" si="41"/>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P46" s="4">
-        <f t="shared" si="38"/>
-        <v>537.22646999999984</v>
-      </c>
-      <c r="Q46" s="4">
+      <c r="O46" s="3">
+        <f t="shared" si="55"/>
+        <v>3.67</v>
+      </c>
+      <c r="P46" s="3">
+        <f t="shared" si="52"/>
+        <v>537.71485769999992</v>
+      </c>
+      <c r="Q46" s="3">
         <f>_xlfn.XLOOKUP($B46,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0</v>
       </c>
-      <c r="R46" s="4">
+      <c r="R46" s="3">
         <f>_xlfn.XLOOKUP($B46,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0</v>
       </c>
-      <c r="S46" s="4">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T46" s="4">
-        <f>_xlfn.XLOOKUP(A46,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U46" s="4">
-        <f>_xlfn.XLOOKUP(A46,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V46" s="4">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W46" s="4">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="X46" s="4"/>
-      <c r="Y46" s="4"/>
-      <c r="Z46" s="4"/>
+      <c r="S46" s="3">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T46" s="3">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V46" s="3">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W46" s="3">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="X46" s="3"/>
+      <c r="Y46" s="3"/>
+      <c r="Z46" s="3"/>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A47" s="6" t="s">
+      <c r="A47" t="s">
         <v>5</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" t="s">
         <v>3</v>
       </c>
-      <c r="C47" s="6">
+      <c r="C47">
         <v>1234</v>
       </c>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6">
+      <c r="E47">
         <f>_xlfn.XLOOKUP(B47, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.5</v>
       </c>
-      <c r="F47" s="6">
+      <c r="F47">
         <f>IF(C47&lt;&gt;"", C47,D47*E47)</f>
         <v>1234</v>
       </c>
-      <c r="G47" s="6">
+      <c r="G47">
         <f>_xlfn.XLOOKUP(A47,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
         <v>7.5000000000000002E-4</v>
       </c>
-      <c r="H47" s="6">
+      <c r="H47">
         <f>G47*F47</f>
         <v>0.92549999999999999</v>
       </c>
-      <c r="I47" s="6">
+      <c r="I47">
         <f>_xlfn.XLOOKUP(A47,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
         <v>9.4300000000000002E-5</v>
       </c>
-      <c r="J47" s="6">
+      <c r="J47">
         <f>F47*I47</f>
         <v>0.1163662</v>
       </c>
-      <c r="K47" s="6">
+      <c r="K47">
         <f>_xlfn.XLOOKUP($B47,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L47" s="6">
+      <c r="L47">
         <f>_xlfn.XLOOKUP($B47, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.38</v>
       </c>
-      <c r="M47" s="6">
+      <c r="M47">
         <f>_xlfn.XLOOKUP($B47, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N47" s="6">
+      <c r="N47">
         <f>_xlfn.XLOOKUP($B47, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O47" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P47" s="6">
+      <c r="O47">
+        <f t="shared" ref="O47:O54" si="56">$AC$5</f>
+        <v>3.67</v>
+      </c>
+      <c r="P47">
         <f>IF(A47&lt;&gt;"Incineration", 0, F47*K47*L47*M47*N47*O47)</f>
         <v>0</v>
       </c>
-      <c r="Q47" s="6">
+      <c r="Q47">
         <f>_xlfn.XLOOKUP($B47,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.15</v>
       </c>
-      <c r="R47" s="6">
+      <c r="R47">
         <f>_xlfn.XLOOKUP($B47,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.84</v>
       </c>
-      <c r="S47" s="6">
+      <c r="S47">
         <f>$AC$7</f>
         <v>0.5</v>
       </c>
-      <c r="T47" s="6">
-        <f>_xlfn.XLOOKUP(A47,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U47" s="6">
-        <f>_xlfn.XLOOKUP(A47,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V47" s="6">
+      <c r="T47">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V47">
         <f>$AC$6</f>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W47" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="W47">
         <f>F47*Q47*R47*S47*T47*V47*(1-U47)</f>
         <v>0</v>
       </c>
-      <c r="X47" s="6">
+      <c r="X47">
         <f>SUM(P47:P56)</f>
-        <v>10.059280000000001</v>
-      </c>
-      <c r="Y47" s="6">
+        <v>10.068424800000003</v>
+      </c>
+      <c r="Y47">
         <f>SUM(H47:H56,W47:W56)</f>
-        <v>87.181038666666666</v>
-      </c>
-      <c r="Z47" s="6">
+        <v>86.967473900000016</v>
+      </c>
+      <c r="Z47">
         <f>SUM(J47:J56)</f>
         <v>0.18124459999999998</v>
       </c>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A48" s="6" t="s">
+      <c r="A48" t="s">
         <v>5</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" t="s">
         <v>3</v>
       </c>
-      <c r="C48" s="6">
+      <c r="C48">
         <v>342</v>
       </c>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6">
+      <c r="E48">
         <f>_xlfn.XLOOKUP(B48, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.5</v>
       </c>
-      <c r="F48" s="6">
-        <f t="shared" ref="F48:F56" si="42">IF(C48&lt;&gt;"", C48,D48*E48)</f>
+      <c r="F48">
+        <f t="shared" ref="F48:F56" si="57">IF(C48&lt;&gt;"", C48,D48*E48)</f>
         <v>342</v>
       </c>
-      <c r="G48" s="6">
-        <f t="shared" ref="G48:G56" si="43">_xlfn.XLOOKUP(A48,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
+      <c r="G48">
+        <f t="shared" ref="G48:G56" si="58">_xlfn.XLOOKUP(A48,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
         <v>7.5000000000000002E-4</v>
       </c>
-      <c r="H48" s="6">
-        <f t="shared" ref="H48:H53" si="44">G48*F48</f>
+      <c r="H48">
+        <f t="shared" ref="H48:H53" si="59">G48*F48</f>
         <v>0.25650000000000001</v>
       </c>
-      <c r="I48" s="6">
-        <f t="shared" ref="I48:I56" si="45">_xlfn.XLOOKUP(A48,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
+      <c r="I48">
+        <f t="shared" ref="I48:I56" si="60">_xlfn.XLOOKUP(A48,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
         <v>9.4300000000000002E-5</v>
       </c>
-      <c r="J48" s="6">
-        <f t="shared" ref="J48:J56" si="46">F48*I48</f>
+      <c r="J48">
+        <f t="shared" ref="J48:J56" si="61">F48*I48</f>
         <v>3.2250599999999997E-2</v>
       </c>
-      <c r="K48" s="6">
+      <c r="K48">
         <f>_xlfn.XLOOKUP($B48,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L48" s="6">
+      <c r="L48">
         <f>_xlfn.XLOOKUP($B48, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.38</v>
       </c>
-      <c r="M48" s="6">
+      <c r="M48">
         <f>_xlfn.XLOOKUP($B48, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N48" s="6">
+      <c r="N48">
         <f>_xlfn.XLOOKUP($B48, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O48" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P48" s="6">
-        <f t="shared" ref="P48:P56" si="47">IF(A48&lt;&gt;"Incineration", 0, F48*K48*L48*M48*N48*O48)</f>
-        <v>0</v>
-      </c>
-      <c r="Q48" s="6">
+      <c r="O48">
+        <f t="shared" si="56"/>
+        <v>3.67</v>
+      </c>
+      <c r="P48">
+        <f t="shared" ref="P48:P56" si="62">IF(A48&lt;&gt;"Incineration", 0, F48*K48*L48*M48*N48*O48)</f>
+        <v>0</v>
+      </c>
+      <c r="Q48">
         <f>_xlfn.XLOOKUP($B48,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.15</v>
       </c>
-      <c r="R48" s="6">
+      <c r="R48">
         <f>_xlfn.XLOOKUP($B48,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.84</v>
       </c>
-      <c r="S48" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T48" s="6">
-        <f>_xlfn.XLOOKUP(A48,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U48" s="6">
-        <f>_xlfn.XLOOKUP(A48,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V48" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W48" s="6">
-        <f t="shared" ref="W48:W56" si="48">F48*Q48*R48*S48*T48*V48*(1-U48)</f>
-        <v>0</v>
-      </c>
-      <c r="X48" s="6"/>
-      <c r="Y48" s="6"/>
-      <c r="Z48" s="6"/>
+      <c r="S48">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T48">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W48">
+        <f t="shared" ref="W48:W56" si="63">F48*Q48*R48*S48*T48*V48*(1-U48)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A49" s="6" t="s">
+      <c r="A49" t="s">
         <v>5</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" t="s">
         <v>4</v>
       </c>
-      <c r="C49" s="6">
+      <c r="C49">
         <v>346</v>
       </c>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6">
+      <c r="E49">
         <f>_xlfn.XLOOKUP(B49, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.24</v>
       </c>
-      <c r="F49" s="6">
-        <f t="shared" si="42"/>
+      <c r="F49">
+        <f t="shared" si="57"/>
         <v>346</v>
       </c>
-      <c r="G49" s="6">
-        <f t="shared" si="43"/>
+      <c r="G49">
+        <f t="shared" si="58"/>
         <v>7.5000000000000002E-4</v>
       </c>
-      <c r="H49" s="6">
-        <f t="shared" si="44"/>
+      <c r="H49">
+        <f t="shared" si="59"/>
         <v>0.25950000000000001</v>
       </c>
-      <c r="I49" s="6">
-        <f t="shared" si="45"/>
+      <c r="I49">
+        <f t="shared" si="60"/>
         <v>9.4300000000000002E-5</v>
       </c>
-      <c r="J49" s="6">
-        <f t="shared" si="46"/>
+      <c r="J49">
+        <f t="shared" si="61"/>
         <v>3.2627799999999998E-2</v>
       </c>
-      <c r="K49" s="6">
+      <c r="K49">
         <f>_xlfn.XLOOKUP($B49,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L49" s="6">
+      <c r="L49">
         <f>_xlfn.XLOOKUP($B49, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.49</v>
       </c>
-      <c r="M49" s="6">
+      <c r="M49">
         <f>_xlfn.XLOOKUP($B49, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N49" s="6">
+      <c r="N49">
         <f>_xlfn.XLOOKUP($B49, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O49" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P49" s="6">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q49" s="6">
+      <c r="O49">
+        <f t="shared" si="56"/>
+        <v>3.67</v>
+      </c>
+      <c r="P49">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="Q49">
         <f>_xlfn.XLOOKUP($B49,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.2</v>
       </c>
-      <c r="R49" s="6">
+      <c r="R49">
         <f>_xlfn.XLOOKUP($B49,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.47</v>
       </c>
-      <c r="S49" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T49" s="6">
-        <f>_xlfn.XLOOKUP(A49,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U49" s="6">
-        <f>_xlfn.XLOOKUP(A49,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V49" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W49" s="6">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="X49" s="6"/>
-      <c r="Y49" s="6"/>
-      <c r="Z49" s="6"/>
+      <c r="S49">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T49">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W49">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A50" s="6" t="s">
+      <c r="A50" t="s">
         <v>40</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" t="s">
         <v>45</v>
       </c>
-      <c r="C50" s="6">
+      <c r="C50">
         <v>1435</v>
       </c>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6">
+      <c r="E50">
         <f>_xlfn.XLOOKUP(B50, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.15</v>
       </c>
-      <c r="F50" s="6">
-        <f t="shared" si="42"/>
+      <c r="F50">
+        <f t="shared" si="57"/>
         <v>1435</v>
       </c>
-      <c r="G50" s="6">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="H50" s="6">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="I50" s="6">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="J50" s="6">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="K50" s="6">
+      <c r="G50">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="K50">
         <f>_xlfn.XLOOKUP($B50,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L50" s="6">
+      <c r="L50">
         <f>_xlfn.XLOOKUP($B50, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M50" s="6">
+      <c r="M50">
         <f>_xlfn.XLOOKUP($B50, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N50" s="6">
+      <c r="N50">
         <f>_xlfn.XLOOKUP($B50, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O50" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P50" s="6">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q50" s="6">
+      <c r="O50">
+        <f t="shared" si="56"/>
+        <v>3.67</v>
+      </c>
+      <c r="P50">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="Q50">
         <f>_xlfn.XLOOKUP($B50,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.43</v>
       </c>
-      <c r="R50" s="6">
+      <c r="R50">
         <f>_xlfn.XLOOKUP($B50,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.1</v>
       </c>
-      <c r="S50" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T50" s="6">
-        <f>_xlfn.XLOOKUP(A50,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S50">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T50">
+        <f t="shared" si="17"/>
         <v>0.4</v>
       </c>
-      <c r="U50" s="6">
-        <f>_xlfn.XLOOKUP(A50,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V50" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W50" s="6">
-        <f t="shared" si="48"/>
-        <v>16.454666666666668</v>
-      </c>
-      <c r="X50" s="6"/>
-      <c r="Y50" s="6"/>
-      <c r="Z50" s="6"/>
+      <c r="U50">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W50">
+        <f t="shared" si="63"/>
+        <v>16.413530000000002</v>
+      </c>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A51" s="6" t="s">
+      <c r="A51" t="s">
         <v>40</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" t="s">
         <v>46</v>
       </c>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6">
+      <c r="D51">
         <v>1235</v>
       </c>
-      <c r="E51" s="6">
+      <c r="E51">
         <f>_xlfn.XLOOKUP(B51, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.15</v>
       </c>
-      <c r="F51" s="6">
-        <f t="shared" si="42"/>
+      <c r="F51">
+        <f t="shared" si="57"/>
         <v>185.25</v>
       </c>
-      <c r="G51" s="6">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="H51" s="6">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="I51" s="6">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="J51" s="6">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="K51" s="6">
+      <c r="G51">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="K51">
         <f>_xlfn.XLOOKUP($B51,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.9</v>
       </c>
-      <c r="L51" s="6">
+      <c r="L51">
         <f>_xlfn.XLOOKUP($B51, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M51" s="6">
+      <c r="M51">
         <f>_xlfn.XLOOKUP($B51, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N51" s="6">
+      <c r="N51">
         <f>_xlfn.XLOOKUP($B51, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O51" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P51" s="6">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q51" s="6">
+      <c r="O51">
+        <f t="shared" si="56"/>
+        <v>3.67</v>
+      </c>
+      <c r="P51">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="Q51">
         <f>_xlfn.XLOOKUP($B51,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.43</v>
       </c>
-      <c r="R51" s="6">
+      <c r="R51">
         <f>_xlfn.XLOOKUP($B51,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.1</v>
       </c>
-      <c r="S51" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T51" s="6">
-        <f>_xlfn.XLOOKUP(A51,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S51">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T51">
+        <f t="shared" si="17"/>
         <v>0.4</v>
       </c>
-      <c r="U51" s="6">
-        <f>_xlfn.XLOOKUP(A51,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V51" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W51" s="6">
-        <f t="shared" si="48"/>
-        <v>2.1242000000000001</v>
-      </c>
-      <c r="X51" s="6"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
+      <c r="U51">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V51">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W51">
+        <f t="shared" si="63"/>
+        <v>2.1188895000000003</v>
+      </c>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A52" s="6" t="s">
+      <c r="A52" t="s">
         <v>2</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6">
+      <c r="D52">
         <v>345</v>
       </c>
-      <c r="E52" s="6">
+      <c r="E52">
         <f>_xlfn.XLOOKUP(B52, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="F52" s="6">
-        <f t="shared" si="42"/>
+      <c r="F52">
+        <f t="shared" si="57"/>
         <v>48.300000000000004</v>
       </c>
-      <c r="G52" s="6">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="H52" s="6">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="I52" s="6">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="J52" s="6">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="K52" s="6">
+      <c r="G52">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="K52">
         <f>_xlfn.XLOOKUP($B52,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.8</v>
       </c>
-      <c r="L52" s="6">
+      <c r="L52">
         <f>_xlfn.XLOOKUP($B52, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M52" s="6">
+      <c r="M52">
         <f>_xlfn.XLOOKUP($B52, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.2</v>
       </c>
-      <c r="N52" s="6">
+      <c r="N52">
         <f>_xlfn.XLOOKUP($B52, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O52" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P52" s="6">
-        <f t="shared" si="47"/>
-        <v>10.059280000000001</v>
-      </c>
-      <c r="Q52" s="6">
+      <c r="O52">
+        <f t="shared" si="56"/>
+        <v>3.67</v>
+      </c>
+      <c r="P52">
+        <f t="shared" si="62"/>
+        <v>10.068424800000003</v>
+      </c>
+      <c r="Q52">
         <f>_xlfn.XLOOKUP($B52,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.24</v>
       </c>
-      <c r="R52" s="6">
+      <c r="R52">
         <f>_xlfn.XLOOKUP($B52,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S52" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T52" s="6">
-        <f>_xlfn.XLOOKUP(A52,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U52" s="6">
-        <f>_xlfn.XLOOKUP(A52,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V52" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W52" s="6">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="X52" s="6"/>
-      <c r="Y52" s="6"/>
-      <c r="Z52" s="6"/>
+      <c r="S52">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T52">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U52">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W52">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A53" s="6" t="s">
+      <c r="A53" t="s">
         <v>9</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" t="s">
         <v>1</v>
       </c>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6">
+      <c r="D53">
         <v>4356</v>
       </c>
-      <c r="E53" s="6">
+      <c r="E53">
         <f>_xlfn.XLOOKUP(B53, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.72</v>
       </c>
-      <c r="F53" s="6">
-        <f t="shared" si="42"/>
+      <c r="F53">
+        <f t="shared" si="57"/>
         <v>3136.3199999999997</v>
       </c>
-      <c r="G53" s="6">
-        <f t="shared" si="43"/>
+      <c r="G53">
+        <f t="shared" si="58"/>
         <v>1E-4</v>
       </c>
-      <c r="H53" s="6">
-        <f t="shared" si="44"/>
+      <c r="H53">
+        <f t="shared" si="59"/>
         <v>0.31363199999999997</v>
       </c>
-      <c r="I53" s="6">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="J53" s="6">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="K53" s="6">
+      <c r="I53">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="K53">
         <f>_xlfn.XLOOKUP($B53,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0</v>
       </c>
-      <c r="L53" s="6">
+      <c r="L53">
         <f>_xlfn.XLOOKUP($B53, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M53" s="6">
+      <c r="M53">
         <f>_xlfn.XLOOKUP($B53, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N53" s="6">
+      <c r="N53">
         <f>_xlfn.XLOOKUP($B53, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O53" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P53" s="6">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q53" s="6">
+      <c r="O53">
+        <f t="shared" si="56"/>
+        <v>3.67</v>
+      </c>
+      <c r="P53">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="Q53">
         <f>_xlfn.XLOOKUP($B53,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.05</v>
       </c>
-      <c r="R53" s="6">
+      <c r="R53">
         <f>_xlfn.XLOOKUP($B53,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S53" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T53" s="6">
-        <f>_xlfn.XLOOKUP(A53,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U53" s="6">
-        <f>_xlfn.XLOOKUP(A53,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V53" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W53" s="6">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="X53" s="6"/>
-      <c r="Y53" s="6"/>
-      <c r="Z53" s="6"/>
+      <c r="S53">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T53">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W53">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A54" s="6" t="s">
+      <c r="A54" t="s">
         <v>38</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" t="s">
         <v>54</v>
       </c>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6">
+      <c r="D54">
         <v>324</v>
       </c>
-      <c r="E54" s="6">
+      <c r="E54">
         <f>_xlfn.XLOOKUP(B54, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.39</v>
       </c>
-      <c r="F54" s="6">
-        <f t="shared" si="42"/>
+      <c r="F54">
+        <f t="shared" si="57"/>
         <v>126.36</v>
       </c>
-      <c r="G54" s="6">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="H54" s="6">
+      <c r="G54">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="H54">
         <f>G54*F54</f>
         <v>0</v>
       </c>
-      <c r="I54" s="6">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="J54" s="6">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="K54" s="6">
+      <c r="I54">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="K54">
         <f>_xlfn.XLOOKUP($B54,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L54" s="6">
+      <c r="L54">
         <f>_xlfn.XLOOKUP($B54, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.7</v>
       </c>
-      <c r="M54" s="6">
+      <c r="M54">
         <f>_xlfn.XLOOKUP($B54, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.1</v>
       </c>
-      <c r="N54" s="6">
+      <c r="N54">
         <f>_xlfn.XLOOKUP($B54, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O54" s="6">
-        <f>$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P54" s="6">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q54" s="6">
+      <c r="O54">
+        <f t="shared" si="56"/>
+        <v>3.67</v>
+      </c>
+      <c r="P54">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="Q54">
         <f>_xlfn.XLOOKUP($B54,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.24</v>
       </c>
-      <c r="R54" s="6">
+      <c r="R54">
         <f>_xlfn.XLOOKUP($B54,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S54" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T54" s="6">
-        <f>_xlfn.XLOOKUP(A54,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S54">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T54">
+        <f t="shared" si="17"/>
         <v>0.8</v>
       </c>
-      <c r="U54" s="6">
-        <f>_xlfn.XLOOKUP(A54,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V54" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W54" s="6">
-        <f t="shared" si="48"/>
-        <v>8.08704</v>
-      </c>
-      <c r="X54" s="6"/>
-      <c r="Y54" s="6"/>
-      <c r="Z54" s="6"/>
+      <c r="U54">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V54">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W54">
+        <f t="shared" si="63"/>
+        <v>8.0668224000000013</v>
+      </c>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A55" s="6" t="s">
+      <c r="A55" t="s">
         <v>38</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" t="s">
         <v>8</v>
       </c>
-      <c r="C55" s="6">
+      <c r="C55">
         <v>565</v>
       </c>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6">
+      <c r="E55">
         <f>_xlfn.XLOOKUP(B55, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="F55" s="6">
-        <f t="shared" si="42"/>
+      <c r="F55">
+        <f t="shared" si="57"/>
         <v>565</v>
       </c>
-      <c r="G55" s="6">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="H55" s="6">
-        <f t="shared" ref="H55:H56" si="49">G55*F55</f>
-        <v>0</v>
-      </c>
-      <c r="I55" s="6">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="J55" s="6">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="K55" s="6">
+      <c r="G55">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <f t="shared" ref="H55:H56" si="64">G55*F55</f>
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="K55">
         <f>_xlfn.XLOOKUP($B55,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.84</v>
       </c>
-      <c r="L55" s="6">
+      <c r="L55">
         <f>_xlfn.XLOOKUP($B55, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.67</v>
       </c>
-      <c r="M55" s="6">
+      <c r="M55">
         <f>_xlfn.XLOOKUP($B55, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.2</v>
       </c>
-      <c r="N55" s="6">
+      <c r="N55">
         <f>_xlfn.XLOOKUP($B55, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O55" s="6">
-        <f t="shared" ref="O55:O56" si="50">$AC$5</f>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P55" s="6">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q55" s="6">
+      <c r="O55">
+        <f t="shared" ref="O55:O56" si="65">$AC$5</f>
+        <v>3.67</v>
+      </c>
+      <c r="P55">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="Q55">
         <f>_xlfn.XLOOKUP($B55,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.39</v>
       </c>
-      <c r="R55" s="6">
+      <c r="R55">
         <f>_xlfn.XLOOKUP($B55,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S55" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T55" s="6">
-        <f>_xlfn.XLOOKUP(A55,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S55">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T55">
+        <f t="shared" si="17"/>
         <v>0.8</v>
       </c>
-      <c r="U55" s="6">
-        <f>_xlfn.XLOOKUP(A55,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V55" s="6">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W55" s="6">
-        <f t="shared" si="48"/>
-        <v>58.76</v>
-      </c>
-      <c r="X55" s="6"/>
-      <c r="Y55" s="6"/>
-      <c r="Z55" s="6"/>
+      <c r="U55">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V55">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W55">
+        <f t="shared" si="63"/>
+        <v>58.613100000000003</v>
+      </c>
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C56" s="4">
+      <c r="C56" s="3">
         <v>7643</v>
       </c>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4">
+      <c r="D56" s="3"/>
+      <c r="E56" s="3">
         <f>_xlfn.XLOOKUP(B56, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.42</v>
       </c>
-      <c r="F56" s="4">
-        <f t="shared" si="42"/>
+      <c r="F56" s="3">
+        <f t="shared" si="57"/>
         <v>7643</v>
       </c>
-      <c r="G56" s="4">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="H56" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="I56" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="J56" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="K56" s="4">
+      <c r="G56" s="3">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="H56" s="3">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="I56" s="3">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="3">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="3">
         <f>_xlfn.XLOOKUP($B56,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.9</v>
       </c>
-      <c r="L56" s="4">
+      <c r="L56" s="3">
         <f>_xlfn.XLOOKUP($B56, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.03</v>
       </c>
-      <c r="M56" s="4">
+      <c r="M56" s="3">
         <f>_xlfn.XLOOKUP($B56, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>1</v>
       </c>
-      <c r="N56" s="4">
+      <c r="N56" s="3">
         <f>_xlfn.XLOOKUP($B56, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O56" s="4">
-        <f t="shared" si="50"/>
-        <v>3.6666666666666665</v>
-      </c>
-      <c r="P56" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q56" s="4">
+      <c r="O56" s="3">
+        <f t="shared" si="65"/>
+        <v>3.67</v>
+      </c>
+      <c r="P56" s="3">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="Q56" s="3">
         <f>_xlfn.XLOOKUP($B56,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0</v>
       </c>
-      <c r="R56" s="4">
+      <c r="R56" s="3">
         <f>_xlfn.XLOOKUP($B56,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0</v>
       </c>
-      <c r="S56" s="4">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T56" s="4">
-        <f>_xlfn.XLOOKUP(A56,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S56" s="3">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T56" s="3">
+        <f t="shared" si="17"/>
         <v>0.8</v>
       </c>
-      <c r="U56" s="4">
-        <f>_xlfn.XLOOKUP(A56,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V56" s="4">
-        <f t="shared" si="14"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="W56" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="X56" s="4"/>
-      <c r="Y56" s="4"/>
-      <c r="Z56" s="4"/>
+      <c r="U56" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V56" s="3">
+        <f t="shared" si="26"/>
+        <v>1.33</v>
+      </c>
+      <c r="W56" s="3">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/packages/calculators/src/modules/test/10.1-solid-waste.xlsx
+++ b/packages/calculators/src/modules/test/10.1-solid-waste.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators-internal/packages/calculators/src/modules/test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators/packages/calculators/src/modules/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C17E295-9462-B64B-8EF0-E6EBC04BC2CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1E3CD2-329B-5E49-B469-EF2BDFED75AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15880" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
@@ -297,14 +297,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -820,23 +818,23 @@
         <v>6000</v>
       </c>
       <c r="G5">
-        <f>$Y$5</f>
+        <f t="shared" ref="G5:G10" si="0">$Y$5</f>
         <v>7.5000000000000002E-4</v>
       </c>
       <c r="H5">
-        <f>$Y$6</f>
-        <v>1E-4</v>
+        <f t="shared" ref="H5:H10" si="1">$Y$6</f>
+        <v>1E-3</v>
       </c>
       <c r="I5">
         <f>A5*G5+B5*H5</f>
-        <v>0.95</v>
+        <v>2.75</v>
       </c>
       <c r="J5">
-        <f>$Z$5</f>
+        <f t="shared" ref="J5:J10" si="2">$Z$5</f>
         <v>9.4300000000000002E-5</v>
       </c>
       <c r="K5">
-        <f>$Z$6</f>
+        <f t="shared" ref="K5:K10" si="3">$Z$6</f>
         <v>0</v>
       </c>
       <c r="L5">
@@ -844,11 +842,11 @@
         <v>9.4299999999999995E-2</v>
       </c>
       <c r="M5">
-        <f>$AC$4</f>
+        <f t="shared" ref="M5:M10" si="4">$AC$4</f>
         <v>5.0500000000000003E-2</v>
       </c>
       <c r="N5">
-        <f>$AC$5</f>
+        <f t="shared" ref="N5:N10" si="5">$AC$5</f>
         <v>3.6666666666666665</v>
       </c>
       <c r="O5">
@@ -856,15 +854,15 @@
         <v>555.5</v>
       </c>
       <c r="P5">
-        <f>$Y$9</f>
+        <f t="shared" ref="P5:P10" si="6">$Y$9</f>
         <v>5.0200000000000002E-2</v>
       </c>
       <c r="Q5">
-        <f>$Y$10</f>
+        <f t="shared" ref="Q5:Q10" si="7">$Y$10</f>
         <v>2.5100000000000001E-2</v>
       </c>
       <c r="R5">
-        <f>$Y$11</f>
+        <f t="shared" ref="R5:R10" si="8">$Y$11</f>
         <v>3.95E-2</v>
       </c>
       <c r="S5">
@@ -877,7 +875,7 @@
       </c>
       <c r="U5">
         <f>I5+S5</f>
-        <v>564.25</v>
+        <v>566.04999999999995</v>
       </c>
       <c r="V5">
         <f>L5</f>
@@ -944,74 +942,74 @@
         <v>1000</v>
       </c>
       <c r="G6">
-        <f>$Y$5</f>
+        <f t="shared" si="0"/>
         <v>7.5000000000000002E-4</v>
       </c>
       <c r="H6">
-        <f>$Y$6</f>
-        <v>1E-4</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="I6">
-        <f t="shared" ref="I6:I10" si="0">A6*G6+B6*H6</f>
-        <v>0.85</v>
+        <f t="shared" ref="I6:I10" si="9">A6*G6+B6*H6</f>
+        <v>1.75</v>
       </c>
       <c r="J6">
-        <f>$Z$5</f>
+        <f t="shared" si="2"/>
         <v>9.4300000000000002E-5</v>
       </c>
       <c r="K6">
-        <f>$Z$6</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L6">
-        <f t="shared" ref="L6:L10" si="1">A6*J6+B6*K6</f>
+        <f t="shared" ref="L6:L10" si="10">A6*J6+B6*K6</f>
         <v>9.4299999999999995E-2</v>
       </c>
       <c r="M6">
-        <f>$AC$4</f>
+        <f t="shared" si="4"/>
         <v>5.0500000000000003E-2</v>
       </c>
       <c r="N6">
-        <f>$AC$5</f>
+        <f t="shared" si="5"/>
         <v>3.6666666666666665</v>
       </c>
       <c r="O6">
-        <f t="shared" ref="O6:O10" si="2">C6*M6*N6</f>
+        <f t="shared" ref="O6:O10" si="11">C6*M6*N6</f>
         <v>185.16666666666666</v>
       </c>
       <c r="P6">
-        <f>$Y$9</f>
+        <f t="shared" si="6"/>
         <v>5.0200000000000002E-2</v>
       </c>
       <c r="Q6">
-        <f>$Y$10</f>
+        <f t="shared" si="7"/>
         <v>2.5100000000000001E-2</v>
       </c>
       <c r="R6">
-        <f>$Y$11</f>
+        <f t="shared" si="8"/>
         <v>3.95E-2</v>
       </c>
       <c r="S6">
-        <f t="shared" ref="S6:S10" si="3">D6*P6+E6*Q6+F6*R6</f>
+        <f t="shared" ref="S6:S10" si="12">D6*P6+E6*Q6+F6*R6</f>
         <v>114.80000000000001</v>
       </c>
       <c r="T6">
-        <f t="shared" ref="T6:T10" si="4">O6</f>
+        <f t="shared" ref="T6:T10" si="13">O6</f>
         <v>185.16666666666666</v>
       </c>
       <c r="U6">
-        <f t="shared" ref="U6:U10" si="5">I6+S6</f>
-        <v>115.65</v>
+        <f t="shared" ref="U6:U10" si="14">I6+S6</f>
+        <v>116.55000000000001</v>
       </c>
       <c r="V6">
-        <f t="shared" ref="V6:V10" si="6">L6</f>
+        <f t="shared" ref="V6:V10" si="15">L6</f>
         <v>9.4299999999999995E-2</v>
       </c>
-      <c r="X6" s="3" t="s">
+      <c r="X6" t="s">
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>1E-4</v>
+        <v>1E-3</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1059,67 +1057,67 @@
         <v>1234</v>
       </c>
       <c r="G7">
-        <f>$Y$5</f>
+        <f t="shared" si="0"/>
         <v>7.5000000000000002E-4</v>
       </c>
       <c r="H7">
-        <f>$Y$6</f>
-        <v>1E-4</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="I7">
-        <f t="shared" si="0"/>
-        <v>0.95</v>
+        <f t="shared" si="9"/>
+        <v>2.75</v>
       </c>
       <c r="J7">
-        <f>$Z$5</f>
+        <f t="shared" si="2"/>
         <v>9.4300000000000002E-5</v>
       </c>
       <c r="K7">
-        <f>$Z$6</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>9.4299999999999995E-2</v>
       </c>
       <c r="M7">
-        <f>$AC$4</f>
+        <f t="shared" si="4"/>
         <v>5.0500000000000003E-2</v>
       </c>
       <c r="N7">
-        <f>$AC$5</f>
+        <f t="shared" si="5"/>
         <v>3.6666666666666665</v>
       </c>
       <c r="O7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>228.49566666666669</v>
       </c>
       <c r="P7">
-        <f>$Y$9</f>
+        <f t="shared" si="6"/>
         <v>5.0200000000000002E-2</v>
       </c>
       <c r="Q7">
-        <f>$Y$10</f>
+        <f t="shared" si="7"/>
         <v>2.5100000000000001E-2</v>
       </c>
       <c r="R7">
-        <f>$Y$11</f>
+        <f t="shared" si="8"/>
         <v>3.95E-2</v>
       </c>
       <c r="S7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>228.49566666666669</v>
       </c>
       <c r="U7">
-        <f t="shared" si="5"/>
-        <v>0.95</v>
+        <f t="shared" si="14"/>
+        <v>2.75</v>
       </c>
       <c r="V7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>9.4299999999999995E-2</v>
       </c>
       <c r="AB7" t="s">
@@ -1164,67 +1162,67 @@
         <v>6000</v>
       </c>
       <c r="G8">
-        <f>$Y$5</f>
+        <f t="shared" si="0"/>
         <v>7.5000000000000002E-4</v>
       </c>
       <c r="H8">
-        <f>$Y$6</f>
-        <v>1E-4</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="I8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="J8">
-        <f>$Z$5</f>
+        <f t="shared" si="2"/>
         <v>9.4300000000000002E-5</v>
       </c>
       <c r="K8">
-        <f>$Z$6</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M8">
-        <f>$AC$4</f>
+        <f t="shared" si="4"/>
         <v>5.0500000000000003E-2</v>
       </c>
       <c r="N8">
-        <f>$AC$5</f>
+        <f t="shared" si="5"/>
         <v>3.6666666666666665</v>
       </c>
       <c r="O8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P8">
-        <f>$Y$9</f>
+        <f t="shared" si="6"/>
         <v>5.0200000000000002E-2</v>
       </c>
       <c r="Q8">
-        <f>$Y$10</f>
+        <f t="shared" si="7"/>
         <v>2.5100000000000001E-2</v>
       </c>
       <c r="R8">
-        <f>$Y$11</f>
+        <f t="shared" si="8"/>
         <v>3.95E-2</v>
       </c>
       <c r="S8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>563.29999999999995</v>
       </c>
       <c r="T8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="U8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="14"/>
         <v>563.29999999999995</v>
       </c>
       <c r="V8">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="X8" t="s">
@@ -1278,67 +1276,67 @@
         <v>6000</v>
       </c>
       <c r="G9">
-        <f>$Y$5</f>
+        <f t="shared" si="0"/>
         <v>7.5000000000000002E-4</v>
       </c>
       <c r="H9">
-        <f>$Y$6</f>
-        <v>1E-4</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="I9">
-        <f t="shared" si="0"/>
-        <v>0.2</v>
+        <f t="shared" si="9"/>
+        <v>2</v>
       </c>
       <c r="J9">
-        <f>$Z$5</f>
+        <f t="shared" si="2"/>
         <v>9.4300000000000002E-5</v>
       </c>
       <c r="K9">
-        <f>$Z$6</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M9">
-        <f>$AC$4</f>
+        <f t="shared" si="4"/>
         <v>5.0500000000000003E-2</v>
       </c>
       <c r="N9">
-        <f>$AC$5</f>
+        <f t="shared" si="5"/>
         <v>3.6666666666666665</v>
       </c>
       <c r="O9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>434.21583333333336</v>
       </c>
       <c r="P9">
-        <f>$Y$9</f>
+        <f t="shared" si="6"/>
         <v>5.0200000000000002E-2</v>
       </c>
       <c r="Q9">
-        <f>$Y$10</f>
+        <f t="shared" si="7"/>
         <v>2.5100000000000001E-2</v>
       </c>
       <c r="R9">
-        <f>$Y$11</f>
+        <f t="shared" si="8"/>
         <v>3.95E-2</v>
       </c>
       <c r="S9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>437.8</v>
       </c>
       <c r="T9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>434.21583333333336</v>
       </c>
       <c r="U9">
-        <f t="shared" si="5"/>
-        <v>438</v>
+        <f t="shared" si="14"/>
+        <v>439.8</v>
       </c>
       <c r="V9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="X9" t="s">
@@ -1395,67 +1393,67 @@
         <v>6000</v>
       </c>
       <c r="G10">
-        <f>$Y$5</f>
+        <f t="shared" si="0"/>
         <v>7.5000000000000002E-4</v>
       </c>
       <c r="H10">
-        <f>$Y$6</f>
-        <v>1E-4</v>
+        <f t="shared" si="1"/>
+        <v>1E-3</v>
       </c>
       <c r="I10">
-        <f t="shared" si="0"/>
-        <v>0.95</v>
+        <f t="shared" si="9"/>
+        <v>2.75</v>
       </c>
       <c r="J10">
-        <f>$Z$5</f>
+        <f t="shared" si="2"/>
         <v>9.4300000000000002E-5</v>
       </c>
       <c r="K10">
-        <f>$Z$6</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="10"/>
         <v>9.4299999999999995E-2</v>
       </c>
       <c r="M10">
-        <f>$AC$4</f>
+        <f t="shared" si="4"/>
         <v>5.0500000000000003E-2</v>
       </c>
       <c r="N10">
-        <f>$AC$5</f>
+        <f t="shared" si="5"/>
         <v>3.6666666666666665</v>
       </c>
       <c r="O10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P10">
-        <f>$Y$9</f>
+        <f t="shared" si="6"/>
         <v>5.0200000000000002E-2</v>
       </c>
       <c r="Q10">
-        <f>$Y$10</f>
+        <f t="shared" si="7"/>
         <v>2.5100000000000001E-2</v>
       </c>
       <c r="R10">
-        <f>$Y$11</f>
+        <f t="shared" si="8"/>
         <v>3.95E-2</v>
       </c>
       <c r="S10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="12"/>
         <v>563.29999999999995</v>
       </c>
       <c r="T10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="U10">
-        <f t="shared" si="5"/>
-        <v>564.25</v>
+        <f t="shared" si="14"/>
+        <v>566.04999999999995</v>
       </c>
       <c r="V10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="15"/>
         <v>9.4299999999999995E-2</v>
       </c>
       <c r="X10" t="s">
@@ -1660,1031 +1658,997 @@
       <c r="W16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="X16" s="5" t="s">
+      <c r="X16" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="Y16" s="5" t="s">
+      <c r="Y16" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="Z16" s="5" t="s">
+      <c r="Z16" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
+      <c r="A17" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17">
         <v>1234</v>
       </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6">
+      <c r="E17">
         <f>_xlfn.XLOOKUP(B17, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.5</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17">
         <f>IF(C17&lt;&gt;"", C17,D17*E17)</f>
         <v>1234</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17">
         <f>_xlfn.XLOOKUP(A17,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17">
         <f>G17*F17</f>
         <v>0</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17">
         <f>_xlfn.XLOOKUP(A17,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="6">
+      <c r="J17">
         <f>F17*I17</f>
         <v>0</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K17">
         <f>_xlfn.XLOOKUP($B17,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L17" s="6">
+      <c r="L17">
         <f>_xlfn.XLOOKUP($B17, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.38</v>
       </c>
-      <c r="M17" s="6">
+      <c r="M17">
         <f>_xlfn.XLOOKUP($B17, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N17" s="6">
+      <c r="N17">
         <f>_xlfn.XLOOKUP($B17, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O17" s="6">
-        <f>$AC$5</f>
+      <c r="O17">
+        <f t="shared" ref="O17:O24" si="16">$AC$5</f>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P17" s="6">
+      <c r="P17">
         <f>IF(A17&lt;&gt;"Incineration", 0, F17*K17*L17*M17*N17*O17)</f>
         <v>0</v>
       </c>
-      <c r="Q17" s="6">
+      <c r="Q17">
         <f>_xlfn.XLOOKUP($B17,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.15</v>
       </c>
-      <c r="R17" s="6">
+      <c r="R17">
         <f>_xlfn.XLOOKUP($B17,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.84</v>
       </c>
-      <c r="S17" s="6">
+      <c r="S17">
         <f>$AC$7</f>
         <v>0.5</v>
       </c>
-      <c r="T17" s="6">
-        <f>_xlfn.XLOOKUP(A17,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U17" s="6">
-        <f>_xlfn.XLOOKUP(A17,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V17" s="6">
+      <c r="T17">
+        <f t="shared" ref="T17:T56" si="17">_xlfn.XLOOKUP(A17,$X$9:$X$11,Z$9:Z$11, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <f t="shared" ref="U17:U56" si="18">_xlfn.XLOOKUP(A17,$X$9:$X$11,AA$9:AA$11, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="V17">
         <f>$AC$6</f>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W17" s="6">
+      <c r="W17">
         <f>F17*Q17*R17*S17*T17*V17*(1-U17)</f>
         <v>0</v>
       </c>
-      <c r="X17" s="6">
+      <c r="X17">
         <f>SUM(P17:P26)</f>
         <v>188.51871719999997</v>
       </c>
-      <c r="Y17" s="6">
+      <c r="Y17">
         <f>SUM(H17:H26,W17:W26)</f>
         <v>0</v>
       </c>
-      <c r="Z17" s="6">
+      <c r="Z17">
         <f>SUM(J17:J26)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
+      <c r="A18" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18">
         <v>342</v>
       </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6">
+      <c r="E18">
         <f>_xlfn.XLOOKUP(B18, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.09</v>
       </c>
-      <c r="F18" s="6">
-        <f t="shared" ref="F18:F24" si="7">IF(C18&lt;&gt;"", C18,D18*E18)</f>
+      <c r="F18">
+        <f t="shared" ref="F18:F24" si="19">IF(C18&lt;&gt;"", C18,D18*E18)</f>
         <v>342</v>
       </c>
-      <c r="G18" s="6">
-        <f t="shared" ref="G18:G24" si="8">_xlfn.XLOOKUP(A18,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="6">
-        <f t="shared" ref="H18:H23" si="9">G18*F18</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="6">
-        <f t="shared" ref="I18:I24" si="10">_xlfn.XLOOKUP(A18,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="6">
-        <f t="shared" ref="J18:J24" si="11">F18*I18</f>
-        <v>0</v>
-      </c>
-      <c r="K18" s="6">
+      <c r="G18">
+        <f t="shared" ref="G18:G24" si="20">_xlfn.XLOOKUP(A18,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <f t="shared" ref="H18:H23" si="21">G18*F18</f>
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <f t="shared" ref="I18:I24" si="22">_xlfn.XLOOKUP(A18,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <f t="shared" ref="J18:J24" si="23">F18*I18</f>
+        <v>0</v>
+      </c>
+      <c r="K18">
         <f>_xlfn.XLOOKUP($B18,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.9</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L18">
         <f>_xlfn.XLOOKUP($B18, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.46</v>
       </c>
-      <c r="M18" s="6">
+      <c r="M18">
         <f>_xlfn.XLOOKUP($B18, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.01</v>
       </c>
-      <c r="N18" s="6">
+      <c r="N18">
         <f>_xlfn.XLOOKUP($B18, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O18" s="6">
-        <f>$AC$5</f>
+      <c r="O18">
+        <f t="shared" si="16"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P18" s="6">
-        <f t="shared" ref="P18:P24" si="12">IF(A18&lt;&gt;"Incineration", 0, F18*K18*L18*M18*N18*O18)</f>
+      <c r="P18">
+        <f t="shared" ref="P18:P24" si="24">IF(A18&lt;&gt;"Incineration", 0, F18*K18*L18*M18*N18*O18)</f>
         <v>3.6860075999999999</v>
       </c>
-      <c r="Q18" s="6">
+      <c r="Q18">
         <f>_xlfn.XLOOKUP($B18,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.4</v>
       </c>
-      <c r="R18" s="6">
+      <c r="R18">
         <f>_xlfn.XLOOKUP($B18,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.49</v>
       </c>
-      <c r="S18" s="6">
-        <f t="shared" ref="S18:S56" si="13">$AC$7</f>
-        <v>0.5</v>
-      </c>
-      <c r="T18" s="6">
-        <f>_xlfn.XLOOKUP(A18,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U18" s="6">
-        <f>_xlfn.XLOOKUP(A18,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V18" s="6">
-        <f t="shared" ref="V18:V56" si="14">$AC$6</f>
+      <c r="S18">
+        <f t="shared" ref="S18:S56" si="25">$AC$7</f>
+        <v>0.5</v>
+      </c>
+      <c r="T18">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <f t="shared" ref="V18:V56" si="26">$AC$6</f>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W18" s="6">
-        <f t="shared" ref="W18:W24" si="15">F18*Q18*R18*S18*T18*V18*(1-U18)</f>
-        <v>0</v>
-      </c>
-      <c r="X18" s="6"/>
-      <c r="Y18" s="6"/>
-      <c r="Z18" s="6"/>
+      <c r="W18">
+        <f t="shared" ref="W18:W24" si="27">F18*Q18*R18*S18*T18*V18*(1-U18)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
+      <c r="A19" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" t="s">
         <v>4</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19">
         <v>346</v>
       </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6">
+      <c r="E19">
         <f>_xlfn.XLOOKUP(B19, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.24</v>
       </c>
-      <c r="F19" s="6">
-        <f t="shared" si="7"/>
+      <c r="F19">
+        <f t="shared" si="19"/>
         <v>346</v>
       </c>
-      <c r="G19" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H19" s="6">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="I19" s="6">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K19" s="6">
+      <c r="G19">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="K19">
         <f>_xlfn.XLOOKUP($B19,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L19" s="6">
+      <c r="L19">
         <f>_xlfn.XLOOKUP($B19, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.49</v>
       </c>
-      <c r="M19" s="6">
+      <c r="M19">
         <f>_xlfn.XLOOKUP($B19, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N19" s="6">
+      <c r="N19">
         <f>_xlfn.XLOOKUP($B19, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O19" s="6">
-        <f>$AC$5</f>
+      <c r="O19">
+        <f t="shared" si="16"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P19" s="6">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="6">
+      <c r="P19">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Q19">
         <f>_xlfn.XLOOKUP($B19,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.2</v>
       </c>
-      <c r="R19" s="6">
+      <c r="R19">
         <f>_xlfn.XLOOKUP($B19,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.47</v>
       </c>
-      <c r="S19" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T19" s="6">
-        <f>_xlfn.XLOOKUP(A19,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U19" s="6">
-        <f>_xlfn.XLOOKUP(A19,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V19" s="6">
-        <f t="shared" si="14"/>
+      <c r="S19">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W19" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X19" s="6"/>
-      <c r="Y19" s="6"/>
-      <c r="Z19" s="6"/>
+      <c r="W19">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
+      <c r="A20" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20">
         <v>1435</v>
       </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6">
+      <c r="E20">
         <f>_xlfn.XLOOKUP(B20, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.15</v>
       </c>
-      <c r="F20" s="6">
-        <f t="shared" si="7"/>
+      <c r="F20">
+        <f t="shared" si="19"/>
         <v>1435</v>
       </c>
-      <c r="G20" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H20" s="6">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="6">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="6">
+      <c r="G20">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="K20">
         <f>_xlfn.XLOOKUP($B20,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L20" s="6">
+      <c r="L20">
         <f>_xlfn.XLOOKUP($B20, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M20" s="6">
+      <c r="M20">
         <f>_xlfn.XLOOKUP($B20, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N20" s="6">
+      <c r="N20">
         <f>_xlfn.XLOOKUP($B20, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O20" s="6">
-        <f>$AC$5</f>
+      <c r="O20">
+        <f t="shared" si="16"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P20" s="6">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="6">
+      <c r="P20">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Q20">
         <f>_xlfn.XLOOKUP($B20,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.43</v>
       </c>
-      <c r="R20" s="6">
+      <c r="R20">
         <f>_xlfn.XLOOKUP($B20,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.1</v>
       </c>
-      <c r="S20" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T20" s="6">
-        <f>_xlfn.XLOOKUP(A20,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U20" s="6">
-        <f>_xlfn.XLOOKUP(A20,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V20" s="6">
-        <f t="shared" si="14"/>
+      <c r="S20">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W20" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X20" s="6"/>
-      <c r="Y20" s="6"/>
-      <c r="Z20" s="6"/>
+      <c r="W20">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A21" s="6" t="s">
+      <c r="A21" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6">
+      <c r="D21">
         <v>1235</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21">
         <f>_xlfn.XLOOKUP(B21, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.15</v>
       </c>
-      <c r="F21" s="6">
-        <f t="shared" si="7"/>
+      <c r="F21">
+        <f t="shared" si="19"/>
         <v>185.25</v>
       </c>
-      <c r="G21" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="6">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="6">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K21" s="6">
+      <c r="G21">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="K21">
         <f>_xlfn.XLOOKUP($B21,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.9</v>
       </c>
-      <c r="L21" s="6">
+      <c r="L21">
         <f>_xlfn.XLOOKUP($B21, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M21" s="6">
+      <c r="M21">
         <f>_xlfn.XLOOKUP($B21, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N21" s="6">
+      <c r="N21">
         <f>_xlfn.XLOOKUP($B21, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O21" s="6">
-        <f>$AC$5</f>
+      <c r="O21">
+        <f t="shared" si="16"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P21" s="6">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="6">
+      <c r="P21">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Q21">
         <f>_xlfn.XLOOKUP($B21,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.43</v>
       </c>
-      <c r="R21" s="6">
+      <c r="R21">
         <f>_xlfn.XLOOKUP($B21,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.1</v>
       </c>
-      <c r="S21" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T21" s="6">
-        <f>_xlfn.XLOOKUP(A21,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U21" s="6">
-        <f>_xlfn.XLOOKUP(A21,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V21" s="6">
-        <f t="shared" si="14"/>
+      <c r="S21">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W21" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X21" s="6"/>
-      <c r="Y21" s="6"/>
-      <c r="Z21" s="6"/>
+      <c r="W21">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A22" s="6" t="s">
+      <c r="A22" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6">
+      <c r="D22">
         <v>345</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22">
         <f>_xlfn.XLOOKUP(B22, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="F22" s="6">
-        <f t="shared" si="7"/>
+      <c r="F22">
+        <f t="shared" si="19"/>
         <v>48.300000000000004</v>
       </c>
-      <c r="G22" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H22" s="6">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="I22" s="6">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J22" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="6">
+      <c r="G22">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="K22">
         <f>_xlfn.XLOOKUP($B22,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.8</v>
       </c>
-      <c r="L22" s="6">
+      <c r="L22">
         <f>_xlfn.XLOOKUP($B22, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M22" s="6">
+      <c r="M22">
         <f>_xlfn.XLOOKUP($B22, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.2</v>
       </c>
-      <c r="N22" s="6">
+      <c r="N22">
         <f>_xlfn.XLOOKUP($B22, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O22" s="6">
-        <f>$AC$5</f>
+      <c r="O22">
+        <f t="shared" si="16"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P22" s="6">
-        <f t="shared" si="12"/>
+      <c r="P22">
+        <f t="shared" si="24"/>
         <v>10.059280000000001</v>
       </c>
-      <c r="Q22" s="6">
+      <c r="Q22">
         <f>_xlfn.XLOOKUP($B22,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.24</v>
       </c>
-      <c r="R22" s="6">
+      <c r="R22">
         <f>_xlfn.XLOOKUP($B22,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S22" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T22" s="6">
-        <f>_xlfn.XLOOKUP(A22,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U22" s="6">
-        <f>_xlfn.XLOOKUP(A22,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V22" s="6">
-        <f t="shared" si="14"/>
+      <c r="S22">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T22">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W22" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X22" s="6"/>
-      <c r="Y22" s="6"/>
-      <c r="Z22" s="6"/>
+      <c r="W22">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A23" s="6" t="s">
+      <c r="A23" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" t="s">
         <v>1</v>
       </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6">
+      <c r="D23">
         <v>4356</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23">
         <f>_xlfn.XLOOKUP(B23, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.72</v>
       </c>
-      <c r="F23" s="6">
-        <f t="shared" si="7"/>
+      <c r="F23">
+        <f t="shared" si="19"/>
         <v>3136.3199999999997</v>
       </c>
-      <c r="G23" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H23" s="6">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="I23" s="6">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="6">
+      <c r="G23">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="K23">
         <f>_xlfn.XLOOKUP($B23,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0</v>
       </c>
-      <c r="L23" s="6">
+      <c r="L23">
         <f>_xlfn.XLOOKUP($B23, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M23" s="6">
+      <c r="M23">
         <f>_xlfn.XLOOKUP($B23, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N23" s="6">
+      <c r="N23">
         <f>_xlfn.XLOOKUP($B23, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O23" s="6">
-        <f>$AC$5</f>
+      <c r="O23">
+        <f t="shared" si="16"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P23" s="6">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="6">
+      <c r="P23">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Q23">
         <f>_xlfn.XLOOKUP($B23,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.05</v>
       </c>
-      <c r="R23" s="6">
+      <c r="R23">
         <f>_xlfn.XLOOKUP($B23,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S23" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T23" s="6">
-        <f>_xlfn.XLOOKUP(A23,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U23" s="6">
-        <f>_xlfn.XLOOKUP(A23,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V23" s="6">
-        <f t="shared" si="14"/>
+      <c r="S23">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T23">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W23" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X23" s="6"/>
-      <c r="Y23" s="6"/>
-      <c r="Z23" s="6"/>
+      <c r="W23">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A24" s="6" t="s">
+      <c r="A24" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6">
+      <c r="D24">
         <v>324</v>
       </c>
-      <c r="E24" s="6">
+      <c r="E24">
         <f>_xlfn.XLOOKUP(B24, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.39</v>
       </c>
-      <c r="F24" s="6">
-        <f t="shared" si="7"/>
+      <c r="F24">
+        <f t="shared" si="19"/>
         <v>126.36</v>
       </c>
-      <c r="G24" s="6">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="H24" s="6">
+      <c r="G24">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H24">
         <f>G24*F24</f>
         <v>0</v>
       </c>
-      <c r="I24" s="6">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J24" s="6">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K24" s="6">
+      <c r="I24">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="K24">
         <f>_xlfn.XLOOKUP($B24,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L24" s="6">
+      <c r="L24">
         <f>_xlfn.XLOOKUP($B24, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.7</v>
       </c>
-      <c r="M24" s="6">
+      <c r="M24">
         <f>_xlfn.XLOOKUP($B24, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.1</v>
       </c>
-      <c r="N24" s="6">
+      <c r="N24">
         <f>_xlfn.XLOOKUP($B24, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O24" s="6">
-        <f>$AC$5</f>
+      <c r="O24">
+        <f t="shared" si="16"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P24" s="6">
-        <f t="shared" si="12"/>
+      <c r="P24">
+        <f t="shared" si="24"/>
         <v>9.2108015999999999</v>
       </c>
-      <c r="Q24" s="6">
+      <c r="Q24">
         <f>_xlfn.XLOOKUP($B24,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.24</v>
       </c>
-      <c r="R24" s="6">
+      <c r="R24">
         <f>_xlfn.XLOOKUP($B24,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S24" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T24" s="6">
-        <f>_xlfn.XLOOKUP(A24,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U24" s="6">
-        <f>_xlfn.XLOOKUP(A24,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V24" s="6">
-        <f t="shared" si="14"/>
+      <c r="S24">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T24">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W24" s="6">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="X24" s="6"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
+      <c r="W24">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A25" s="6" t="s">
+      <c r="A25" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25">
         <v>565</v>
       </c>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6">
+      <c r="E25">
         <f>_xlfn.XLOOKUP(B25, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="F25" s="6">
-        <f t="shared" ref="F25:F26" si="16">IF(C25&lt;&gt;"", C25,D25*E25)</f>
+      <c r="F25">
+        <f t="shared" ref="F25:F26" si="28">IF(C25&lt;&gt;"", C25,D25*E25)</f>
         <v>565</v>
       </c>
-      <c r="G25" s="6">
-        <f t="shared" ref="G25:G26" si="17">_xlfn.XLOOKUP(A25,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="6">
-        <f t="shared" ref="H25:H26" si="18">G25*F25</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="6">
-        <f t="shared" ref="I25:I26" si="19">_xlfn.XLOOKUP(A25,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="J25" s="6">
-        <f t="shared" ref="J25:J26" si="20">F25*I25</f>
-        <v>0</v>
-      </c>
-      <c r="K25" s="6">
+      <c r="G25">
+        <f t="shared" ref="G25:G26" si="29">_xlfn.XLOOKUP(A25,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <f t="shared" ref="H25:H26" si="30">G25*F25</f>
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <f t="shared" ref="I25:I26" si="31">_xlfn.XLOOKUP(A25,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <f t="shared" ref="J25:J26" si="32">F25*I25</f>
+        <v>0</v>
+      </c>
+      <c r="K25">
         <f>_xlfn.XLOOKUP($B25,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.84</v>
       </c>
-      <c r="L25" s="6">
+      <c r="L25">
         <f>_xlfn.XLOOKUP($B25, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.67</v>
       </c>
-      <c r="M25" s="6">
+      <c r="M25">
         <f>_xlfn.XLOOKUP($B25, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.2</v>
       </c>
-      <c r="N25" s="6">
+      <c r="N25">
         <f>_xlfn.XLOOKUP($B25, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O25" s="6">
-        <f t="shared" ref="O25:O26" si="21">$AC$5</f>
+      <c r="O25">
+        <f t="shared" ref="O25:O26" si="33">$AC$5</f>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P25" s="6">
+      <c r="P25">
         <f>IF(A25&lt;&gt;"Incineration", 0, F25*K25*L25*M25*N25*O25)</f>
         <v>165.56262799999996</v>
       </c>
-      <c r="Q25" s="6">
+      <c r="Q25">
         <f>_xlfn.XLOOKUP($B25,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.39</v>
       </c>
-      <c r="R25" s="6">
+      <c r="R25">
         <f>_xlfn.XLOOKUP($B25,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S25" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T25" s="6">
-        <f>_xlfn.XLOOKUP(A25,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U25" s="6">
-        <f>_xlfn.XLOOKUP(A25,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V25" s="6">
-        <f t="shared" si="14"/>
+      <c r="S25">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T25">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W25" s="6">
-        <f t="shared" ref="W25:W26" si="22">F25*Q25*R25*S25*T25*V25*(1-U25)</f>
-        <v>0</v>
-      </c>
-      <c r="X25" s="6"/>
-      <c r="Y25" s="6"/>
-      <c r="Z25" s="6"/>
+      <c r="W25">
+        <f t="shared" ref="W25:W26" si="34">F25*Q25*R25*S25*T25*V25*(1-U25)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="4">
-        <v>0</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4">
+      <c r="C26" s="3">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3">
         <f>_xlfn.XLOOKUP(B26, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.42</v>
       </c>
-      <c r="F26" s="4">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="G26" s="4">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="H26" s="4">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="4">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="4">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="4">
+      <c r="F26" s="3">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
         <f>_xlfn.XLOOKUP($B26,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.9</v>
       </c>
-      <c r="L26" s="4">
+      <c r="L26" s="3">
         <f>_xlfn.XLOOKUP($B26, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.03</v>
       </c>
-      <c r="M26" s="4">
+      <c r="M26" s="3">
         <f>_xlfn.XLOOKUP($B26, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>1</v>
       </c>
-      <c r="N26" s="4">
+      <c r="N26" s="3">
         <f>_xlfn.XLOOKUP($B26, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O26" s="4">
-        <f t="shared" si="21"/>
+      <c r="O26" s="3">
+        <f t="shared" si="33"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P26" s="4">
-        <f t="shared" ref="P25:P26" si="23">IF(A26&lt;&gt;"Incineration", 0, F26*K26*L26*M26*N26*O26)</f>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="4">
+      <c r="P26" s="3">
+        <f t="shared" ref="P26" si="35">IF(A26&lt;&gt;"Incineration", 0, F26*K26*L26*M26*N26*O26)</f>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
         <f>_xlfn.XLOOKUP($B26,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0</v>
       </c>
-      <c r="R26" s="4">
+      <c r="R26" s="3">
         <f>_xlfn.XLOOKUP($B26,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0</v>
       </c>
-      <c r="S26" s="4">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T26" s="4">
-        <f>_xlfn.XLOOKUP(A26,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U26" s="4">
-        <f>_xlfn.XLOOKUP(A26,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V26" s="4">
-        <f t="shared" si="14"/>
+      <c r="S26" s="3">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T26" s="3">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="3">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W26" s="4">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="X26" s="4"/>
-      <c r="Y26" s="4"/>
-      <c r="Z26" s="4"/>
+      <c r="W26" s="3">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="X26" s="3"/>
+      <c r="Y26" s="3"/>
+      <c r="Z26" s="3"/>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27">
         <v>1234</v>
       </c>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6">
+      <c r="E27">
         <f>_xlfn.XLOOKUP(B27, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.5</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27">
         <f>IF(C27&lt;&gt;"", C27,D27*E27)</f>
         <v>1234</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G27">
         <f>_xlfn.XLOOKUP(A27,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
         <v>0</v>
       </c>
-      <c r="H27" s="6">
+      <c r="H27">
         <f>G27*F27</f>
         <v>0</v>
       </c>
-      <c r="I27" s="6">
+      <c r="I27">
         <f>_xlfn.XLOOKUP(A27,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
         <v>0</v>
       </c>
-      <c r="J27" s="6">
+      <c r="J27">
         <f>F27*I27</f>
         <v>0</v>
       </c>
-      <c r="K27" s="6">
+      <c r="K27">
         <f>_xlfn.XLOOKUP($B27,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L27" s="6">
+      <c r="L27">
         <f>_xlfn.XLOOKUP($B27, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.38</v>
       </c>
-      <c r="M27" s="6">
+      <c r="M27">
         <f>_xlfn.XLOOKUP($B27, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N27" s="6">
+      <c r="N27">
         <f>_xlfn.XLOOKUP($B27, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O27" s="6">
-        <f>$AC$5</f>
+      <c r="O27">
+        <f t="shared" ref="O27:O34" si="36">$AC$5</f>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P27" s="6">
+      <c r="P27">
         <f>IF(A27&lt;&gt;"Incineration", 0, F27*K27*L27*M27*N27*O27)</f>
         <v>0</v>
       </c>
-      <c r="Q27" s="6">
+      <c r="Q27">
         <f>_xlfn.XLOOKUP($B27,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.15</v>
       </c>
-      <c r="R27" s="6">
+      <c r="R27">
         <f>_xlfn.XLOOKUP($B27,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.84</v>
       </c>
-      <c r="S27" s="6">
+      <c r="S27">
         <f>$AC$7</f>
         <v>0.5</v>
       </c>
-      <c r="T27" s="6">
-        <f>_xlfn.XLOOKUP(A27,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="T27">
+        <f t="shared" si="17"/>
         <v>0.8</v>
       </c>
-      <c r="U27" s="6">
-        <f>_xlfn.XLOOKUP(A27,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V27" s="6">
+      <c r="U27">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V27">
         <f>$AC$6</f>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W27" s="6">
+      <c r="W27">
         <f>F27*Q27*R27*S27*T27*V27*(1-U27)</f>
         <v>82.924799999999991</v>
       </c>
-      <c r="X27" s="6">
+      <c r="X27">
         <f>SUM(P27:P36)</f>
         <v>0</v>
       </c>
-      <c r="Y27" s="6">
+      <c r="Y27">
         <f>SUM(H27:H36,W27:W36)</f>
         <v>231.21257333333332</v>
       </c>
-      <c r="Z27" s="6">
+      <c r="Z27">
         <f>SUM(J27:J36)</f>
         <v>0</v>
       </c>
@@ -2693,2658 +2657,2560 @@
       <c r="A28" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28">
         <v>342</v>
       </c>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6">
+      <c r="E28">
         <f>_xlfn.XLOOKUP(B28, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.09</v>
       </c>
-      <c r="F28" s="6">
-        <f t="shared" ref="F28:F36" si="24">IF(C28&lt;&gt;"", C28,D28*E28)</f>
+      <c r="F28">
+        <f t="shared" ref="F28:F36" si="37">IF(C28&lt;&gt;"", C28,D28*E28)</f>
         <v>342</v>
       </c>
-      <c r="G28" s="6">
-        <f t="shared" ref="G28:G36" si="25">_xlfn.XLOOKUP(A28,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="H28" s="6">
-        <f t="shared" ref="H28:H33" si="26">G28*F28</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="6">
-        <f t="shared" ref="I28:I36" si="27">_xlfn.XLOOKUP(A28,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="J28" s="6">
-        <f t="shared" ref="J28:J36" si="28">F28*I28</f>
-        <v>0</v>
-      </c>
-      <c r="K28" s="6">
+      <c r="G28">
+        <f t="shared" ref="G28:G36" si="38">_xlfn.XLOOKUP(A28,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <f t="shared" ref="H28:H33" si="39">G28*F28</f>
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <f t="shared" ref="I28:I36" si="40">_xlfn.XLOOKUP(A28,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <f t="shared" ref="J28:J36" si="41">F28*I28</f>
+        <v>0</v>
+      </c>
+      <c r="K28">
         <f>_xlfn.XLOOKUP($B28,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.9</v>
       </c>
-      <c r="L28" s="6">
+      <c r="L28">
         <f>_xlfn.XLOOKUP($B28, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.46</v>
       </c>
-      <c r="M28" s="6">
+      <c r="M28">
         <f>_xlfn.XLOOKUP($B28, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.01</v>
       </c>
-      <c r="N28" s="6">
+      <c r="N28">
         <f>_xlfn.XLOOKUP($B28, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O28" s="6">
-        <f>$AC$5</f>
+      <c r="O28">
+        <f t="shared" si="36"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P28" s="6">
-        <f t="shared" ref="P28:P36" si="29">IF(A28&lt;&gt;"Incineration", 0, F28*K28*L28*M28*N28*O28)</f>
-        <v>0</v>
-      </c>
-      <c r="Q28" s="6">
+      <c r="P28">
+        <f t="shared" ref="P28:P36" si="42">IF(A28&lt;&gt;"Incineration", 0, F28*K28*L28*M28*N28*O28)</f>
+        <v>0</v>
+      </c>
+      <c r="Q28">
         <f>_xlfn.XLOOKUP($B28,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.4</v>
       </c>
-      <c r="R28" s="6">
+      <c r="R28">
         <f>_xlfn.XLOOKUP($B28,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.49</v>
       </c>
-      <c r="S28" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T28" s="6">
-        <f>_xlfn.XLOOKUP(A28,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S28">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T28">
+        <f t="shared" si="17"/>
         <v>0.4</v>
       </c>
-      <c r="U28" s="6">
-        <f>_xlfn.XLOOKUP(A28,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V28" s="6">
-        <f t="shared" si="14"/>
+      <c r="U28">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W28" s="6">
-        <f t="shared" ref="W28:W36" si="30">F28*Q28*R28*S28*T28*V28*(1-U28)</f>
+      <c r="W28">
+        <f t="shared" ref="W28:W36" si="43">F28*Q28*R28*S28*T28*V28*(1-U28)</f>
         <v>17.875200000000003</v>
       </c>
-      <c r="X28" s="6"/>
-      <c r="Y28" s="6"/>
-      <c r="Z28" s="6"/>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" t="s">
         <v>4</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29">
         <v>346</v>
       </c>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6">
+      <c r="E29">
         <f>_xlfn.XLOOKUP(B29, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.24</v>
       </c>
-      <c r="F29" s="6">
-        <f t="shared" si="24"/>
+      <c r="F29">
+        <f t="shared" si="37"/>
         <v>346</v>
       </c>
-      <c r="G29" s="6">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="H29" s="6">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="I29" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="J29" s="6">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="K29" s="6">
+      <c r="G29">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="K29">
         <f>_xlfn.XLOOKUP($B29,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L29" s="6">
+      <c r="L29">
         <f>_xlfn.XLOOKUP($B29, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.49</v>
       </c>
-      <c r="M29" s="6">
+      <c r="M29">
         <f>_xlfn.XLOOKUP($B29, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N29" s="6">
+      <c r="N29">
         <f>_xlfn.XLOOKUP($B29, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O29" s="6">
-        <f>$AC$5</f>
+      <c r="O29">
+        <f t="shared" si="36"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P29" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="Q29" s="6">
+      <c r="P29">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="Q29">
         <f>_xlfn.XLOOKUP($B29,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.2</v>
       </c>
-      <c r="R29" s="6">
+      <c r="R29">
         <f>_xlfn.XLOOKUP($B29,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.47</v>
       </c>
-      <c r="S29" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T29" s="6">
-        <f>_xlfn.XLOOKUP(A29,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S29">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T29">
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
-      <c r="U29" s="6">
-        <f>_xlfn.XLOOKUP(A29,$X$9:$X$11,AA$9:AA$11, 0)</f>
+      <c r="U29">
+        <f t="shared" si="18"/>
         <v>0.1</v>
       </c>
-      <c r="V29" s="6">
-        <f t="shared" si="14"/>
+      <c r="V29">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W29" s="6">
-        <f t="shared" si="30"/>
+      <c r="W29">
+        <f t="shared" si="43"/>
         <v>13.660080000000001</v>
       </c>
-      <c r="X29" s="6"/>
-      <c r="Y29" s="6"/>
-      <c r="Z29" s="6"/>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" t="s">
         <v>45</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30">
         <v>1435</v>
       </c>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6">
+      <c r="E30">
         <f>_xlfn.XLOOKUP(B30, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.15</v>
       </c>
-      <c r="F30" s="6">
-        <f t="shared" si="24"/>
+      <c r="F30">
+        <f t="shared" si="37"/>
         <v>1435</v>
       </c>
-      <c r="G30" s="6">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="H30" s="6">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="I30" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="J30" s="6">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="K30" s="6">
+      <c r="G30">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="K30">
         <f>_xlfn.XLOOKUP($B30,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L30" s="6">
+      <c r="L30">
         <f>_xlfn.XLOOKUP($B30, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M30" s="6">
+      <c r="M30">
         <f>_xlfn.XLOOKUP($B30, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N30" s="6">
+      <c r="N30">
         <f>_xlfn.XLOOKUP($B30, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O30" s="6">
-        <f>$AC$5</f>
+      <c r="O30">
+        <f t="shared" si="36"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P30" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="Q30" s="6">
+      <c r="P30">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="Q30">
         <f>_xlfn.XLOOKUP($B30,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.43</v>
       </c>
-      <c r="R30" s="6">
+      <c r="R30">
         <f>_xlfn.XLOOKUP($B30,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.1</v>
       </c>
-      <c r="S30" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T30" s="6">
-        <f>_xlfn.XLOOKUP(A30,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S30">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T30">
+        <f t="shared" si="17"/>
         <v>0.8</v>
       </c>
-      <c r="U30" s="6">
-        <f>_xlfn.XLOOKUP(A30,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V30" s="6">
-        <f t="shared" si="14"/>
+      <c r="U30">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W30" s="6">
-        <f t="shared" si="30"/>
+      <c r="W30">
+        <f t="shared" si="43"/>
         <v>32.909333333333336</v>
       </c>
-      <c r="X30" s="6"/>
-      <c r="Y30" s="6"/>
-      <c r="Z30" s="6"/>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" t="s">
         <v>46</v>
       </c>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6">
+      <c r="D31">
         <v>1235</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31">
         <f>_xlfn.XLOOKUP(B31, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.15</v>
       </c>
-      <c r="F31" s="6">
-        <f t="shared" si="24"/>
+      <c r="F31">
+        <f t="shared" si="37"/>
         <v>185.25</v>
       </c>
-      <c r="G31" s="6">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="H31" s="6">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="I31" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="J31" s="6">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="K31" s="6">
+      <c r="G31">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="K31">
         <f>_xlfn.XLOOKUP($B31,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.9</v>
       </c>
-      <c r="L31" s="6">
+      <c r="L31">
         <f>_xlfn.XLOOKUP($B31, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M31" s="6">
+      <c r="M31">
         <f>_xlfn.XLOOKUP($B31, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N31" s="6">
+      <c r="N31">
         <f>_xlfn.XLOOKUP($B31, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O31" s="6">
-        <f>$AC$5</f>
+      <c r="O31">
+        <f t="shared" si="36"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P31" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="6">
+      <c r="P31">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="Q31">
         <f>_xlfn.XLOOKUP($B31,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.43</v>
       </c>
-      <c r="R31" s="6">
+      <c r="R31">
         <f>_xlfn.XLOOKUP($B31,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.1</v>
       </c>
-      <c r="S31" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T31" s="6">
-        <f>_xlfn.XLOOKUP(A31,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S31">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T31">
+        <f t="shared" si="17"/>
         <v>0.4</v>
       </c>
-      <c r="U31" s="6">
-        <f>_xlfn.XLOOKUP(A31,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V31" s="6">
-        <f t="shared" si="14"/>
+      <c r="U31">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W31" s="6">
-        <f t="shared" si="30"/>
+      <c r="W31">
+        <f t="shared" si="43"/>
         <v>2.1242000000000001</v>
       </c>
-      <c r="X31" s="6"/>
-      <c r="Y31" s="6"/>
-      <c r="Z31" s="6"/>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6">
+      <c r="D32">
         <v>345</v>
       </c>
-      <c r="E32" s="6">
+      <c r="E32">
         <f>_xlfn.XLOOKUP(B32, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="F32" s="6">
-        <f t="shared" si="24"/>
+      <c r="F32">
+        <f t="shared" si="37"/>
         <v>48.300000000000004</v>
       </c>
-      <c r="G32" s="6">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="H32" s="6">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="I32" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="J32" s="6">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="K32" s="6">
+      <c r="G32">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="K32">
         <f>_xlfn.XLOOKUP($B32,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.8</v>
       </c>
-      <c r="L32" s="6">
+      <c r="L32">
         <f>_xlfn.XLOOKUP($B32, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M32" s="6">
+      <c r="M32">
         <f>_xlfn.XLOOKUP($B32, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.2</v>
       </c>
-      <c r="N32" s="6">
+      <c r="N32">
         <f>_xlfn.XLOOKUP($B32, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O32" s="6">
-        <f>$AC$5</f>
+      <c r="O32">
+        <f t="shared" si="36"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P32" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="Q32" s="6">
+      <c r="P32">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="Q32">
         <f>_xlfn.XLOOKUP($B32,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.24</v>
       </c>
-      <c r="R32" s="6">
+      <c r="R32">
         <f>_xlfn.XLOOKUP($B32,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S32" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T32" s="6">
-        <f>_xlfn.XLOOKUP(A32,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S32">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T32">
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
-      <c r="U32" s="6">
-        <f>_xlfn.XLOOKUP(A32,$X$9:$X$11,AA$9:AA$11, 0)</f>
+      <c r="U32">
+        <f t="shared" si="18"/>
         <v>0.1</v>
       </c>
-      <c r="V32" s="6">
-        <f t="shared" si="14"/>
+      <c r="V32">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W32" s="6">
-        <f t="shared" si="30"/>
+      <c r="W32">
+        <f t="shared" si="43"/>
         <v>2.4343199999999996</v>
       </c>
-      <c r="X32" s="6"/>
-      <c r="Y32" s="6"/>
-      <c r="Z32" s="6"/>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" t="s">
         <v>1</v>
       </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6">
+      <c r="D33">
         <v>4356</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E33">
         <f>_xlfn.XLOOKUP(B33, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.72</v>
       </c>
-      <c r="F33" s="6">
-        <f t="shared" si="24"/>
+      <c r="F33">
+        <f t="shared" si="37"/>
         <v>3136.3199999999997</v>
       </c>
-      <c r="G33" s="6">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="H33" s="6">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="I33" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="J33" s="6">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="K33" s="6">
+      <c r="G33">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="K33">
         <f>_xlfn.XLOOKUP($B33,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0</v>
       </c>
-      <c r="L33" s="6">
+      <c r="L33">
         <f>_xlfn.XLOOKUP($B33, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M33" s="6">
+      <c r="M33">
         <f>_xlfn.XLOOKUP($B33, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N33" s="6">
+      <c r="N33">
         <f>_xlfn.XLOOKUP($B33, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O33" s="6">
-        <f>$AC$5</f>
+      <c r="O33">
+        <f t="shared" si="36"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P33" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="Q33" s="6">
+      <c r="P33">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="Q33">
         <f>_xlfn.XLOOKUP($B33,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.05</v>
       </c>
-      <c r="R33" s="6">
+      <c r="R33">
         <f>_xlfn.XLOOKUP($B33,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S33" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T33" s="6">
-        <f>_xlfn.XLOOKUP(A33,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S33">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T33">
+        <f t="shared" si="17"/>
         <v>0.8</v>
       </c>
-      <c r="U33" s="6">
-        <f>_xlfn.XLOOKUP(A33,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V33" s="6">
-        <f t="shared" si="14"/>
+      <c r="U33">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W33" s="6">
-        <f t="shared" si="30"/>
+      <c r="W33">
+        <f t="shared" si="43"/>
         <v>41.817599999999999</v>
       </c>
-      <c r="X33" s="6"/>
-      <c r="Y33" s="6"/>
-      <c r="Z33" s="6"/>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" t="s">
         <v>54</v>
       </c>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6">
+      <c r="D34">
         <v>324</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E34">
         <f>_xlfn.XLOOKUP(B34, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.39</v>
       </c>
-      <c r="F34" s="6">
-        <f t="shared" si="24"/>
+      <c r="F34">
+        <f t="shared" si="37"/>
         <v>126.36</v>
       </c>
-      <c r="G34" s="6">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="H34" s="6">
+      <c r="G34">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="H34">
         <f>G34*F34</f>
         <v>0</v>
       </c>
-      <c r="I34" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="J34" s="6">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="K34" s="6">
+      <c r="I34">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="K34">
         <f>_xlfn.XLOOKUP($B34,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L34" s="6">
+      <c r="L34">
         <f>_xlfn.XLOOKUP($B34, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.7</v>
       </c>
-      <c r="M34" s="6">
+      <c r="M34">
         <f>_xlfn.XLOOKUP($B34, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.1</v>
       </c>
-      <c r="N34" s="6">
+      <c r="N34">
         <f>_xlfn.XLOOKUP($B34, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O34" s="6">
-        <f>$AC$5</f>
+      <c r="O34">
+        <f t="shared" si="36"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P34" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="Q34" s="6">
+      <c r="P34">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="Q34">
         <f>_xlfn.XLOOKUP($B34,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.24</v>
       </c>
-      <c r="R34" s="6">
+      <c r="R34">
         <f>_xlfn.XLOOKUP($B34,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S34" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T34" s="6">
-        <f>_xlfn.XLOOKUP(A34,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S34">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T34">
+        <f t="shared" si="17"/>
         <v>0.8</v>
       </c>
-      <c r="U34" s="6">
-        <f>_xlfn.XLOOKUP(A34,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V34" s="6">
-        <f t="shared" si="14"/>
+      <c r="U34">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W34" s="6">
-        <f t="shared" si="30"/>
+      <c r="W34">
+        <f t="shared" si="43"/>
         <v>8.08704</v>
       </c>
-      <c r="X34" s="6"/>
-      <c r="Y34" s="6"/>
-      <c r="Z34" s="6"/>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" t="s">
         <v>8</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35">
         <v>565</v>
       </c>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6">
+      <c r="E35">
         <f>_xlfn.XLOOKUP(B35, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="F35" s="6">
-        <f t="shared" si="24"/>
+      <c r="F35">
+        <f t="shared" si="37"/>
         <v>565</v>
       </c>
-      <c r="G35" s="6">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="H35" s="6">
-        <f t="shared" ref="H35:H36" si="31">G35*F35</f>
-        <v>0</v>
-      </c>
-      <c r="I35" s="6">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="J35" s="6">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="K35" s="6">
+      <c r="G35">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <f t="shared" ref="H35:H36" si="44">G35*F35</f>
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="K35">
         <f>_xlfn.XLOOKUP($B35,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.84</v>
       </c>
-      <c r="L35" s="6">
+      <c r="L35">
         <f>_xlfn.XLOOKUP($B35, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.67</v>
       </c>
-      <c r="M35" s="6">
+      <c r="M35">
         <f>_xlfn.XLOOKUP($B35, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.2</v>
       </c>
-      <c r="N35" s="6">
+      <c r="N35">
         <f>_xlfn.XLOOKUP($B35, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O35" s="6">
-        <f t="shared" ref="O35:O36" si="32">$AC$5</f>
+      <c r="O35">
+        <f t="shared" ref="O35:O36" si="45">$AC$5</f>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P35" s="6">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="Q35" s="6">
+      <c r="P35">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="Q35">
         <f>_xlfn.XLOOKUP($B35,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.39</v>
       </c>
-      <c r="R35" s="6">
+      <c r="R35">
         <f>_xlfn.XLOOKUP($B35,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S35" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T35" s="6">
-        <f>_xlfn.XLOOKUP(A35,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S35">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T35">
+        <f t="shared" si="17"/>
         <v>0.4</v>
       </c>
-      <c r="U35" s="6">
-        <f>_xlfn.XLOOKUP(A35,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V35" s="6">
-        <f t="shared" si="14"/>
+      <c r="U35">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W35" s="6">
-        <f t="shared" si="30"/>
+      <c r="W35">
+        <f t="shared" si="43"/>
         <v>29.38</v>
       </c>
-      <c r="X35" s="6"/>
-      <c r="Y35" s="6"/>
-      <c r="Z35" s="6"/>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="3">
         <v>7643</v>
       </c>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4">
+      <c r="D36" s="3"/>
+      <c r="E36" s="3">
         <f>_xlfn.XLOOKUP(B36, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.42</v>
       </c>
-      <c r="F36" s="4">
-        <f t="shared" si="24"/>
+      <c r="F36" s="3">
+        <f t="shared" si="37"/>
         <v>7643</v>
       </c>
-      <c r="G36" s="4">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="H36" s="4">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="I36" s="4">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="J36" s="4">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="K36" s="4">
+      <c r="G36" s="3">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="3">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="3">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="3">
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="3">
         <f>_xlfn.XLOOKUP($B36,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.9</v>
       </c>
-      <c r="L36" s="4">
+      <c r="L36" s="3">
         <f>_xlfn.XLOOKUP($B36, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.03</v>
       </c>
-      <c r="M36" s="4">
+      <c r="M36" s="3">
         <f>_xlfn.XLOOKUP($B36, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>1</v>
       </c>
-      <c r="N36" s="4">
+      <c r="N36" s="3">
         <f>_xlfn.XLOOKUP($B36, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O36" s="4">
-        <f t="shared" si="32"/>
+      <c r="O36" s="3">
+        <f t="shared" si="45"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P36" s="4">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="Q36" s="4">
+      <c r="P36" s="3">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="3">
         <f>_xlfn.XLOOKUP($B36,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0</v>
       </c>
-      <c r="R36" s="4">
+      <c r="R36" s="3">
         <f>_xlfn.XLOOKUP($B36,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0</v>
       </c>
-      <c r="S36" s="4">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T36" s="4">
-        <f>_xlfn.XLOOKUP(A36,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S36" s="3">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T36" s="3">
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
-      <c r="U36" s="4">
-        <f>_xlfn.XLOOKUP(A36,$X$9:$X$11,AA$9:AA$11, 0)</f>
+      <c r="U36" s="3">
+        <f t="shared" si="18"/>
         <v>0.1</v>
       </c>
-      <c r="V36" s="4">
-        <f t="shared" si="14"/>
+      <c r="V36" s="3">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W36" s="4">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="X36" s="4"/>
-      <c r="Y36" s="4"/>
-      <c r="Z36" s="4"/>
+      <c r="W36" s="3">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="3"/>
+      <c r="Y36" s="3"/>
+      <c r="Z36" s="3"/>
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A37" s="6" t="s">
+      <c r="A37" t="s">
         <v>5</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" t="s">
         <v>3</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37">
         <v>1234</v>
       </c>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6">
+      <c r="E37">
         <f>_xlfn.XLOOKUP(B37, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.5</v>
       </c>
-      <c r="F37" s="6">
+      <c r="F37">
         <f>IF(C37&lt;&gt;"", C37,D37*E37)</f>
         <v>1234</v>
       </c>
-      <c r="G37" s="6">
+      <c r="G37">
         <f>_xlfn.XLOOKUP(A37,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
         <v>7.5000000000000002E-4</v>
       </c>
-      <c r="H37" s="6">
+      <c r="H37">
         <f>G37*F37</f>
         <v>0.92549999999999999</v>
       </c>
-      <c r="I37" s="6">
+      <c r="I37">
         <f>_xlfn.XLOOKUP(A37,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
         <v>9.4300000000000002E-5</v>
       </c>
-      <c r="J37" s="6">
+      <c r="J37">
         <f>F37*I37</f>
         <v>0.1163662</v>
       </c>
-      <c r="K37" s="6">
+      <c r="K37">
         <f>_xlfn.XLOOKUP($B37,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L37" s="6">
+      <c r="L37">
         <f>_xlfn.XLOOKUP($B37, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.38</v>
       </c>
-      <c r="M37" s="6">
+      <c r="M37">
         <f>_xlfn.XLOOKUP($B37, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N37" s="6">
+      <c r="N37">
         <f>_xlfn.XLOOKUP($B37, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O37" s="6">
-        <f>$AC$5</f>
+      <c r="O37">
+        <f t="shared" ref="O37:O44" si="46">$AC$5</f>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P37" s="6">
+      <c r="P37">
         <f>IF(A37&lt;&gt;"Incineration", 0, F37*K37*L37*M37*N37*O37)</f>
         <v>0</v>
       </c>
-      <c r="Q37" s="6">
+      <c r="Q37">
         <f>_xlfn.XLOOKUP($B37,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.15</v>
       </c>
-      <c r="R37" s="6">
+      <c r="R37">
         <f>_xlfn.XLOOKUP($B37,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.84</v>
       </c>
-      <c r="S37" s="6">
+      <c r="S37">
         <f>$AC$7</f>
         <v>0.5</v>
       </c>
-      <c r="T37" s="6">
-        <f>_xlfn.XLOOKUP(A37,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U37" s="6">
-        <f>_xlfn.XLOOKUP(A37,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V37" s="6">
+      <c r="T37">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V37">
         <f>$AC$6</f>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W37" s="6">
+      <c r="W37">
         <f>F37*Q37*R37*S37*T37*V37*(1-U37)</f>
         <v>0</v>
       </c>
-      <c r="X37" s="6">
+      <c r="X37">
         <f>SUM(P37:P46)</f>
         <v>547.28574999999978</v>
       </c>
-      <c r="Y37" s="6">
+      <c r="Y37">
         <f>SUM(H37:H46,W37:W46)</f>
-        <v>108.46994266666667</v>
-      </c>
-      <c r="Z37" s="6">
+        <v>111.29263066666667</v>
+      </c>
+      <c r="Z37">
         <f>SUM(J37:J46)</f>
         <v>0.14899400000000002</v>
       </c>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A38" s="6" t="s">
+      <c r="A38" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38">
         <v>342</v>
       </c>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6">
+      <c r="E38">
         <f>_xlfn.XLOOKUP(B38, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.09</v>
       </c>
-      <c r="F38" s="6">
-        <f t="shared" ref="F38:F46" si="33">IF(C38&lt;&gt;"", C38,D38*E38)</f>
+      <c r="F38">
+        <f t="shared" ref="F38:F46" si="47">IF(C38&lt;&gt;"", C38,D38*E38)</f>
         <v>342</v>
       </c>
-      <c r="G38" s="6">
-        <f t="shared" ref="G38:G46" si="34">_xlfn.XLOOKUP(A38,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="H38" s="6">
-        <f t="shared" ref="H38:H43" si="35">G38*F38</f>
-        <v>0</v>
-      </c>
-      <c r="I38" s="6">
-        <f t="shared" ref="I38:I46" si="36">_xlfn.XLOOKUP(A38,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="J38" s="6">
-        <f t="shared" ref="J38:J46" si="37">F38*I38</f>
-        <v>0</v>
-      </c>
-      <c r="K38" s="6">
+      <c r="G38">
+        <f t="shared" ref="G38:G46" si="48">_xlfn.XLOOKUP(A38,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <f t="shared" ref="H38:H43" si="49">G38*F38</f>
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <f t="shared" ref="I38:I46" si="50">_xlfn.XLOOKUP(A38,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <f t="shared" ref="J38:J46" si="51">F38*I38</f>
+        <v>0</v>
+      </c>
+      <c r="K38">
         <f>_xlfn.XLOOKUP($B38,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.9</v>
       </c>
-      <c r="L38" s="6">
+      <c r="L38">
         <f>_xlfn.XLOOKUP($B38, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.46</v>
       </c>
-      <c r="M38" s="6">
+      <c r="M38">
         <f>_xlfn.XLOOKUP($B38, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.01</v>
       </c>
-      <c r="N38" s="6">
+      <c r="N38">
         <f>_xlfn.XLOOKUP($B38, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O38" s="6">
-        <f>$AC$5</f>
+      <c r="O38">
+        <f t="shared" si="46"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P38" s="6">
-        <f t="shared" ref="P38:P46" si="38">IF(A38&lt;&gt;"Incineration", 0, F38*K38*L38*M38*N38*O38)</f>
-        <v>0</v>
-      </c>
-      <c r="Q38" s="6">
+      <c r="P38">
+        <f t="shared" ref="P38:P46" si="52">IF(A38&lt;&gt;"Incineration", 0, F38*K38*L38*M38*N38*O38)</f>
+        <v>0</v>
+      </c>
+      <c r="Q38">
         <f>_xlfn.XLOOKUP($B38,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.4</v>
       </c>
-      <c r="R38" s="6">
+      <c r="R38">
         <f>_xlfn.XLOOKUP($B38,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.49</v>
       </c>
-      <c r="S38" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T38" s="6">
-        <f>_xlfn.XLOOKUP(A38,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S38">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T38">
+        <f t="shared" si="17"/>
         <v>0.8</v>
       </c>
-      <c r="U38" s="6">
-        <f>_xlfn.XLOOKUP(A38,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V38" s="6">
-        <f t="shared" si="14"/>
+      <c r="U38">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W38" s="6">
-        <f t="shared" ref="W38:W46" si="39">F38*Q38*R38*S38*T38*V38*(1-U38)</f>
+      <c r="W38">
+        <f t="shared" ref="W38:W46" si="53">F38*Q38*R38*S38*T38*V38*(1-U38)</f>
         <v>35.750400000000006</v>
       </c>
-      <c r="X38" s="6"/>
-      <c r="Y38" s="6"/>
-      <c r="Z38" s="6"/>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A39" s="6" t="s">
+      <c r="A39" t="s">
         <v>5</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" t="s">
         <v>4</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39">
         <v>346</v>
       </c>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6">
+      <c r="E39">
         <f>_xlfn.XLOOKUP(B39, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.24</v>
       </c>
-      <c r="F39" s="6">
-        <f t="shared" si="33"/>
+      <c r="F39">
+        <f t="shared" si="47"/>
         <v>346</v>
       </c>
-      <c r="G39" s="6">
-        <f t="shared" si="34"/>
+      <c r="G39">
+        <f t="shared" si="48"/>
         <v>7.5000000000000002E-4</v>
       </c>
-      <c r="H39" s="6">
-        <f t="shared" si="35"/>
+      <c r="H39">
+        <f t="shared" si="49"/>
         <v>0.25950000000000001</v>
       </c>
-      <c r="I39" s="6">
-        <f t="shared" si="36"/>
+      <c r="I39">
+        <f t="shared" si="50"/>
         <v>9.4300000000000002E-5</v>
       </c>
-      <c r="J39" s="6">
-        <f t="shared" si="37"/>
+      <c r="J39">
+        <f t="shared" si="51"/>
         <v>3.2627799999999998E-2</v>
       </c>
-      <c r="K39" s="6">
+      <c r="K39">
         <f>_xlfn.XLOOKUP($B39,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L39" s="6">
+      <c r="L39">
         <f>_xlfn.XLOOKUP($B39, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.49</v>
       </c>
-      <c r="M39" s="6">
+      <c r="M39">
         <f>_xlfn.XLOOKUP($B39, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N39" s="6">
+      <c r="N39">
         <f>_xlfn.XLOOKUP($B39, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O39" s="6">
-        <f>$AC$5</f>
+      <c r="O39">
+        <f t="shared" si="46"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P39" s="6">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="Q39" s="6">
+      <c r="P39">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="Q39">
         <f>_xlfn.XLOOKUP($B39,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.2</v>
       </c>
-      <c r="R39" s="6">
+      <c r="R39">
         <f>_xlfn.XLOOKUP($B39,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.47</v>
       </c>
-      <c r="S39" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T39" s="6">
-        <f>_xlfn.XLOOKUP(A39,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U39" s="6">
-        <f>_xlfn.XLOOKUP(A39,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V39" s="6">
-        <f t="shared" si="14"/>
+      <c r="S39">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T39">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W39" s="6">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="X39" s="6"/>
-      <c r="Y39" s="6"/>
-      <c r="Z39" s="6"/>
+      <c r="W39">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A40" s="6" t="s">
+      <c r="A40" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40">
         <v>1435</v>
       </c>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6">
+      <c r="E40">
         <f>_xlfn.XLOOKUP(B40, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.15</v>
       </c>
-      <c r="F40" s="6">
-        <f t="shared" si="33"/>
+      <c r="F40">
+        <f t="shared" si="47"/>
         <v>1435</v>
       </c>
-      <c r="G40" s="6">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="H40" s="6">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="I40" s="6">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="J40" s="6">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="K40" s="6">
+      <c r="G40">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K40">
         <f>_xlfn.XLOOKUP($B40,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L40" s="6">
+      <c r="L40">
         <f>_xlfn.XLOOKUP($B40, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M40" s="6">
+      <c r="M40">
         <f>_xlfn.XLOOKUP($B40, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N40" s="6">
+      <c r="N40">
         <f>_xlfn.XLOOKUP($B40, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O40" s="6">
-        <f>$AC$5</f>
+      <c r="O40">
+        <f t="shared" si="46"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P40" s="6">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="Q40" s="6">
+      <c r="P40">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="Q40">
         <f>_xlfn.XLOOKUP($B40,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.43</v>
       </c>
-      <c r="R40" s="6">
+      <c r="R40">
         <f>_xlfn.XLOOKUP($B40,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.1</v>
       </c>
-      <c r="S40" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T40" s="6">
-        <f>_xlfn.XLOOKUP(A40,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S40">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T40">
+        <f t="shared" si="17"/>
         <v>0.4</v>
       </c>
-      <c r="U40" s="6">
-        <f>_xlfn.XLOOKUP(A40,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V40" s="6">
-        <f t="shared" si="14"/>
+      <c r="U40">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W40" s="6">
-        <f t="shared" si="39"/>
+      <c r="W40">
+        <f t="shared" si="53"/>
         <v>16.454666666666668</v>
       </c>
-      <c r="X40" s="6"/>
-      <c r="Y40" s="6"/>
-      <c r="Z40" s="6"/>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A41" s="6" t="s">
+      <c r="A41" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" t="s">
         <v>46</v>
       </c>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6">
+      <c r="D41">
         <v>1235</v>
       </c>
-      <c r="E41" s="6">
+      <c r="E41">
         <f>_xlfn.XLOOKUP(B41, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.15</v>
       </c>
-      <c r="F41" s="6">
-        <f t="shared" si="33"/>
+      <c r="F41">
+        <f t="shared" si="47"/>
         <v>185.25</v>
       </c>
-      <c r="G41" s="6">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="H41" s="6">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="I41" s="6">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="J41" s="6">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="K41" s="6">
+      <c r="G41">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K41">
         <f>_xlfn.XLOOKUP($B41,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.9</v>
       </c>
-      <c r="L41" s="6">
+      <c r="L41">
         <f>_xlfn.XLOOKUP($B41, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M41" s="6">
+      <c r="M41">
         <f>_xlfn.XLOOKUP($B41, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N41" s="6">
+      <c r="N41">
         <f>_xlfn.XLOOKUP($B41, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O41" s="6">
-        <f>$AC$5</f>
+      <c r="O41">
+        <f t="shared" si="46"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P41" s="6">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="Q41" s="6">
+      <c r="P41">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="Q41">
         <f>_xlfn.XLOOKUP($B41,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.43</v>
       </c>
-      <c r="R41" s="6">
+      <c r="R41">
         <f>_xlfn.XLOOKUP($B41,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.1</v>
       </c>
-      <c r="S41" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T41" s="6">
-        <f>_xlfn.XLOOKUP(A41,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S41">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T41">
+        <f t="shared" si="17"/>
         <v>0.4</v>
       </c>
-      <c r="U41" s="6">
-        <f>_xlfn.XLOOKUP(A41,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V41" s="6">
-        <f t="shared" si="14"/>
+      <c r="U41">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W41" s="6">
-        <f t="shared" si="39"/>
+      <c r="W41">
+        <f t="shared" si="53"/>
         <v>2.1242000000000001</v>
       </c>
-      <c r="X41" s="6"/>
-      <c r="Y41" s="6"/>
-      <c r="Z41" s="6"/>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A42" s="6" t="s">
+      <c r="A42" t="s">
         <v>2</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6">
+      <c r="D42">
         <v>345</v>
       </c>
-      <c r="E42" s="6">
+      <c r="E42">
         <f>_xlfn.XLOOKUP(B42, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="F42" s="6">
-        <f t="shared" si="33"/>
+      <c r="F42">
+        <f t="shared" si="47"/>
         <v>48.300000000000004</v>
       </c>
-      <c r="G42" s="6">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="H42" s="6">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="I42" s="6">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="J42" s="6">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="K42" s="6">
+      <c r="G42">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K42">
         <f>_xlfn.XLOOKUP($B42,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.8</v>
       </c>
-      <c r="L42" s="6">
+      <c r="L42">
         <f>_xlfn.XLOOKUP($B42, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M42" s="6">
+      <c r="M42">
         <f>_xlfn.XLOOKUP($B42, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.2</v>
       </c>
-      <c r="N42" s="6">
+      <c r="N42">
         <f>_xlfn.XLOOKUP($B42, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O42" s="6">
-        <f>$AC$5</f>
+      <c r="O42">
+        <f t="shared" si="46"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P42" s="6">
-        <f t="shared" si="38"/>
+      <c r="P42">
+        <f t="shared" si="52"/>
         <v>10.059280000000001</v>
       </c>
-      <c r="Q42" s="6">
+      <c r="Q42">
         <f>_xlfn.XLOOKUP($B42,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.24</v>
       </c>
-      <c r="R42" s="6">
+      <c r="R42">
         <f>_xlfn.XLOOKUP($B42,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S42" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T42" s="6">
-        <f>_xlfn.XLOOKUP(A42,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U42" s="6">
-        <f>_xlfn.XLOOKUP(A42,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V42" s="6">
-        <f t="shared" si="14"/>
+      <c r="S42">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T42">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W42" s="6">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="X42" s="6"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
+      <c r="W42">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A43" s="6" t="s">
+      <c r="A43" t="s">
         <v>9</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" t="s">
         <v>1</v>
       </c>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6">
+      <c r="D43">
         <v>4356</v>
       </c>
-      <c r="E43" s="6">
+      <c r="E43">
         <f>_xlfn.XLOOKUP(B43, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.72</v>
       </c>
-      <c r="F43" s="6">
-        <f t="shared" si="33"/>
+      <c r="F43">
+        <f t="shared" si="47"/>
         <v>3136.3199999999997</v>
       </c>
-      <c r="G43" s="6">
-        <f t="shared" si="34"/>
-        <v>1E-4</v>
-      </c>
-      <c r="H43" s="6">
-        <f t="shared" si="35"/>
-        <v>0.31363199999999997</v>
-      </c>
-      <c r="I43" s="6">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="J43" s="6">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="K43" s="6">
+      <c r="G43">
+        <f t="shared" si="48"/>
+        <v>1E-3</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="49"/>
+        <v>3.1363199999999996</v>
+      </c>
+      <c r="I43">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K43">
         <f>_xlfn.XLOOKUP($B43,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0</v>
       </c>
-      <c r="L43" s="6">
+      <c r="L43">
         <f>_xlfn.XLOOKUP($B43, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M43" s="6">
+      <c r="M43">
         <f>_xlfn.XLOOKUP($B43, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N43" s="6">
+      <c r="N43">
         <f>_xlfn.XLOOKUP($B43, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O43" s="6">
-        <f>$AC$5</f>
+      <c r="O43">
+        <f t="shared" si="46"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P43" s="6">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="Q43" s="6">
+      <c r="P43">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="Q43">
         <f>_xlfn.XLOOKUP($B43,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.05</v>
       </c>
-      <c r="R43" s="6">
+      <c r="R43">
         <f>_xlfn.XLOOKUP($B43,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S43" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T43" s="6">
-        <f>_xlfn.XLOOKUP(A43,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U43" s="6">
-        <f>_xlfn.XLOOKUP(A43,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V43" s="6">
-        <f t="shared" si="14"/>
+      <c r="S43">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T43">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W43" s="6">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="X43" s="6"/>
-      <c r="Y43" s="6"/>
-      <c r="Z43" s="6"/>
+      <c r="W43">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A44" s="6" t="s">
+      <c r="A44" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" t="s">
         <v>54</v>
       </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6">
+      <c r="D44">
         <v>324</v>
       </c>
-      <c r="E44" s="6">
+      <c r="E44">
         <f>_xlfn.XLOOKUP(B44, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.39</v>
       </c>
-      <c r="F44" s="6">
-        <f t="shared" si="33"/>
+      <c r="F44">
+        <f t="shared" si="47"/>
         <v>126.36</v>
       </c>
-      <c r="G44" s="6">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="H44" s="6">
+      <c r="G44">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="H44">
         <f>G44*F44</f>
         <v>0</v>
       </c>
-      <c r="I44" s="6">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="J44" s="6">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="K44" s="6">
+      <c r="I44">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K44">
         <f>_xlfn.XLOOKUP($B44,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L44" s="6">
+      <c r="L44">
         <f>_xlfn.XLOOKUP($B44, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.7</v>
       </c>
-      <c r="M44" s="6">
+      <c r="M44">
         <f>_xlfn.XLOOKUP($B44, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.1</v>
       </c>
-      <c r="N44" s="6">
+      <c r="N44">
         <f>_xlfn.XLOOKUP($B44, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O44" s="6">
-        <f>$AC$5</f>
+      <c r="O44">
+        <f t="shared" si="46"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P44" s="6">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="Q44" s="6">
+      <c r="P44">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="Q44">
         <f>_xlfn.XLOOKUP($B44,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.24</v>
       </c>
-      <c r="R44" s="6">
+      <c r="R44">
         <f>_xlfn.XLOOKUP($B44,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S44" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T44" s="6">
-        <f>_xlfn.XLOOKUP(A44,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S44">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T44">
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
-      <c r="U44" s="6">
-        <f>_xlfn.XLOOKUP(A44,$X$9:$X$11,AA$9:AA$11, 0)</f>
+      <c r="U44">
+        <f t="shared" si="18"/>
         <v>0.1</v>
       </c>
-      <c r="V44" s="6">
-        <f t="shared" si="14"/>
+      <c r="V44">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W44" s="6">
-        <f t="shared" si="39"/>
+      <c r="W44">
+        <f t="shared" si="53"/>
         <v>6.3685439999999991</v>
       </c>
-      <c r="X44" s="6"/>
-      <c r="Y44" s="6"/>
-      <c r="Z44" s="6"/>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A45" s="6" t="s">
+      <c r="A45" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" t="s">
         <v>8</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C45">
         <v>565</v>
       </c>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6">
+      <c r="E45">
         <f>_xlfn.XLOOKUP(B45, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="F45" s="6">
-        <f t="shared" si="33"/>
+      <c r="F45">
+        <f t="shared" si="47"/>
         <v>565</v>
       </c>
-      <c r="G45" s="6">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="H45" s="6">
-        <f t="shared" ref="H45:H46" si="40">G45*F45</f>
-        <v>0</v>
-      </c>
-      <c r="I45" s="6">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="J45" s="6">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="K45" s="6">
+      <c r="G45">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <f t="shared" ref="H45:H46" si="54">G45*F45</f>
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K45">
         <f>_xlfn.XLOOKUP($B45,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.84</v>
       </c>
-      <c r="L45" s="6">
+      <c r="L45">
         <f>_xlfn.XLOOKUP($B45, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.67</v>
       </c>
-      <c r="M45" s="6">
+      <c r="M45">
         <f>_xlfn.XLOOKUP($B45, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.2</v>
       </c>
-      <c r="N45" s="6">
+      <c r="N45">
         <f>_xlfn.XLOOKUP($B45, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O45" s="6">
-        <f t="shared" ref="O45:O46" si="41">$AC$5</f>
+      <c r="O45">
+        <f t="shared" ref="O45:O46" si="55">$AC$5</f>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P45" s="6">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="Q45" s="6">
+      <c r="P45">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="Q45">
         <f>_xlfn.XLOOKUP($B45,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.39</v>
       </c>
-      <c r="R45" s="6">
+      <c r="R45">
         <f>_xlfn.XLOOKUP($B45,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S45" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T45" s="6">
-        <f>_xlfn.XLOOKUP(A45,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S45">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T45">
+        <f t="shared" si="17"/>
         <v>0.7</v>
       </c>
-      <c r="U45" s="6">
-        <f>_xlfn.XLOOKUP(A45,$X$9:$X$11,AA$9:AA$11, 0)</f>
+      <c r="U45">
+        <f t="shared" si="18"/>
         <v>0.1</v>
       </c>
-      <c r="V45" s="6">
-        <f t="shared" si="14"/>
+      <c r="V45">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W45" s="6">
-        <f t="shared" si="39"/>
+      <c r="W45">
+        <f t="shared" si="53"/>
         <v>46.273499999999991</v>
       </c>
-      <c r="X45" s="6"/>
-      <c r="Y45" s="6"/>
-      <c r="Z45" s="6"/>
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C46" s="4">
+      <c r="C46" s="3">
         <v>7643</v>
       </c>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4">
+      <c r="D46" s="3"/>
+      <c r="E46" s="3">
         <f>_xlfn.XLOOKUP(B46, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.42</v>
       </c>
-      <c r="F46" s="4">
-        <f t="shared" si="33"/>
+      <c r="F46" s="3">
+        <f t="shared" si="47"/>
         <v>7643</v>
       </c>
-      <c r="G46" s="4">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="H46" s="4">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="I46" s="4">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="J46" s="4">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="K46" s="4">
+      <c r="G46" s="3">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="H46" s="3">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="I46" s="3">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="3">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="3">
         <f>_xlfn.XLOOKUP($B46,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.9</v>
       </c>
-      <c r="L46" s="4">
+      <c r="L46" s="3">
         <f>_xlfn.XLOOKUP($B46, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.03</v>
       </c>
-      <c r="M46" s="4">
+      <c r="M46" s="3">
         <f>_xlfn.XLOOKUP($B46, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>1</v>
       </c>
-      <c r="N46" s="4">
+      <c r="N46" s="3">
         <f>_xlfn.XLOOKUP($B46, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O46" s="4">
-        <f t="shared" si="41"/>
+      <c r="O46" s="3">
+        <f t="shared" si="55"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P46" s="4">
-        <f t="shared" si="38"/>
+      <c r="P46" s="3">
+        <f t="shared" si="52"/>
         <v>537.22646999999984</v>
       </c>
-      <c r="Q46" s="4">
+      <c r="Q46" s="3">
         <f>_xlfn.XLOOKUP($B46,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0</v>
       </c>
-      <c r="R46" s="4">
+      <c r="R46" s="3">
         <f>_xlfn.XLOOKUP($B46,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0</v>
       </c>
-      <c r="S46" s="4">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T46" s="4">
-        <f>_xlfn.XLOOKUP(A46,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U46" s="4">
-        <f>_xlfn.XLOOKUP(A46,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V46" s="4">
-        <f t="shared" si="14"/>
+      <c r="S46" s="3">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T46" s="3">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V46" s="3">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W46" s="4">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="X46" s="4"/>
-      <c r="Y46" s="4"/>
-      <c r="Z46" s="4"/>
+      <c r="W46" s="3">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="X46" s="3"/>
+      <c r="Y46" s="3"/>
+      <c r="Z46" s="3"/>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A47" s="6" t="s">
+      <c r="A47" t="s">
         <v>5</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" t="s">
         <v>3</v>
       </c>
-      <c r="C47" s="6">
+      <c r="C47">
         <v>1234</v>
       </c>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6">
+      <c r="E47">
         <f>_xlfn.XLOOKUP(B47, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.5</v>
       </c>
-      <c r="F47" s="6">
+      <c r="F47">
         <f>IF(C47&lt;&gt;"", C47,D47*E47)</f>
         <v>1234</v>
       </c>
-      <c r="G47" s="6">
+      <c r="G47">
         <f>_xlfn.XLOOKUP(A47,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
         <v>7.5000000000000002E-4</v>
       </c>
-      <c r="H47" s="6">
+      <c r="H47">
         <f>G47*F47</f>
         <v>0.92549999999999999</v>
       </c>
-      <c r="I47" s="6">
+      <c r="I47">
         <f>_xlfn.XLOOKUP(A47,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
         <v>9.4300000000000002E-5</v>
       </c>
-      <c r="J47" s="6">
+      <c r="J47">
         <f>F47*I47</f>
         <v>0.1163662</v>
       </c>
-      <c r="K47" s="6">
+      <c r="K47">
         <f>_xlfn.XLOOKUP($B47,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L47" s="6">
+      <c r="L47">
         <f>_xlfn.XLOOKUP($B47, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.38</v>
       </c>
-      <c r="M47" s="6">
+      <c r="M47">
         <f>_xlfn.XLOOKUP($B47, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N47" s="6">
+      <c r="N47">
         <f>_xlfn.XLOOKUP($B47, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O47" s="6">
-        <f>$AC$5</f>
+      <c r="O47">
+        <f t="shared" ref="O47:O54" si="56">$AC$5</f>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P47" s="6">
+      <c r="P47">
         <f>IF(A47&lt;&gt;"Incineration", 0, F47*K47*L47*M47*N47*O47)</f>
         <v>0</v>
       </c>
-      <c r="Q47" s="6">
+      <c r="Q47">
         <f>_xlfn.XLOOKUP($B47,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.15</v>
       </c>
-      <c r="R47" s="6">
+      <c r="R47">
         <f>_xlfn.XLOOKUP($B47,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.84</v>
       </c>
-      <c r="S47" s="6">
+      <c r="S47">
         <f>$AC$7</f>
         <v>0.5</v>
       </c>
-      <c r="T47" s="6">
-        <f>_xlfn.XLOOKUP(A47,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U47" s="6">
-        <f>_xlfn.XLOOKUP(A47,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V47" s="6">
+      <c r="T47">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V47">
         <f>$AC$6</f>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W47" s="6">
+      <c r="W47">
         <f>F47*Q47*R47*S47*T47*V47*(1-U47)</f>
         <v>0</v>
       </c>
-      <c r="X47" s="6">
+      <c r="X47">
         <f>SUM(P47:P56)</f>
         <v>10.059280000000001</v>
       </c>
-      <c r="Y47" s="6">
+      <c r="Y47">
         <f>SUM(H47:H56,W47:W56)</f>
-        <v>87.181038666666666</v>
-      </c>
-      <c r="Z47" s="6">
+        <v>90.003726666666665</v>
+      </c>
+      <c r="Z47">
         <f>SUM(J47:J56)</f>
         <v>0.18124459999999998</v>
       </c>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A48" s="6" t="s">
+      <c r="A48" t="s">
         <v>5</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" t="s">
         <v>3</v>
       </c>
-      <c r="C48" s="6">
+      <c r="C48">
         <v>342</v>
       </c>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6">
+      <c r="E48">
         <f>_xlfn.XLOOKUP(B48, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.5</v>
       </c>
-      <c r="F48" s="6">
-        <f t="shared" ref="F48:F56" si="42">IF(C48&lt;&gt;"", C48,D48*E48)</f>
+      <c r="F48">
+        <f t="shared" ref="F48:F56" si="57">IF(C48&lt;&gt;"", C48,D48*E48)</f>
         <v>342</v>
       </c>
-      <c r="G48" s="6">
-        <f t="shared" ref="G48:G56" si="43">_xlfn.XLOOKUP(A48,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
+      <c r="G48">
+        <f t="shared" ref="G48:G56" si="58">_xlfn.XLOOKUP(A48,$X$5:$X$6,$Y$5:$Y$6, 0)</f>
         <v>7.5000000000000002E-4</v>
       </c>
-      <c r="H48" s="6">
-        <f t="shared" ref="H48:H53" si="44">G48*F48</f>
+      <c r="H48">
+        <f t="shared" ref="H48:H53" si="59">G48*F48</f>
         <v>0.25650000000000001</v>
       </c>
-      <c r="I48" s="6">
-        <f t="shared" ref="I48:I56" si="45">_xlfn.XLOOKUP(A48,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
+      <c r="I48">
+        <f t="shared" ref="I48:I56" si="60">_xlfn.XLOOKUP(A48,$X$5:$X$6,$Z$5:$Z$6, 0)</f>
         <v>9.4300000000000002E-5</v>
       </c>
-      <c r="J48" s="6">
-        <f t="shared" ref="J48:J56" si="46">F48*I48</f>
+      <c r="J48">
+        <f t="shared" ref="J48:J56" si="61">F48*I48</f>
         <v>3.2250599999999997E-2</v>
       </c>
-      <c r="K48" s="6">
+      <c r="K48">
         <f>_xlfn.XLOOKUP($B48,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L48" s="6">
+      <c r="L48">
         <f>_xlfn.XLOOKUP($B48, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.38</v>
       </c>
-      <c r="M48" s="6">
+      <c r="M48">
         <f>_xlfn.XLOOKUP($B48, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N48" s="6">
+      <c r="N48">
         <f>_xlfn.XLOOKUP($B48, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O48" s="6">
-        <f>$AC$5</f>
+      <c r="O48">
+        <f t="shared" si="56"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P48" s="6">
-        <f t="shared" ref="P48:P56" si="47">IF(A48&lt;&gt;"Incineration", 0, F48*K48*L48*M48*N48*O48)</f>
-        <v>0</v>
-      </c>
-      <c r="Q48" s="6">
+      <c r="P48">
+        <f t="shared" ref="P48:P56" si="62">IF(A48&lt;&gt;"Incineration", 0, F48*K48*L48*M48*N48*O48)</f>
+        <v>0</v>
+      </c>
+      <c r="Q48">
         <f>_xlfn.XLOOKUP($B48,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.15</v>
       </c>
-      <c r="R48" s="6">
+      <c r="R48">
         <f>_xlfn.XLOOKUP($B48,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.84</v>
       </c>
-      <c r="S48" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T48" s="6">
-        <f>_xlfn.XLOOKUP(A48,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U48" s="6">
-        <f>_xlfn.XLOOKUP(A48,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V48" s="6">
-        <f t="shared" si="14"/>
+      <c r="S48">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T48">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W48" s="6">
-        <f t="shared" ref="W48:W56" si="48">F48*Q48*R48*S48*T48*V48*(1-U48)</f>
-        <v>0</v>
-      </c>
-      <c r="X48" s="6"/>
-      <c r="Y48" s="6"/>
-      <c r="Z48" s="6"/>
+      <c r="W48">
+        <f t="shared" ref="W48:W56" si="63">F48*Q48*R48*S48*T48*V48*(1-U48)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A49" s="6" t="s">
+      <c r="A49" t="s">
         <v>5</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" t="s">
         <v>4</v>
       </c>
-      <c r="C49" s="6">
+      <c r="C49">
         <v>346</v>
       </c>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6">
+      <c r="E49">
         <f>_xlfn.XLOOKUP(B49, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.24</v>
       </c>
-      <c r="F49" s="6">
-        <f t="shared" si="42"/>
+      <c r="F49">
+        <f t="shared" si="57"/>
         <v>346</v>
       </c>
-      <c r="G49" s="6">
-        <f t="shared" si="43"/>
+      <c r="G49">
+        <f t="shared" si="58"/>
         <v>7.5000000000000002E-4</v>
       </c>
-      <c r="H49" s="6">
-        <f t="shared" si="44"/>
+      <c r="H49">
+        <f t="shared" si="59"/>
         <v>0.25950000000000001</v>
       </c>
-      <c r="I49" s="6">
-        <f t="shared" si="45"/>
+      <c r="I49">
+        <f t="shared" si="60"/>
         <v>9.4300000000000002E-5</v>
       </c>
-      <c r="J49" s="6">
-        <f t="shared" si="46"/>
+      <c r="J49">
+        <f t="shared" si="61"/>
         <v>3.2627799999999998E-2</v>
       </c>
-      <c r="K49" s="6">
+      <c r="K49">
         <f>_xlfn.XLOOKUP($B49,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L49" s="6">
+      <c r="L49">
         <f>_xlfn.XLOOKUP($B49, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.49</v>
       </c>
-      <c r="M49" s="6">
+      <c r="M49">
         <f>_xlfn.XLOOKUP($B49, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N49" s="6">
+      <c r="N49">
         <f>_xlfn.XLOOKUP($B49, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O49" s="6">
-        <f>$AC$5</f>
+      <c r="O49">
+        <f t="shared" si="56"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P49" s="6">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q49" s="6">
+      <c r="P49">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="Q49">
         <f>_xlfn.XLOOKUP($B49,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.2</v>
       </c>
-      <c r="R49" s="6">
+      <c r="R49">
         <f>_xlfn.XLOOKUP($B49,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.47</v>
       </c>
-      <c r="S49" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T49" s="6">
-        <f>_xlfn.XLOOKUP(A49,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U49" s="6">
-        <f>_xlfn.XLOOKUP(A49,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V49" s="6">
-        <f t="shared" si="14"/>
+      <c r="S49">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T49">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W49" s="6">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="X49" s="6"/>
-      <c r="Y49" s="6"/>
-      <c r="Z49" s="6"/>
+      <c r="W49">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A50" s="6" t="s">
+      <c r="A50" t="s">
         <v>40</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" t="s">
         <v>45</v>
       </c>
-      <c r="C50" s="6">
+      <c r="C50">
         <v>1435</v>
       </c>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6">
+      <c r="E50">
         <f>_xlfn.XLOOKUP(B50, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.15</v>
       </c>
-      <c r="F50" s="6">
-        <f t="shared" si="42"/>
+      <c r="F50">
+        <f t="shared" si="57"/>
         <v>1435</v>
       </c>
-      <c r="G50" s="6">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="H50" s="6">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="I50" s="6">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="J50" s="6">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="K50" s="6">
+      <c r="G50">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="K50">
         <f>_xlfn.XLOOKUP($B50,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L50" s="6">
+      <c r="L50">
         <f>_xlfn.XLOOKUP($B50, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M50" s="6">
+      <c r="M50">
         <f>_xlfn.XLOOKUP($B50, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N50" s="6">
+      <c r="N50">
         <f>_xlfn.XLOOKUP($B50, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O50" s="6">
-        <f>$AC$5</f>
+      <c r="O50">
+        <f t="shared" si="56"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P50" s="6">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q50" s="6">
+      <c r="P50">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="Q50">
         <f>_xlfn.XLOOKUP($B50,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.43</v>
       </c>
-      <c r="R50" s="6">
+      <c r="R50">
         <f>_xlfn.XLOOKUP($B50,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.1</v>
       </c>
-      <c r="S50" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T50" s="6">
-        <f>_xlfn.XLOOKUP(A50,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S50">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T50">
+        <f t="shared" si="17"/>
         <v>0.4</v>
       </c>
-      <c r="U50" s="6">
-        <f>_xlfn.XLOOKUP(A50,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V50" s="6">
-        <f t="shared" si="14"/>
+      <c r="U50">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W50" s="6">
-        <f t="shared" si="48"/>
+      <c r="W50">
+        <f t="shared" si="63"/>
         <v>16.454666666666668</v>
       </c>
-      <c r="X50" s="6"/>
-      <c r="Y50" s="6"/>
-      <c r="Z50" s="6"/>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A51" s="6" t="s">
+      <c r="A51" t="s">
         <v>40</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" t="s">
         <v>46</v>
       </c>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6">
+      <c r="D51">
         <v>1235</v>
       </c>
-      <c r="E51" s="6">
+      <c r="E51">
         <f>_xlfn.XLOOKUP(B51, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.15</v>
       </c>
-      <c r="F51" s="6">
-        <f t="shared" si="42"/>
+      <c r="F51">
+        <f t="shared" si="57"/>
         <v>185.25</v>
       </c>
-      <c r="G51" s="6">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="H51" s="6">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="I51" s="6">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="J51" s="6">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="K51" s="6">
+      <c r="G51">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="K51">
         <f>_xlfn.XLOOKUP($B51,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.9</v>
       </c>
-      <c r="L51" s="6">
+      <c r="L51">
         <f>_xlfn.XLOOKUP($B51, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M51" s="6">
+      <c r="M51">
         <f>_xlfn.XLOOKUP($B51, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N51" s="6">
+      <c r="N51">
         <f>_xlfn.XLOOKUP($B51, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O51" s="6">
-        <f>$AC$5</f>
+      <c r="O51">
+        <f t="shared" si="56"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P51" s="6">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q51" s="6">
+      <c r="P51">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="Q51">
         <f>_xlfn.XLOOKUP($B51,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.43</v>
       </c>
-      <c r="R51" s="6">
+      <c r="R51">
         <f>_xlfn.XLOOKUP($B51,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.1</v>
       </c>
-      <c r="S51" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T51" s="6">
-        <f>_xlfn.XLOOKUP(A51,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S51">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T51">
+        <f t="shared" si="17"/>
         <v>0.4</v>
       </c>
-      <c r="U51" s="6">
-        <f>_xlfn.XLOOKUP(A51,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V51" s="6">
-        <f t="shared" si="14"/>
+      <c r="U51">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V51">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W51" s="6">
-        <f t="shared" si="48"/>
+      <c r="W51">
+        <f t="shared" si="63"/>
         <v>2.1242000000000001</v>
       </c>
-      <c r="X51" s="6"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A52" s="6" t="s">
+      <c r="A52" t="s">
         <v>2</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6">
+      <c r="D52">
         <v>345</v>
       </c>
-      <c r="E52" s="6">
+      <c r="E52">
         <f>_xlfn.XLOOKUP(B52, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="F52" s="6">
-        <f t="shared" si="42"/>
+      <c r="F52">
+        <f t="shared" si="57"/>
         <v>48.300000000000004</v>
       </c>
-      <c r="G52" s="6">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="H52" s="6">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="I52" s="6">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="J52" s="6">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="K52" s="6">
+      <c r="G52">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="K52">
         <f>_xlfn.XLOOKUP($B52,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.8</v>
       </c>
-      <c r="L52" s="6">
+      <c r="L52">
         <f>_xlfn.XLOOKUP($B52, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M52" s="6">
+      <c r="M52">
         <f>_xlfn.XLOOKUP($B52, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.2</v>
       </c>
-      <c r="N52" s="6">
+      <c r="N52">
         <f>_xlfn.XLOOKUP($B52, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O52" s="6">
-        <f>$AC$5</f>
+      <c r="O52">
+        <f t="shared" si="56"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P52" s="6">
-        <f t="shared" si="47"/>
+      <c r="P52">
+        <f t="shared" si="62"/>
         <v>10.059280000000001</v>
       </c>
-      <c r="Q52" s="6">
+      <c r="Q52">
         <f>_xlfn.XLOOKUP($B52,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.24</v>
       </c>
-      <c r="R52" s="6">
+      <c r="R52">
         <f>_xlfn.XLOOKUP($B52,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S52" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T52" s="6">
-        <f>_xlfn.XLOOKUP(A52,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U52" s="6">
-        <f>_xlfn.XLOOKUP(A52,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V52" s="6">
-        <f t="shared" si="14"/>
+      <c r="S52">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T52">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U52">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W52" s="6">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="X52" s="6"/>
-      <c r="Y52" s="6"/>
-      <c r="Z52" s="6"/>
+      <c r="W52">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A53" s="6" t="s">
+      <c r="A53" t="s">
         <v>9</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" t="s">
         <v>1</v>
       </c>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6">
+      <c r="D53">
         <v>4356</v>
       </c>
-      <c r="E53" s="6">
+      <c r="E53">
         <f>_xlfn.XLOOKUP(B53, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.72</v>
       </c>
-      <c r="F53" s="6">
-        <f t="shared" si="42"/>
+      <c r="F53">
+        <f t="shared" si="57"/>
         <v>3136.3199999999997</v>
       </c>
-      <c r="G53" s="6">
-        <f t="shared" si="43"/>
-        <v>1E-4</v>
-      </c>
-      <c r="H53" s="6">
-        <f t="shared" si="44"/>
-        <v>0.31363199999999997</v>
-      </c>
-      <c r="I53" s="6">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="J53" s="6">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="K53" s="6">
+      <c r="G53">
+        <f t="shared" si="58"/>
+        <v>1E-3</v>
+      </c>
+      <c r="H53">
+        <f t="shared" si="59"/>
+        <v>3.1363199999999996</v>
+      </c>
+      <c r="I53">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="K53">
         <f>_xlfn.XLOOKUP($B53,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0</v>
       </c>
-      <c r="L53" s="6">
+      <c r="L53">
         <f>_xlfn.XLOOKUP($B53, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.5</v>
       </c>
-      <c r="M53" s="6">
+      <c r="M53">
         <f>_xlfn.XLOOKUP($B53, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0</v>
       </c>
-      <c r="N53" s="6">
+      <c r="N53">
         <f>_xlfn.XLOOKUP($B53, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O53" s="6">
-        <f>$AC$5</f>
+      <c r="O53">
+        <f t="shared" si="56"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P53" s="6">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q53" s="6">
+      <c r="P53">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="Q53">
         <f>_xlfn.XLOOKUP($B53,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.05</v>
       </c>
-      <c r="R53" s="6">
+      <c r="R53">
         <f>_xlfn.XLOOKUP($B53,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S53" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T53" s="6">
-        <f>_xlfn.XLOOKUP(A53,$X$9:$X$11,Z$9:Z$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="U53" s="6">
-        <f>_xlfn.XLOOKUP(A53,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V53" s="6">
-        <f t="shared" si="14"/>
+      <c r="S53">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T53">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="U53">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W53" s="6">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="X53" s="6"/>
-      <c r="Y53" s="6"/>
-      <c r="Z53" s="6"/>
+      <c r="W53">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A54" s="6" t="s">
+      <c r="A54" t="s">
         <v>38</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" t="s">
         <v>54</v>
       </c>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6">
+      <c r="D54">
         <v>324</v>
       </c>
-      <c r="E54" s="6">
+      <c r="E54">
         <f>_xlfn.XLOOKUP(B54, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.39</v>
       </c>
-      <c r="F54" s="6">
-        <f t="shared" si="42"/>
+      <c r="F54">
+        <f t="shared" si="57"/>
         <v>126.36</v>
       </c>
-      <c r="G54" s="6">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="H54" s="6">
+      <c r="G54">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="H54">
         <f>G54*F54</f>
         <v>0</v>
       </c>
-      <c r="I54" s="6">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="J54" s="6">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="K54" s="6">
+      <c r="I54">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="K54">
         <f>_xlfn.XLOOKUP($B54,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.4</v>
       </c>
-      <c r="L54" s="6">
+      <c r="L54">
         <f>_xlfn.XLOOKUP($B54, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.7</v>
       </c>
-      <c r="M54" s="6">
+      <c r="M54">
         <f>_xlfn.XLOOKUP($B54, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.1</v>
       </c>
-      <c r="N54" s="6">
+      <c r="N54">
         <f>_xlfn.XLOOKUP($B54, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O54" s="6">
-        <f>$AC$5</f>
+      <c r="O54">
+        <f t="shared" si="56"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P54" s="6">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q54" s="6">
+      <c r="P54">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="Q54">
         <f>_xlfn.XLOOKUP($B54,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.24</v>
       </c>
-      <c r="R54" s="6">
+      <c r="R54">
         <f>_xlfn.XLOOKUP($B54,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S54" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T54" s="6">
-        <f>_xlfn.XLOOKUP(A54,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S54">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T54">
+        <f t="shared" si="17"/>
         <v>0.8</v>
       </c>
-      <c r="U54" s="6">
-        <f>_xlfn.XLOOKUP(A54,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V54" s="6">
-        <f t="shared" si="14"/>
+      <c r="U54">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V54">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W54" s="6">
-        <f t="shared" si="48"/>
+      <c r="W54">
+        <f t="shared" si="63"/>
         <v>8.08704</v>
       </c>
-      <c r="X54" s="6"/>
-      <c r="Y54" s="6"/>
-      <c r="Z54" s="6"/>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A55" s="6" t="s">
+      <c r="A55" t="s">
         <v>38</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" t="s">
         <v>8</v>
       </c>
-      <c r="C55" s="6">
+      <c r="C55">
         <v>565</v>
       </c>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6">
+      <c r="E55">
         <f>_xlfn.XLOOKUP(B55, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="F55" s="6">
-        <f t="shared" si="42"/>
+      <c r="F55">
+        <f t="shared" si="57"/>
         <v>565</v>
       </c>
-      <c r="G55" s="6">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="H55" s="6">
-        <f t="shared" ref="H55:H56" si="49">G55*F55</f>
-        <v>0</v>
-      </c>
-      <c r="I55" s="6">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="J55" s="6">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="K55" s="6">
+      <c r="G55">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <f t="shared" ref="H55:H56" si="64">G55*F55</f>
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="K55">
         <f>_xlfn.XLOOKUP($B55,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.84</v>
       </c>
-      <c r="L55" s="6">
+      <c r="L55">
         <f>_xlfn.XLOOKUP($B55, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.67</v>
       </c>
-      <c r="M55" s="6">
+      <c r="M55">
         <f>_xlfn.XLOOKUP($B55, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>0.2</v>
       </c>
-      <c r="N55" s="6">
+      <c r="N55">
         <f>_xlfn.XLOOKUP($B55, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O55" s="6">
-        <f t="shared" ref="O55:O56" si="50">$AC$5</f>
+      <c r="O55">
+        <f t="shared" ref="O55:O56" si="65">$AC$5</f>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P55" s="6">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q55" s="6">
+      <c r="P55">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="Q55">
         <f>_xlfn.XLOOKUP($B55,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0.39</v>
       </c>
-      <c r="R55" s="6">
+      <c r="R55">
         <f>_xlfn.XLOOKUP($B55,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0.5</v>
       </c>
-      <c r="S55" s="6">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T55" s="6">
-        <f>_xlfn.XLOOKUP(A55,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S55">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T55">
+        <f t="shared" si="17"/>
         <v>0.8</v>
       </c>
-      <c r="U55" s="6">
-        <f>_xlfn.XLOOKUP(A55,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V55" s="6">
-        <f t="shared" si="14"/>
+      <c r="U55">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V55">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W55" s="6">
-        <f t="shared" si="48"/>
+      <c r="W55">
+        <f t="shared" si="63"/>
         <v>58.76</v>
       </c>
-      <c r="X55" s="6"/>
-      <c r="Y55" s="6"/>
-      <c r="Z55" s="6"/>
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C56" s="4">
+      <c r="C56" s="3">
         <v>7643</v>
       </c>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4">
+      <c r="D56" s="3"/>
+      <c r="E56" s="3">
         <f>_xlfn.XLOOKUP(B56, WasteEFs[w], WasteEFs[VTMw])</f>
         <v>0.42</v>
       </c>
-      <c r="F56" s="4">
-        <f t="shared" si="42"/>
+      <c r="F56" s="3">
+        <f t="shared" si="57"/>
         <v>7643</v>
       </c>
-      <c r="G56" s="4">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="H56" s="4">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="I56" s="4">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="J56" s="4">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="K56" s="4">
+      <c r="G56" s="3">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="H56" s="3">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="I56" s="3">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="3">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="3">
         <f>_xlfn.XLOOKUP($B56,WasteEFs[w],WasteEFs[dmw])</f>
         <v>0.9</v>
       </c>
-      <c r="L56" s="4">
+      <c r="L56" s="3">
         <f>_xlfn.XLOOKUP($B56, WasteEFs[w], WasteEFs[CCw])</f>
         <v>0.03</v>
       </c>
-      <c r="M56" s="4">
+      <c r="M56" s="3">
         <f>_xlfn.XLOOKUP($B56, WasteEFs[w], WasteEFs[FCCw])</f>
         <v>1</v>
       </c>
-      <c r="N56" s="4">
+      <c r="N56" s="3">
         <f>_xlfn.XLOOKUP($B56, WasteEFs[w], WasteEFs[OFw])</f>
         <v>0.71</v>
       </c>
-      <c r="O56" s="4">
-        <f t="shared" si="50"/>
+      <c r="O56" s="3">
+        <f t="shared" si="65"/>
         <v>3.6666666666666665</v>
       </c>
-      <c r="P56" s="4">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q56" s="4">
+      <c r="P56" s="3">
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="Q56" s="3">
         <f>_xlfn.XLOOKUP($B56,WasteEFs[w],WasteEFs[DOCw])</f>
         <v>0</v>
       </c>
-      <c r="R56" s="4">
+      <c r="R56" s="3">
         <f>_xlfn.XLOOKUP($B56,WasteEFs[w],WasteEFs[DOCFw])</f>
         <v>0</v>
       </c>
-      <c r="S56" s="4">
-        <f t="shared" si="13"/>
-        <v>0.5</v>
-      </c>
-      <c r="T56" s="4">
-        <f>_xlfn.XLOOKUP(A56,$X$9:$X$11,Z$9:Z$11, 0)</f>
+      <c r="S56" s="3">
+        <f t="shared" si="25"/>
+        <v>0.5</v>
+      </c>
+      <c r="T56" s="3">
+        <f t="shared" si="17"/>
         <v>0.8</v>
       </c>
-      <c r="U56" s="4">
-        <f>_xlfn.XLOOKUP(A56,$X$9:$X$11,AA$9:AA$11, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="V56" s="4">
-        <f t="shared" si="14"/>
+      <c r="U56" s="3">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="V56" s="3">
+        <f t="shared" si="26"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="W56" s="4">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="X56" s="4"/>
-      <c r="Y56" s="4"/>
-      <c r="Z56" s="4"/>
+      <c r="W56" s="3">
+        <f t="shared" si="63"/>
+        <v>0</v>
+      </c>
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/packages/calculators/src/modules/test/10.1-solid-waste.xlsx
+++ b/packages/calculators/src/modules/test/10.1-solid-waste.xlsx
@@ -3,18 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators/packages/calculators/src/modules/test/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1E3CD2-329B-5E49-B469-EF2BDFED75AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2FDE9F-62D6-0D48-A01B-F475A1722B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15880" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
   <sheets>
     <sheet name="10.1" sheetId="4" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -318,6 +316,34 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="common"/>
+    </sheetNames>
+    <definedNames>
+      <definedName name="common_cch4" refersTo="='common'!$B$3"/>
+      <definedName name="common_cco2" refersTo="='common'!$B$2"/>
+    </definedNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="B2">
+            <v>3.67</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>1.33</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -847,11 +873,11 @@
       </c>
       <c r="N5">
         <f t="shared" ref="N5:N10" si="5">$AC$5</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="O5">
         <f>C5*M5*N5</f>
-        <v>555.5</v>
+        <v>556.005</v>
       </c>
       <c r="P5">
         <f t="shared" ref="P5:P10" si="6">$Y$9</f>
@@ -871,7 +897,7 @@
       </c>
       <c r="T5">
         <f>O5</f>
-        <v>555.5</v>
+        <v>556.005</v>
       </c>
       <c r="U5">
         <f>I5+S5</f>
@@ -894,8 +920,8 @@
         <v>20</v>
       </c>
       <c r="AC5">
-        <f>44/12</f>
-        <v>3.6666666666666665</v>
+        <f>[1]!common_cco2</f>
+        <v>3.67</v>
       </c>
       <c r="AE5" t="s">
         <v>6</v>
@@ -971,11 +997,11 @@
       </c>
       <c r="N6">
         <f t="shared" si="5"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="O6">
         <f t="shared" ref="O6:O10" si="11">C6*M6*N6</f>
-        <v>185.16666666666666</v>
+        <v>185.33500000000001</v>
       </c>
       <c r="P6">
         <f t="shared" si="6"/>
@@ -995,7 +1021,7 @@
       </c>
       <c r="T6">
         <f t="shared" ref="T6:T10" si="13">O6</f>
-        <v>185.16666666666666</v>
+        <v>185.33500000000001</v>
       </c>
       <c r="U6">
         <f t="shared" ref="U6:U10" si="14">I6+S6</f>
@@ -1018,8 +1044,8 @@
         <v>62</v>
       </c>
       <c r="AC6">
-        <f>16/12</f>
-        <v>1.3333333333333333</v>
+        <f>[1]!common_cch4</f>
+        <v>1.33</v>
       </c>
       <c r="AE6" t="s">
         <v>4</v>
@@ -1086,11 +1112,11 @@
       </c>
       <c r="N7">
         <f t="shared" si="5"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="O7">
         <f t="shared" si="11"/>
-        <v>228.49566666666669</v>
+        <v>228.70339000000001</v>
       </c>
       <c r="P7">
         <f t="shared" si="6"/>
@@ -1110,7 +1136,7 @@
       </c>
       <c r="T7">
         <f t="shared" si="13"/>
-        <v>228.49566666666669</v>
+        <v>228.70339000000001</v>
       </c>
       <c r="U7">
         <f t="shared" si="14"/>
@@ -1191,7 +1217,7 @@
       </c>
       <c r="N8">
         <f t="shared" si="5"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="O8">
         <f t="shared" si="11"/>
@@ -1305,11 +1331,11 @@
       </c>
       <c r="N9">
         <f t="shared" si="5"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="O9">
         <f t="shared" si="11"/>
-        <v>434.21583333333336</v>
+        <v>434.61057500000004</v>
       </c>
       <c r="P9">
         <f t="shared" si="6"/>
@@ -1329,7 +1355,7 @@
       </c>
       <c r="T9">
         <f t="shared" si="13"/>
-        <v>434.21583333333336</v>
+        <v>434.61057500000004</v>
       </c>
       <c r="U9">
         <f t="shared" si="14"/>
@@ -1422,7 +1448,7 @@
       </c>
       <c r="N10">
         <f t="shared" si="5"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="O10">
         <f t="shared" si="11"/>
@@ -1720,7 +1746,7 @@
       </c>
       <c r="O17">
         <f t="shared" ref="O17:O24" si="16">$AC$5</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P17">
         <f>IF(A17&lt;&gt;"Incineration", 0, F17*K17*L17*M17*N17*O17)</f>
@@ -1748,7 +1774,7 @@
       </c>
       <c r="V17">
         <f>$AC$6</f>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W17">
         <f>F17*Q17*R17*S17*T17*V17*(1-U17)</f>
@@ -1756,7 +1782,7 @@
       </c>
       <c r="X17">
         <f>SUM(P17:P26)</f>
-        <v>188.51871719999997</v>
+        <v>188.69009785199998</v>
       </c>
       <c r="Y17">
         <f>SUM(H17:H26,W17:W26)</f>
@@ -1819,11 +1845,11 @@
       </c>
       <c r="O18">
         <f t="shared" si="16"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P18">
         <f t="shared" ref="P18:P24" si="24">IF(A18&lt;&gt;"Incineration", 0, F18*K18*L18*M18*N18*O18)</f>
-        <v>3.6860075999999999</v>
+        <v>3.689358516</v>
       </c>
       <c r="Q18">
         <f>_xlfn.XLOOKUP($B18,WasteEFs[w],WasteEFs[DOCw])</f>
@@ -1847,7 +1873,7 @@
       </c>
       <c r="V18">
         <f t="shared" ref="V18:V56" si="26">$AC$6</f>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W18">
         <f t="shared" ref="W18:W24" si="27">F18*Q18*R18*S18*T18*V18*(1-U18)</f>
@@ -1906,7 +1932,7 @@
       </c>
       <c r="O19">
         <f t="shared" si="16"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P19">
         <f t="shared" si="24"/>
@@ -1934,7 +1960,7 @@
       </c>
       <c r="V19">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W19">
         <f t="shared" si="27"/>
@@ -1993,7 +2019,7 @@
       </c>
       <c r="O20">
         <f t="shared" si="16"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P20">
         <f t="shared" si="24"/>
@@ -2021,7 +2047,7 @@
       </c>
       <c r="V20">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W20">
         <f t="shared" si="27"/>
@@ -2080,7 +2106,7 @@
       </c>
       <c r="O21">
         <f t="shared" si="16"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P21">
         <f t="shared" si="24"/>
@@ -2108,7 +2134,7 @@
       </c>
       <c r="V21">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W21">
         <f t="shared" si="27"/>
@@ -2167,11 +2193,11 @@
       </c>
       <c r="O22">
         <f t="shared" si="16"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P22">
         <f t="shared" si="24"/>
-        <v>10.059280000000001</v>
+        <v>10.068424800000003</v>
       </c>
       <c r="Q22">
         <f>_xlfn.XLOOKUP($B22,WasteEFs[w],WasteEFs[DOCw])</f>
@@ -2195,7 +2221,7 @@
       </c>
       <c r="V22">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W22">
         <f t="shared" si="27"/>
@@ -2254,7 +2280,7 @@
       </c>
       <c r="O23">
         <f t="shared" si="16"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P23">
         <f t="shared" si="24"/>
@@ -2282,7 +2308,7 @@
       </c>
       <c r="V23">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W23">
         <f t="shared" si="27"/>
@@ -2341,11 +2367,11 @@
       </c>
       <c r="O24">
         <f t="shared" si="16"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P24">
         <f t="shared" si="24"/>
-        <v>9.2108015999999999</v>
+        <v>9.219175056000001</v>
       </c>
       <c r="Q24">
         <f>_xlfn.XLOOKUP($B24,WasteEFs[w],WasteEFs[DOCw])</f>
@@ -2369,7 +2395,7 @@
       </c>
       <c r="V24">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W24">
         <f t="shared" si="27"/>
@@ -2428,11 +2454,11 @@
       </c>
       <c r="O25">
         <f t="shared" ref="O25:O26" si="33">$AC$5</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P25">
         <f>IF(A25&lt;&gt;"Incineration", 0, F25*K25*L25*M25*N25*O25)</f>
-        <v>165.56262799999996</v>
+        <v>165.71313947999997</v>
       </c>
       <c r="Q25">
         <f>_xlfn.XLOOKUP($B25,WasteEFs[w],WasteEFs[DOCw])</f>
@@ -2456,7 +2482,7 @@
       </c>
       <c r="V25">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W25">
         <f t="shared" ref="W25:W26" si="34">F25*Q25*R25*S25*T25*V25*(1-U25)</f>
@@ -2516,7 +2542,7 @@
       </c>
       <c r="O26" s="3">
         <f t="shared" si="33"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P26" s="3">
         <f t="shared" ref="P26" si="35">IF(A26&lt;&gt;"Incineration", 0, F26*K26*L26*M26*N26*O26)</f>
@@ -2544,7 +2570,7 @@
       </c>
       <c r="V26" s="3">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W26" s="3">
         <f t="shared" si="34"/>
@@ -2606,7 +2632,7 @@
       </c>
       <c r="O27">
         <f t="shared" ref="O27:O34" si="36">$AC$5</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P27">
         <f>IF(A27&lt;&gt;"Incineration", 0, F27*K27*L27*M27*N27*O27)</f>
@@ -2634,11 +2660,11 @@
       </c>
       <c r="V27">
         <f>$AC$6</f>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W27">
         <f>F27*Q27*R27*S27*T27*V27*(1-U27)</f>
-        <v>82.924799999999991</v>
+        <v>82.717488000000003</v>
       </c>
       <c r="X27">
         <f>SUM(P27:P36)</f>
@@ -2646,7 +2672,7 @@
       </c>
       <c r="Y27">
         <f>SUM(H27:H36,W27:W36)</f>
-        <v>231.21257333333332</v>
+        <v>230.63454189999999</v>
       </c>
       <c r="Z27">
         <f>SUM(J27:J36)</f>
@@ -2705,7 +2731,7 @@
       </c>
       <c r="O28">
         <f t="shared" si="36"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P28">
         <f t="shared" ref="P28:P36" si="42">IF(A28&lt;&gt;"Incineration", 0, F28*K28*L28*M28*N28*O28)</f>
@@ -2733,11 +2759,11 @@
       </c>
       <c r="V28">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W28">
         <f t="shared" ref="W28:W36" si="43">F28*Q28*R28*S28*T28*V28*(1-U28)</f>
-        <v>17.875200000000003</v>
+        <v>17.830512000000006</v>
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.2">
@@ -2792,7 +2818,7 @@
       </c>
       <c r="O29">
         <f t="shared" si="36"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P29">
         <f t="shared" si="42"/>
@@ -2820,11 +2846,11 @@
       </c>
       <c r="V29">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W29">
         <f t="shared" si="43"/>
-        <v>13.660080000000001</v>
+        <v>13.6259298</v>
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.2">
@@ -2879,7 +2905,7 @@
       </c>
       <c r="O30">
         <f t="shared" si="36"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P30">
         <f t="shared" si="42"/>
@@ -2907,11 +2933,11 @@
       </c>
       <c r="V30">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W30">
         <f t="shared" si="43"/>
-        <v>32.909333333333336</v>
+        <v>32.827060000000003</v>
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.2">
@@ -2966,7 +2992,7 @@
       </c>
       <c r="O31">
         <f t="shared" si="36"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P31">
         <f t="shared" si="42"/>
@@ -2994,11 +3020,11 @@
       </c>
       <c r="V31">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W31">
         <f t="shared" si="43"/>
-        <v>2.1242000000000001</v>
+        <v>2.1188895000000003</v>
       </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.2">
@@ -3053,7 +3079,7 @@
       </c>
       <c r="O32">
         <f t="shared" si="36"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P32">
         <f t="shared" si="42"/>
@@ -3081,11 +3107,11 @@
       </c>
       <c r="V32">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W32">
         <f t="shared" si="43"/>
-        <v>2.4343199999999996</v>
+        <v>2.4282341999999999</v>
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.2">
@@ -3140,7 +3166,7 @@
       </c>
       <c r="O33">
         <f t="shared" si="36"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P33">
         <f t="shared" si="42"/>
@@ -3168,11 +3194,11 @@
       </c>
       <c r="V33">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W33">
         <f t="shared" si="43"/>
-        <v>41.817599999999999</v>
+        <v>41.713056000000009</v>
       </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.2">
@@ -3227,7 +3253,7 @@
       </c>
       <c r="O34">
         <f t="shared" si="36"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P34">
         <f t="shared" si="42"/>
@@ -3255,11 +3281,11 @@
       </c>
       <c r="V34">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W34">
         <f t="shared" si="43"/>
-        <v>8.08704</v>
+        <v>8.0668224000000013</v>
       </c>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.2">
@@ -3314,7 +3340,7 @@
       </c>
       <c r="O35">
         <f t="shared" ref="O35:O36" si="45">$AC$5</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P35">
         <f t="shared" si="42"/>
@@ -3342,11 +3368,11 @@
       </c>
       <c r="V35">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W35">
         <f t="shared" si="43"/>
-        <v>29.38</v>
+        <v>29.306550000000001</v>
       </c>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.2">
@@ -3402,7 +3428,7 @@
       </c>
       <c r="O36" s="3">
         <f t="shared" si="45"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P36" s="3">
         <f t="shared" si="42"/>
@@ -3430,7 +3456,7 @@
       </c>
       <c r="V36" s="3">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W36" s="3">
         <f t="shared" si="43"/>
@@ -3492,7 +3518,7 @@
       </c>
       <c r="O37">
         <f t="shared" ref="O37:O44" si="46">$AC$5</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P37">
         <f>IF(A37&lt;&gt;"Incineration", 0, F37*K37*L37*M37*N37*O37)</f>
@@ -3520,7 +3546,7 @@
       </c>
       <c r="V37">
         <f>$AC$6</f>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W37">
         <f>F37*Q37*R37*S37*T37*V37*(1-U37)</f>
@@ -3528,11 +3554,11 @@
       </c>
       <c r="X37">
         <f>SUM(P37:P46)</f>
-        <v>547.28574999999978</v>
+        <v>547.78328249999993</v>
       </c>
       <c r="Y37">
         <f>SUM(H37:H46,W37:W46)</f>
-        <v>111.29263066666667</v>
+        <v>111.02520239</v>
       </c>
       <c r="Z37">
         <f>SUM(J37:J46)</f>
@@ -3591,7 +3617,7 @@
       </c>
       <c r="O38">
         <f t="shared" si="46"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P38">
         <f t="shared" ref="P38:P46" si="52">IF(A38&lt;&gt;"Incineration", 0, F38*K38*L38*M38*N38*O38)</f>
@@ -3619,11 +3645,11 @@
       </c>
       <c r="V38">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W38">
         <f t="shared" ref="W38:W46" si="53">F38*Q38*R38*S38*T38*V38*(1-U38)</f>
-        <v>35.750400000000006</v>
+        <v>35.661024000000012</v>
       </c>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.2">
@@ -3678,7 +3704,7 @@
       </c>
       <c r="O39">
         <f t="shared" si="46"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P39">
         <f t="shared" si="52"/>
@@ -3706,7 +3732,7 @@
       </c>
       <c r="V39">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W39">
         <f t="shared" si="53"/>
@@ -3765,7 +3791,7 @@
       </c>
       <c r="O40">
         <f t="shared" si="46"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P40">
         <f t="shared" si="52"/>
@@ -3793,11 +3819,11 @@
       </c>
       <c r="V40">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W40">
         <f t="shared" si="53"/>
-        <v>16.454666666666668</v>
+        <v>16.413530000000002</v>
       </c>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.2">
@@ -3852,7 +3878,7 @@
       </c>
       <c r="O41">
         <f t="shared" si="46"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P41">
         <f t="shared" si="52"/>
@@ -3880,11 +3906,11 @@
       </c>
       <c r="V41">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W41">
         <f t="shared" si="53"/>
-        <v>2.1242000000000001</v>
+        <v>2.1188895000000003</v>
       </c>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.2">
@@ -3939,11 +3965,11 @@
       </c>
       <c r="O42">
         <f t="shared" si="46"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P42">
         <f t="shared" si="52"/>
-        <v>10.059280000000001</v>
+        <v>10.068424800000003</v>
       </c>
       <c r="Q42">
         <f>_xlfn.XLOOKUP($B42,WasteEFs[w],WasteEFs[DOCw])</f>
@@ -3967,7 +3993,7 @@
       </c>
       <c r="V42">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W42">
         <f t="shared" si="53"/>
@@ -4026,7 +4052,7 @@
       </c>
       <c r="O43">
         <f t="shared" si="46"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P43">
         <f t="shared" si="52"/>
@@ -4054,7 +4080,7 @@
       </c>
       <c r="V43">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W43">
         <f t="shared" si="53"/>
@@ -4113,7 +4139,7 @@
       </c>
       <c r="O44">
         <f t="shared" si="46"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P44">
         <f t="shared" si="52"/>
@@ -4141,11 +4167,11 @@
       </c>
       <c r="V44">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W44">
         <f t="shared" si="53"/>
-        <v>6.3685439999999991</v>
+        <v>6.3526226399999999</v>
       </c>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.2">
@@ -4200,7 +4226,7 @@
       </c>
       <c r="O45">
         <f t="shared" ref="O45:O46" si="55">$AC$5</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P45">
         <f t="shared" si="52"/>
@@ -4228,11 +4254,11 @@
       </c>
       <c r="V45">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W45">
         <f t="shared" si="53"/>
-        <v>46.273499999999991</v>
+        <v>46.157816249999996</v>
       </c>
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.2">
@@ -4288,11 +4314,11 @@
       </c>
       <c r="O46" s="3">
         <f t="shared" si="55"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P46" s="3">
         <f t="shared" si="52"/>
-        <v>537.22646999999984</v>
+        <v>537.71485769999992</v>
       </c>
       <c r="Q46" s="3">
         <f>_xlfn.XLOOKUP($B46,WasteEFs[w],WasteEFs[DOCw])</f>
@@ -4316,7 +4342,7 @@
       </c>
       <c r="V46" s="3">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W46" s="3">
         <f t="shared" si="53"/>
@@ -4378,7 +4404,7 @@
       </c>
       <c r="O47">
         <f t="shared" ref="O47:O54" si="56">$AC$5</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P47">
         <f>IF(A47&lt;&gt;"Incineration", 0, F47*K47*L47*M47*N47*O47)</f>
@@ -4406,7 +4432,7 @@
       </c>
       <c r="V47">
         <f>$AC$6</f>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W47">
         <f>F47*Q47*R47*S47*T47*V47*(1-U47)</f>
@@ -4414,11 +4440,11 @@
       </c>
       <c r="X47">
         <f>SUM(P47:P56)</f>
-        <v>10.059280000000001</v>
+        <v>10.068424800000003</v>
       </c>
       <c r="Y47">
         <f>SUM(H47:H56,W47:W56)</f>
-        <v>90.003726666666665</v>
+        <v>89.790161900000015</v>
       </c>
       <c r="Z47">
         <f>SUM(J47:J56)</f>
@@ -4477,7 +4503,7 @@
       </c>
       <c r="O48">
         <f t="shared" si="56"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P48">
         <f t="shared" ref="P48:P56" si="62">IF(A48&lt;&gt;"Incineration", 0, F48*K48*L48*M48*N48*O48)</f>
@@ -4505,7 +4531,7 @@
       </c>
       <c r="V48">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W48">
         <f t="shared" ref="W48:W56" si="63">F48*Q48*R48*S48*T48*V48*(1-U48)</f>
@@ -4564,7 +4590,7 @@
       </c>
       <c r="O49">
         <f t="shared" si="56"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P49">
         <f t="shared" si="62"/>
@@ -4592,7 +4618,7 @@
       </c>
       <c r="V49">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W49">
         <f t="shared" si="63"/>
@@ -4651,7 +4677,7 @@
       </c>
       <c r="O50">
         <f t="shared" si="56"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P50">
         <f t="shared" si="62"/>
@@ -4679,11 +4705,11 @@
       </c>
       <c r="V50">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W50">
         <f t="shared" si="63"/>
-        <v>16.454666666666668</v>
+        <v>16.413530000000002</v>
       </c>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.2">
@@ -4738,7 +4764,7 @@
       </c>
       <c r="O51">
         <f t="shared" si="56"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P51">
         <f t="shared" si="62"/>
@@ -4766,11 +4792,11 @@
       </c>
       <c r="V51">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W51">
         <f t="shared" si="63"/>
-        <v>2.1242000000000001</v>
+        <v>2.1188895000000003</v>
       </c>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.2">
@@ -4825,11 +4851,11 @@
       </c>
       <c r="O52">
         <f t="shared" si="56"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P52">
         <f t="shared" si="62"/>
-        <v>10.059280000000001</v>
+        <v>10.068424800000003</v>
       </c>
       <c r="Q52">
         <f>_xlfn.XLOOKUP($B52,WasteEFs[w],WasteEFs[DOCw])</f>
@@ -4853,7 +4879,7 @@
       </c>
       <c r="V52">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W52">
         <f t="shared" si="63"/>
@@ -4912,7 +4938,7 @@
       </c>
       <c r="O53">
         <f t="shared" si="56"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P53">
         <f t="shared" si="62"/>
@@ -4940,7 +4966,7 @@
       </c>
       <c r="V53">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W53">
         <f t="shared" si="63"/>
@@ -4999,7 +5025,7 @@
       </c>
       <c r="O54">
         <f t="shared" si="56"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P54">
         <f t="shared" si="62"/>
@@ -5027,11 +5053,11 @@
       </c>
       <c r="V54">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W54">
         <f t="shared" si="63"/>
-        <v>8.08704</v>
+        <v>8.0668224000000013</v>
       </c>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.2">
@@ -5086,7 +5112,7 @@
       </c>
       <c r="O55">
         <f t="shared" ref="O55:O56" si="65">$AC$5</f>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P55">
         <f t="shared" si="62"/>
@@ -5114,11 +5140,11 @@
       </c>
       <c r="V55">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W55">
         <f t="shared" si="63"/>
-        <v>58.76</v>
+        <v>58.613100000000003</v>
       </c>
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.2">
@@ -5174,7 +5200,7 @@
       </c>
       <c r="O56" s="3">
         <f t="shared" si="65"/>
-        <v>3.6666666666666665</v>
+        <v>3.67</v>
       </c>
       <c r="P56" s="3">
         <f t="shared" si="62"/>
@@ -5202,7 +5228,7 @@
       </c>
       <c r="V56" s="3">
         <f t="shared" si="26"/>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="W56" s="3">
         <f t="shared" si="63"/>

--- a/packages/calculators/src/modules/test/10.1-solid-waste.xlsx
+++ b/packages/calculators/src/modules/test/10.1-solid-waste.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB77C36-C68E-D748-B59F-24285B8FDE41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF2FDE9F-62D6-0D48-A01B-F475A1722B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15880" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15880" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
   <sheets>
     <sheet name="10.1" sheetId="4" r:id="rId1"/>
@@ -849,11 +849,11 @@
       </c>
       <c r="H5">
         <f t="shared" ref="H5:H10" si="1">$Y$6</f>
-        <v>1E-4</v>
+        <v>1E-3</v>
       </c>
       <c r="I5">
         <f>A5*G5+B5*H5</f>
-        <v>0.95</v>
+        <v>2.75</v>
       </c>
       <c r="J5">
         <f t="shared" ref="J5:J10" si="2">$Z$5</f>
@@ -901,7 +901,7 @@
       </c>
       <c r="U5">
         <f>I5+S5</f>
-        <v>564.25</v>
+        <v>566.04999999999995</v>
       </c>
       <c r="V5">
         <f>L5</f>
@@ -973,11 +973,11 @@
       </c>
       <c r="H6">
         <f t="shared" si="1"/>
-        <v>1E-4</v>
+        <v>1E-3</v>
       </c>
       <c r="I6">
         <f t="shared" ref="I6:I10" si="9">A6*G6+B6*H6</f>
-        <v>0.85</v>
+        <v>1.75</v>
       </c>
       <c r="J6">
         <f t="shared" si="2"/>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="U6">
         <f t="shared" ref="U6:U10" si="14">I6+S6</f>
-        <v>115.65</v>
+        <v>116.55000000000001</v>
       </c>
       <c r="V6">
         <f t="shared" ref="V6:V10" si="15">L6</f>
@@ -1035,7 +1035,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>1E-4</v>
+        <v>1E-3</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1088,11 +1088,11 @@
       </c>
       <c r="H7">
         <f t="shared" si="1"/>
-        <v>1E-4</v>
+        <v>1E-3</v>
       </c>
       <c r="I7">
         <f t="shared" si="9"/>
-        <v>0.95</v>
+        <v>2.75</v>
       </c>
       <c r="J7">
         <f t="shared" si="2"/>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="U7">
         <f t="shared" si="14"/>
-        <v>0.95</v>
+        <v>2.75</v>
       </c>
       <c r="V7">
         <f t="shared" si="15"/>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="H8">
         <f t="shared" si="1"/>
-        <v>1E-4</v>
+        <v>1E-3</v>
       </c>
       <c r="I8">
         <f t="shared" si="9"/>
@@ -1307,11 +1307,11 @@
       </c>
       <c r="H9">
         <f t="shared" si="1"/>
-        <v>1E-4</v>
+        <v>1E-3</v>
       </c>
       <c r="I9">
         <f t="shared" si="9"/>
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="J9">
         <f t="shared" si="2"/>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="U9">
         <f t="shared" si="14"/>
-        <v>438</v>
+        <v>439.8</v>
       </c>
       <c r="V9">
         <f t="shared" si="15"/>
@@ -1424,11 +1424,11 @@
       </c>
       <c r="H10">
         <f t="shared" si="1"/>
-        <v>1E-4</v>
+        <v>1E-3</v>
       </c>
       <c r="I10">
         <f t="shared" si="9"/>
-        <v>0.95</v>
+        <v>2.75</v>
       </c>
       <c r="J10">
         <f t="shared" si="2"/>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="U10">
         <f t="shared" si="14"/>
-        <v>564.25</v>
+        <v>566.04999999999995</v>
       </c>
       <c r="V10">
         <f t="shared" si="15"/>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="Y37">
         <f>SUM(H37:H46,W37:W46)</f>
-        <v>108.20251439</v>
+        <v>111.02520239</v>
       </c>
       <c r="Z37">
         <f>SUM(J37:J46)</f>
@@ -4020,11 +4020,11 @@
       </c>
       <c r="G43">
         <f t="shared" si="48"/>
-        <v>1E-4</v>
+        <v>1E-3</v>
       </c>
       <c r="H43">
         <f t="shared" si="49"/>
-        <v>0.31363199999999997</v>
+        <v>3.1363199999999996</v>
       </c>
       <c r="I43">
         <f t="shared" si="50"/>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="Y47">
         <f>SUM(H47:H56,W47:W56)</f>
-        <v>86.967473900000016</v>
+        <v>89.790161900000015</v>
       </c>
       <c r="Z47">
         <f>SUM(J47:J56)</f>
@@ -4906,11 +4906,11 @@
       </c>
       <c r="G53">
         <f t="shared" si="58"/>
-        <v>1E-4</v>
+        <v>1E-3</v>
       </c>
       <c r="H53">
         <f t="shared" si="59"/>
-        <v>0.31363199999999997</v>
+        <v>3.1363199999999996</v>
       </c>
       <c r="I53">
         <f t="shared" si="60"/>
